--- a/ExactMass_Impurities.xlsx
+++ b/ExactMass_Impurities.xlsx
@@ -1793,7 +1793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA150"/>
+  <dimension ref="A1:AA156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2064,133 +2064,82 @@
         </is>
       </c>
       <c r="B7" s="11">
-        <f>CONCATENATE(B6, C6, D6, E6, F6, G6, H6, I6, J6, K6, L6, M6, N6, O6, P6, Q6, R6, S6, T6, U6, V6, W6, X6, Y6, Z6, AA6)</f>
+        <f>CONCATENATE(B6, C6, D6, E6, F6, G6, H6, I6, J6, K6, L6, M6, N6, O6, P6, Q6, R6, S6, T6, U6, V6, W6, X6, Y6, Z6, AA6) &amp; IF(OR(B9="",B9=0),"",IF(ABS(B9)=1,IF(B9&gt;0,"⁺","⁻"),SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TEXT(ABS(B9),"0"),"0","⁰"),"1","¹"),"2","²"),"3","³"),"4","⁴"),"5","⁵"),"6","⁶"),"7","⁷"),"8","⁸"),"9","⁹")&amp;IF(B9&gt;0,"⁺","⁻")))</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
+          <t>电荷数 z</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
           <t>使用说明：</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>1. 输入一个同位素修饰的分子式：第3行选元素，第4行选同位素种类（natural=天然，或质量数如 2=氘D、13=¹³C），第5行输入原子个数</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>2. 点击"列举杂质"按钮，枚举该修饰分子与天然化合物之间的所有同位素取代杂质（含天然形式，不含输入本身）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>3. 例：输入 C2D3 → 输出 C2H3（全天然）、C2H2D、C2HD2</t>
+          <t>1. 输入一个同位素修饰的分子式：第3行选元素，第4行选同位素种类（natural=天然，或质量数如 2=氘D、13=¹³C），第5行输入原子个数</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>4. natural 列（如 C natural）不参与枚举——天然同位素杂质（如 ¹³C）忽略，不列举</t>
+          <t>2. 第9行电荷数 z（可正可负，0=中性分子不加电荷）</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>输出：同位素取代杂质（每杂质 4 行：名称 / 元素 / 同位素 / 个数）</t>
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>3. 点击"列举杂质"按钮，枚举该修饰分子与天然化合物之间的所有同位素取代杂质（含天然形式，不含输入本身）</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>6. 需要本机安装 Python 与 molmass 库：pip install molmass</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="n"/>
-      <c r="C15" s="14" t="n"/>
-      <c r="D15" s="15" t="n"/>
-      <c r="E15" s="15" t="n"/>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
-      <c r="H15" s="15" t="n"/>
-      <c r="I15" s="15" t="n"/>
-      <c r="J15" s="15" t="n"/>
-      <c r="K15" s="15" t="n"/>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>4. 例：输入 C2D3（z=1）→ 输出 C₂H₃⁺（全天然）、C₂H₂D⁺、C₂HD₂⁺</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="n"/>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="15" t="n"/>
-      <c r="F16" s="15" t="n"/>
-      <c r="G16" s="15" t="n"/>
-      <c r="H16" s="15" t="n"/>
-      <c r="I16" s="15" t="n"/>
-      <c r="J16" s="15" t="n"/>
-      <c r="K16" s="15" t="n"/>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>5. natural 列（如 C natural）不参与枚举——天然同位素杂质（如 ¹³C）忽略，不列举</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="n"/>
-      <c r="B17" s="14" t="n"/>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="15" t="n"/>
-      <c r="E17" s="15" t="n"/>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
-      <c r="H17" s="15" t="n"/>
-      <c r="I17" s="15" t="n"/>
-      <c r="J17" s="15" t="n"/>
-      <c r="K17" s="15" t="n"/>
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>6. 多个修饰同位素列时按组合枚举（笛卡尔积）；修饰原子数为 n 时输出 n 个杂质</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="n"/>
-      <c r="B18" s="14" t="n"/>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="15" t="n"/>
-      <c r="E18" s="15" t="n"/>
-      <c r="F18" s="15" t="n"/>
-      <c r="G18" s="15" t="n"/>
-      <c r="H18" s="15" t="n"/>
-      <c r="I18" s="15" t="n"/>
-      <c r="J18" s="15" t="n"/>
-      <c r="K18" s="15" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="n"/>
-      <c r="B19" s="14" t="n"/>
-      <c r="C19" s="14" t="n"/>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="15" t="n"/>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
-      <c r="H19" s="15" t="n"/>
-      <c r="I19" s="15" t="n"/>
-      <c r="J19" s="15" t="n"/>
-      <c r="K19" s="15" t="n"/>
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>7. 需要本机安装 Python 与 molmass 库：pip install molmass</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="n"/>
-      <c r="B20" s="14" t="n"/>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="15" t="n"/>
-      <c r="E20" s="15" t="n"/>
-      <c r="F20" s="15" t="n"/>
-      <c r="G20" s="15" t="n"/>
-      <c r="H20" s="15" t="n"/>
-      <c r="I20" s="15" t="n"/>
-      <c r="J20" s="15" t="n"/>
-      <c r="K20" s="15" t="n"/>
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>输出：同位素取代杂质（每杂质 4 行：分子式 / 元素 / 同位素种类 / 原子个数）</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="n"/>
@@ -3674,8 +3623,86 @@
       <c r="J134" s="15" t="n"/>
       <c r="K134" s="15" t="n"/>
     </row>
-    <row r="150">
-      <c r="A150" s="16" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="13" t="n"/>
+      <c r="B135" s="14" t="n"/>
+      <c r="C135" s="14" t="n"/>
+      <c r="D135" s="15" t="n"/>
+      <c r="E135" s="15" t="n"/>
+      <c r="F135" s="15" t="n"/>
+      <c r="G135" s="15" t="n"/>
+      <c r="H135" s="15" t="n"/>
+      <c r="I135" s="15" t="n"/>
+      <c r="J135" s="15" t="n"/>
+      <c r="K135" s="15" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="13" t="n"/>
+      <c r="B136" s="14" t="n"/>
+      <c r="C136" s="14" t="n"/>
+      <c r="D136" s="15" t="n"/>
+      <c r="E136" s="15" t="n"/>
+      <c r="F136" s="15" t="n"/>
+      <c r="G136" s="15" t="n"/>
+      <c r="H136" s="15" t="n"/>
+      <c r="I136" s="15" t="n"/>
+      <c r="J136" s="15" t="n"/>
+      <c r="K136" s="15" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="13" t="n"/>
+      <c r="B137" s="14" t="n"/>
+      <c r="C137" s="14" t="n"/>
+      <c r="D137" s="15" t="n"/>
+      <c r="E137" s="15" t="n"/>
+      <c r="F137" s="15" t="n"/>
+      <c r="G137" s="15" t="n"/>
+      <c r="H137" s="15" t="n"/>
+      <c r="I137" s="15" t="n"/>
+      <c r="J137" s="15" t="n"/>
+      <c r="K137" s="15" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="13" t="n"/>
+      <c r="B138" s="14" t="n"/>
+      <c r="C138" s="14" t="n"/>
+      <c r="D138" s="15" t="n"/>
+      <c r="E138" s="15" t="n"/>
+      <c r="F138" s="15" t="n"/>
+      <c r="G138" s="15" t="n"/>
+      <c r="H138" s="15" t="n"/>
+      <c r="I138" s="15" t="n"/>
+      <c r="J138" s="15" t="n"/>
+      <c r="K138" s="15" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="13" t="n"/>
+      <c r="B139" s="14" t="n"/>
+      <c r="C139" s="14" t="n"/>
+      <c r="D139" s="15" t="n"/>
+      <c r="E139" s="15" t="n"/>
+      <c r="F139" s="15" t="n"/>
+      <c r="G139" s="15" t="n"/>
+      <c r="H139" s="15" t="n"/>
+      <c r="I139" s="15" t="n"/>
+      <c r="J139" s="15" t="n"/>
+      <c r="K139" s="15" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="13" t="n"/>
+      <c r="B140" s="14" t="n"/>
+      <c r="C140" s="14" t="n"/>
+      <c r="D140" s="15" t="n"/>
+      <c r="E140" s="15" t="n"/>
+      <c r="F140" s="15" t="n"/>
+      <c r="G140" s="15" t="n"/>
+      <c r="H140" s="15" t="n"/>
+      <c r="I140" s="15" t="n"/>
+      <c r="J140" s="15" t="n"/>
+      <c r="K140" s="15" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="16" t="inlineStr">
         <is>
           <t>▶ 按钮"列举杂质"由构建脚本自动放置（E40 区域）</t>
         </is>

--- a/ExactMass_Impurities.xlsx
+++ b/ExactMass_Impurities.xlsx
@@ -1793,7 +1793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA156"/>
+  <dimension ref="A1:AA630"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3701,8 +3701,6248 @@
       <c r="J140" s="15" t="n"/>
       <c r="K140" s="15" t="n"/>
     </row>
+    <row r="141">
+      <c r="A141" s="13" t="n"/>
+      <c r="B141" s="14" t="n"/>
+      <c r="C141" s="14" t="n"/>
+      <c r="D141" s="15" t="n"/>
+      <c r="E141" s="15" t="n"/>
+      <c r="F141" s="15" t="n"/>
+      <c r="G141" s="15" t="n"/>
+      <c r="H141" s="15" t="n"/>
+      <c r="I141" s="15" t="n"/>
+      <c r="J141" s="15" t="n"/>
+      <c r="K141" s="15" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="13" t="n"/>
+      <c r="B142" s="14" t="n"/>
+      <c r="C142" s="14" t="n"/>
+      <c r="D142" s="15" t="n"/>
+      <c r="E142" s="15" t="n"/>
+      <c r="F142" s="15" t="n"/>
+      <c r="G142" s="15" t="n"/>
+      <c r="H142" s="15" t="n"/>
+      <c r="I142" s="15" t="n"/>
+      <c r="J142" s="15" t="n"/>
+      <c r="K142" s="15" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="13" t="n"/>
+      <c r="B143" s="14" t="n"/>
+      <c r="C143" s="14" t="n"/>
+      <c r="D143" s="15" t="n"/>
+      <c r="E143" s="15" t="n"/>
+      <c r="F143" s="15" t="n"/>
+      <c r="G143" s="15" t="n"/>
+      <c r="H143" s="15" t="n"/>
+      <c r="I143" s="15" t="n"/>
+      <c r="J143" s="15" t="n"/>
+      <c r="K143" s="15" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="13" t="n"/>
+      <c r="B144" s="14" t="n"/>
+      <c r="C144" s="14" t="n"/>
+      <c r="D144" s="15" t="n"/>
+      <c r="E144" s="15" t="n"/>
+      <c r="F144" s="15" t="n"/>
+      <c r="G144" s="15" t="n"/>
+      <c r="H144" s="15" t="n"/>
+      <c r="I144" s="15" t="n"/>
+      <c r="J144" s="15" t="n"/>
+      <c r="K144" s="15" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="13" t="n"/>
+      <c r="B145" s="14" t="n"/>
+      <c r="C145" s="14" t="n"/>
+      <c r="D145" s="15" t="n"/>
+      <c r="E145" s="15" t="n"/>
+      <c r="F145" s="15" t="n"/>
+      <c r="G145" s="15" t="n"/>
+      <c r="H145" s="15" t="n"/>
+      <c r="I145" s="15" t="n"/>
+      <c r="J145" s="15" t="n"/>
+      <c r="K145" s="15" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="13" t="n"/>
+      <c r="B146" s="14" t="n"/>
+      <c r="C146" s="14" t="n"/>
+      <c r="D146" s="15" t="n"/>
+      <c r="E146" s="15" t="n"/>
+      <c r="F146" s="15" t="n"/>
+      <c r="G146" s="15" t="n"/>
+      <c r="H146" s="15" t="n"/>
+      <c r="I146" s="15" t="n"/>
+      <c r="J146" s="15" t="n"/>
+      <c r="K146" s="15" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="13" t="n"/>
+      <c r="B147" s="14" t="n"/>
+      <c r="C147" s="14" t="n"/>
+      <c r="D147" s="15" t="n"/>
+      <c r="E147" s="15" t="n"/>
+      <c r="F147" s="15" t="n"/>
+      <c r="G147" s="15" t="n"/>
+      <c r="H147" s="15" t="n"/>
+      <c r="I147" s="15" t="n"/>
+      <c r="J147" s="15" t="n"/>
+      <c r="K147" s="15" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="13" t="n"/>
+      <c r="B148" s="14" t="n"/>
+      <c r="C148" s="14" t="n"/>
+      <c r="D148" s="15" t="n"/>
+      <c r="E148" s="15" t="n"/>
+      <c r="F148" s="15" t="n"/>
+      <c r="G148" s="15" t="n"/>
+      <c r="H148" s="15" t="n"/>
+      <c r="I148" s="15" t="n"/>
+      <c r="J148" s="15" t="n"/>
+      <c r="K148" s="15" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="13" t="n"/>
+      <c r="B149" s="14" t="n"/>
+      <c r="C149" s="14" t="n"/>
+      <c r="D149" s="15" t="n"/>
+      <c r="E149" s="15" t="n"/>
+      <c r="F149" s="15" t="n"/>
+      <c r="G149" s="15" t="n"/>
+      <c r="H149" s="15" t="n"/>
+      <c r="I149" s="15" t="n"/>
+      <c r="J149" s="15" t="n"/>
+      <c r="K149" s="15" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="13" t="n"/>
+      <c r="B150" s="14" t="n"/>
+      <c r="C150" s="14" t="n"/>
+      <c r="D150" s="15" t="n"/>
+      <c r="E150" s="15" t="n"/>
+      <c r="F150" s="15" t="n"/>
+      <c r="G150" s="15" t="n"/>
+      <c r="H150" s="15" t="n"/>
+      <c r="I150" s="15" t="n"/>
+      <c r="J150" s="15" t="n"/>
+      <c r="K150" s="15" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="13" t="n"/>
+      <c r="B151" s="14" t="n"/>
+      <c r="C151" s="14" t="n"/>
+      <c r="D151" s="15" t="n"/>
+      <c r="E151" s="15" t="n"/>
+      <c r="F151" s="15" t="n"/>
+      <c r="G151" s="15" t="n"/>
+      <c r="H151" s="15" t="n"/>
+      <c r="I151" s="15" t="n"/>
+      <c r="J151" s="15" t="n"/>
+      <c r="K151" s="15" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="13" t="n"/>
+      <c r="B152" s="14" t="n"/>
+      <c r="C152" s="14" t="n"/>
+      <c r="D152" s="15" t="n"/>
+      <c r="E152" s="15" t="n"/>
+      <c r="F152" s="15" t="n"/>
+      <c r="G152" s="15" t="n"/>
+      <c r="H152" s="15" t="n"/>
+      <c r="I152" s="15" t="n"/>
+      <c r="J152" s="15" t="n"/>
+      <c r="K152" s="15" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="13" t="n"/>
+      <c r="B153" s="14" t="n"/>
+      <c r="C153" s="14" t="n"/>
+      <c r="D153" s="15" t="n"/>
+      <c r="E153" s="15" t="n"/>
+      <c r="F153" s="15" t="n"/>
+      <c r="G153" s="15" t="n"/>
+      <c r="H153" s="15" t="n"/>
+      <c r="I153" s="15" t="n"/>
+      <c r="J153" s="15" t="n"/>
+      <c r="K153" s="15" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="13" t="n"/>
+      <c r="B154" s="14" t="n"/>
+      <c r="C154" s="14" t="n"/>
+      <c r="D154" s="15" t="n"/>
+      <c r="E154" s="15" t="n"/>
+      <c r="F154" s="15" t="n"/>
+      <c r="G154" s="15" t="n"/>
+      <c r="H154" s="15" t="n"/>
+      <c r="I154" s="15" t="n"/>
+      <c r="J154" s="15" t="n"/>
+      <c r="K154" s="15" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="13" t="n"/>
+      <c r="B155" s="14" t="n"/>
+      <c r="C155" s="14" t="n"/>
+      <c r="D155" s="15" t="n"/>
+      <c r="E155" s="15" t="n"/>
+      <c r="F155" s="15" t="n"/>
+      <c r="G155" s="15" t="n"/>
+      <c r="H155" s="15" t="n"/>
+      <c r="I155" s="15" t="n"/>
+      <c r="J155" s="15" t="n"/>
+      <c r="K155" s="15" t="n"/>
+    </row>
     <row r="156">
-      <c r="A156" s="16" t="inlineStr">
+      <c r="A156" s="13" t="n"/>
+      <c r="B156" s="14" t="n"/>
+      <c r="C156" s="14" t="n"/>
+      <c r="D156" s="15" t="n"/>
+      <c r="E156" s="15" t="n"/>
+      <c r="F156" s="15" t="n"/>
+      <c r="G156" s="15" t="n"/>
+      <c r="H156" s="15" t="n"/>
+      <c r="I156" s="15" t="n"/>
+      <c r="J156" s="15" t="n"/>
+      <c r="K156" s="15" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="13" t="n"/>
+      <c r="B157" s="14" t="n"/>
+      <c r="C157" s="14" t="n"/>
+      <c r="D157" s="15" t="n"/>
+      <c r="E157" s="15" t="n"/>
+      <c r="F157" s="15" t="n"/>
+      <c r="G157" s="15" t="n"/>
+      <c r="H157" s="15" t="n"/>
+      <c r="I157" s="15" t="n"/>
+      <c r="J157" s="15" t="n"/>
+      <c r="K157" s="15" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="13" t="n"/>
+      <c r="B158" s="14" t="n"/>
+      <c r="C158" s="14" t="n"/>
+      <c r="D158" s="15" t="n"/>
+      <c r="E158" s="15" t="n"/>
+      <c r="F158" s="15" t="n"/>
+      <c r="G158" s="15" t="n"/>
+      <c r="H158" s="15" t="n"/>
+      <c r="I158" s="15" t="n"/>
+      <c r="J158" s="15" t="n"/>
+      <c r="K158" s="15" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="13" t="n"/>
+      <c r="B159" s="14" t="n"/>
+      <c r="C159" s="14" t="n"/>
+      <c r="D159" s="15" t="n"/>
+      <c r="E159" s="15" t="n"/>
+      <c r="F159" s="15" t="n"/>
+      <c r="G159" s="15" t="n"/>
+      <c r="H159" s="15" t="n"/>
+      <c r="I159" s="15" t="n"/>
+      <c r="J159" s="15" t="n"/>
+      <c r="K159" s="15" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="13" t="n"/>
+      <c r="B160" s="14" t="n"/>
+      <c r="C160" s="14" t="n"/>
+      <c r="D160" s="15" t="n"/>
+      <c r="E160" s="15" t="n"/>
+      <c r="F160" s="15" t="n"/>
+      <c r="G160" s="15" t="n"/>
+      <c r="H160" s="15" t="n"/>
+      <c r="I160" s="15" t="n"/>
+      <c r="J160" s="15" t="n"/>
+      <c r="K160" s="15" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="13" t="n"/>
+      <c r="B161" s="14" t="n"/>
+      <c r="C161" s="14" t="n"/>
+      <c r="D161" s="15" t="n"/>
+      <c r="E161" s="15" t="n"/>
+      <c r="F161" s="15" t="n"/>
+      <c r="G161" s="15" t="n"/>
+      <c r="H161" s="15" t="n"/>
+      <c r="I161" s="15" t="n"/>
+      <c r="J161" s="15" t="n"/>
+      <c r="K161" s="15" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="13" t="n"/>
+      <c r="B162" s="14" t="n"/>
+      <c r="C162" s="14" t="n"/>
+      <c r="D162" s="15" t="n"/>
+      <c r="E162" s="15" t="n"/>
+      <c r="F162" s="15" t="n"/>
+      <c r="G162" s="15" t="n"/>
+      <c r="H162" s="15" t="n"/>
+      <c r="I162" s="15" t="n"/>
+      <c r="J162" s="15" t="n"/>
+      <c r="K162" s="15" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="13" t="n"/>
+      <c r="B163" s="14" t="n"/>
+      <c r="C163" s="14" t="n"/>
+      <c r="D163" s="15" t="n"/>
+      <c r="E163" s="15" t="n"/>
+      <c r="F163" s="15" t="n"/>
+      <c r="G163" s="15" t="n"/>
+      <c r="H163" s="15" t="n"/>
+      <c r="I163" s="15" t="n"/>
+      <c r="J163" s="15" t="n"/>
+      <c r="K163" s="15" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="13" t="n"/>
+      <c r="B164" s="14" t="n"/>
+      <c r="C164" s="14" t="n"/>
+      <c r="D164" s="15" t="n"/>
+      <c r="E164" s="15" t="n"/>
+      <c r="F164" s="15" t="n"/>
+      <c r="G164" s="15" t="n"/>
+      <c r="H164" s="15" t="n"/>
+      <c r="I164" s="15" t="n"/>
+      <c r="J164" s="15" t="n"/>
+      <c r="K164" s="15" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="13" t="n"/>
+      <c r="B165" s="14" t="n"/>
+      <c r="C165" s="14" t="n"/>
+      <c r="D165" s="15" t="n"/>
+      <c r="E165" s="15" t="n"/>
+      <c r="F165" s="15" t="n"/>
+      <c r="G165" s="15" t="n"/>
+      <c r="H165" s="15" t="n"/>
+      <c r="I165" s="15" t="n"/>
+      <c r="J165" s="15" t="n"/>
+      <c r="K165" s="15" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="13" t="n"/>
+      <c r="B166" s="14" t="n"/>
+      <c r="C166" s="14" t="n"/>
+      <c r="D166" s="15" t="n"/>
+      <c r="E166" s="15" t="n"/>
+      <c r="F166" s="15" t="n"/>
+      <c r="G166" s="15" t="n"/>
+      <c r="H166" s="15" t="n"/>
+      <c r="I166" s="15" t="n"/>
+      <c r="J166" s="15" t="n"/>
+      <c r="K166" s="15" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="13" t="n"/>
+      <c r="B167" s="14" t="n"/>
+      <c r="C167" s="14" t="n"/>
+      <c r="D167" s="15" t="n"/>
+      <c r="E167" s="15" t="n"/>
+      <c r="F167" s="15" t="n"/>
+      <c r="G167" s="15" t="n"/>
+      <c r="H167" s="15" t="n"/>
+      <c r="I167" s="15" t="n"/>
+      <c r="J167" s="15" t="n"/>
+      <c r="K167" s="15" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="13" t="n"/>
+      <c r="B168" s="14" t="n"/>
+      <c r="C168" s="14" t="n"/>
+      <c r="D168" s="15" t="n"/>
+      <c r="E168" s="15" t="n"/>
+      <c r="F168" s="15" t="n"/>
+      <c r="G168" s="15" t="n"/>
+      <c r="H168" s="15" t="n"/>
+      <c r="I168" s="15" t="n"/>
+      <c r="J168" s="15" t="n"/>
+      <c r="K168" s="15" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="13" t="n"/>
+      <c r="B169" s="14" t="n"/>
+      <c r="C169" s="14" t="n"/>
+      <c r="D169" s="15" t="n"/>
+      <c r="E169" s="15" t="n"/>
+      <c r="F169" s="15" t="n"/>
+      <c r="G169" s="15" t="n"/>
+      <c r="H169" s="15" t="n"/>
+      <c r="I169" s="15" t="n"/>
+      <c r="J169" s="15" t="n"/>
+      <c r="K169" s="15" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="13" t="n"/>
+      <c r="B170" s="14" t="n"/>
+      <c r="C170" s="14" t="n"/>
+      <c r="D170" s="15" t="n"/>
+      <c r="E170" s="15" t="n"/>
+      <c r="F170" s="15" t="n"/>
+      <c r="G170" s="15" t="n"/>
+      <c r="H170" s="15" t="n"/>
+      <c r="I170" s="15" t="n"/>
+      <c r="J170" s="15" t="n"/>
+      <c r="K170" s="15" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="13" t="n"/>
+      <c r="B171" s="14" t="n"/>
+      <c r="C171" s="14" t="n"/>
+      <c r="D171" s="15" t="n"/>
+      <c r="E171" s="15" t="n"/>
+      <c r="F171" s="15" t="n"/>
+      <c r="G171" s="15" t="n"/>
+      <c r="H171" s="15" t="n"/>
+      <c r="I171" s="15" t="n"/>
+      <c r="J171" s="15" t="n"/>
+      <c r="K171" s="15" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="13" t="n"/>
+      <c r="B172" s="14" t="n"/>
+      <c r="C172" s="14" t="n"/>
+      <c r="D172" s="15" t="n"/>
+      <c r="E172" s="15" t="n"/>
+      <c r="F172" s="15" t="n"/>
+      <c r="G172" s="15" t="n"/>
+      <c r="H172" s="15" t="n"/>
+      <c r="I172" s="15" t="n"/>
+      <c r="J172" s="15" t="n"/>
+      <c r="K172" s="15" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="13" t="n"/>
+      <c r="B173" s="14" t="n"/>
+      <c r="C173" s="14" t="n"/>
+      <c r="D173" s="15" t="n"/>
+      <c r="E173" s="15" t="n"/>
+      <c r="F173" s="15" t="n"/>
+      <c r="G173" s="15" t="n"/>
+      <c r="H173" s="15" t="n"/>
+      <c r="I173" s="15" t="n"/>
+      <c r="J173" s="15" t="n"/>
+      <c r="K173" s="15" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="13" t="n"/>
+      <c r="B174" s="14" t="n"/>
+      <c r="C174" s="14" t="n"/>
+      <c r="D174" s="15" t="n"/>
+      <c r="E174" s="15" t="n"/>
+      <c r="F174" s="15" t="n"/>
+      <c r="G174" s="15" t="n"/>
+      <c r="H174" s="15" t="n"/>
+      <c r="I174" s="15" t="n"/>
+      <c r="J174" s="15" t="n"/>
+      <c r="K174" s="15" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="13" t="n"/>
+      <c r="B175" s="14" t="n"/>
+      <c r="C175" s="14" t="n"/>
+      <c r="D175" s="15" t="n"/>
+      <c r="E175" s="15" t="n"/>
+      <c r="F175" s="15" t="n"/>
+      <c r="G175" s="15" t="n"/>
+      <c r="H175" s="15" t="n"/>
+      <c r="I175" s="15" t="n"/>
+      <c r="J175" s="15" t="n"/>
+      <c r="K175" s="15" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="13" t="n"/>
+      <c r="B176" s="14" t="n"/>
+      <c r="C176" s="14" t="n"/>
+      <c r="D176" s="15" t="n"/>
+      <c r="E176" s="15" t="n"/>
+      <c r="F176" s="15" t="n"/>
+      <c r="G176" s="15" t="n"/>
+      <c r="H176" s="15" t="n"/>
+      <c r="I176" s="15" t="n"/>
+      <c r="J176" s="15" t="n"/>
+      <c r="K176" s="15" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="13" t="n"/>
+      <c r="B177" s="14" t="n"/>
+      <c r="C177" s="14" t="n"/>
+      <c r="D177" s="15" t="n"/>
+      <c r="E177" s="15" t="n"/>
+      <c r="F177" s="15" t="n"/>
+      <c r="G177" s="15" t="n"/>
+      <c r="H177" s="15" t="n"/>
+      <c r="I177" s="15" t="n"/>
+      <c r="J177" s="15" t="n"/>
+      <c r="K177" s="15" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="13" t="n"/>
+      <c r="B178" s="14" t="n"/>
+      <c r="C178" s="14" t="n"/>
+      <c r="D178" s="15" t="n"/>
+      <c r="E178" s="15" t="n"/>
+      <c r="F178" s="15" t="n"/>
+      <c r="G178" s="15" t="n"/>
+      <c r="H178" s="15" t="n"/>
+      <c r="I178" s="15" t="n"/>
+      <c r="J178" s="15" t="n"/>
+      <c r="K178" s="15" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="13" t="n"/>
+      <c r="B179" s="14" t="n"/>
+      <c r="C179" s="14" t="n"/>
+      <c r="D179" s="15" t="n"/>
+      <c r="E179" s="15" t="n"/>
+      <c r="F179" s="15" t="n"/>
+      <c r="G179" s="15" t="n"/>
+      <c r="H179" s="15" t="n"/>
+      <c r="I179" s="15" t="n"/>
+      <c r="J179" s="15" t="n"/>
+      <c r="K179" s="15" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="13" t="n"/>
+      <c r="B180" s="14" t="n"/>
+      <c r="C180" s="14" t="n"/>
+      <c r="D180" s="15" t="n"/>
+      <c r="E180" s="15" t="n"/>
+      <c r="F180" s="15" t="n"/>
+      <c r="G180" s="15" t="n"/>
+      <c r="H180" s="15" t="n"/>
+      <c r="I180" s="15" t="n"/>
+      <c r="J180" s="15" t="n"/>
+      <c r="K180" s="15" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="13" t="n"/>
+      <c r="B181" s="14" t="n"/>
+      <c r="C181" s="14" t="n"/>
+      <c r="D181" s="15" t="n"/>
+      <c r="E181" s="15" t="n"/>
+      <c r="F181" s="15" t="n"/>
+      <c r="G181" s="15" t="n"/>
+      <c r="H181" s="15" t="n"/>
+      <c r="I181" s="15" t="n"/>
+      <c r="J181" s="15" t="n"/>
+      <c r="K181" s="15" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="13" t="n"/>
+      <c r="B182" s="14" t="n"/>
+      <c r="C182" s="14" t="n"/>
+      <c r="D182" s="15" t="n"/>
+      <c r="E182" s="15" t="n"/>
+      <c r="F182" s="15" t="n"/>
+      <c r="G182" s="15" t="n"/>
+      <c r="H182" s="15" t="n"/>
+      <c r="I182" s="15" t="n"/>
+      <c r="J182" s="15" t="n"/>
+      <c r="K182" s="15" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="13" t="n"/>
+      <c r="B183" s="14" t="n"/>
+      <c r="C183" s="14" t="n"/>
+      <c r="D183" s="15" t="n"/>
+      <c r="E183" s="15" t="n"/>
+      <c r="F183" s="15" t="n"/>
+      <c r="G183" s="15" t="n"/>
+      <c r="H183" s="15" t="n"/>
+      <c r="I183" s="15" t="n"/>
+      <c r="J183" s="15" t="n"/>
+      <c r="K183" s="15" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="13" t="n"/>
+      <c r="B184" s="14" t="n"/>
+      <c r="C184" s="14" t="n"/>
+      <c r="D184" s="15" t="n"/>
+      <c r="E184" s="15" t="n"/>
+      <c r="F184" s="15" t="n"/>
+      <c r="G184" s="15" t="n"/>
+      <c r="H184" s="15" t="n"/>
+      <c r="I184" s="15" t="n"/>
+      <c r="J184" s="15" t="n"/>
+      <c r="K184" s="15" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="13" t="n"/>
+      <c r="B185" s="14" t="n"/>
+      <c r="C185" s="14" t="n"/>
+      <c r="D185" s="15" t="n"/>
+      <c r="E185" s="15" t="n"/>
+      <c r="F185" s="15" t="n"/>
+      <c r="G185" s="15" t="n"/>
+      <c r="H185" s="15" t="n"/>
+      <c r="I185" s="15" t="n"/>
+      <c r="J185" s="15" t="n"/>
+      <c r="K185" s="15" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="13" t="n"/>
+      <c r="B186" s="14" t="n"/>
+      <c r="C186" s="14" t="n"/>
+      <c r="D186" s="15" t="n"/>
+      <c r="E186" s="15" t="n"/>
+      <c r="F186" s="15" t="n"/>
+      <c r="G186" s="15" t="n"/>
+      <c r="H186" s="15" t="n"/>
+      <c r="I186" s="15" t="n"/>
+      <c r="J186" s="15" t="n"/>
+      <c r="K186" s="15" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="13" t="n"/>
+      <c r="B187" s="14" t="n"/>
+      <c r="C187" s="14" t="n"/>
+      <c r="D187" s="15" t="n"/>
+      <c r="E187" s="15" t="n"/>
+      <c r="F187" s="15" t="n"/>
+      <c r="G187" s="15" t="n"/>
+      <c r="H187" s="15" t="n"/>
+      <c r="I187" s="15" t="n"/>
+      <c r="J187" s="15" t="n"/>
+      <c r="K187" s="15" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="13" t="n"/>
+      <c r="B188" s="14" t="n"/>
+      <c r="C188" s="14" t="n"/>
+      <c r="D188" s="15" t="n"/>
+      <c r="E188" s="15" t="n"/>
+      <c r="F188" s="15" t="n"/>
+      <c r="G188" s="15" t="n"/>
+      <c r="H188" s="15" t="n"/>
+      <c r="I188" s="15" t="n"/>
+      <c r="J188" s="15" t="n"/>
+      <c r="K188" s="15" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="13" t="n"/>
+      <c r="B189" s="14" t="n"/>
+      <c r="C189" s="14" t="n"/>
+      <c r="D189" s="15" t="n"/>
+      <c r="E189" s="15" t="n"/>
+      <c r="F189" s="15" t="n"/>
+      <c r="G189" s="15" t="n"/>
+      <c r="H189" s="15" t="n"/>
+      <c r="I189" s="15" t="n"/>
+      <c r="J189" s="15" t="n"/>
+      <c r="K189" s="15" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="13" t="n"/>
+      <c r="B190" s="14" t="n"/>
+      <c r="C190" s="14" t="n"/>
+      <c r="D190" s="15" t="n"/>
+      <c r="E190" s="15" t="n"/>
+      <c r="F190" s="15" t="n"/>
+      <c r="G190" s="15" t="n"/>
+      <c r="H190" s="15" t="n"/>
+      <c r="I190" s="15" t="n"/>
+      <c r="J190" s="15" t="n"/>
+      <c r="K190" s="15" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="13" t="n"/>
+      <c r="B191" s="14" t="n"/>
+      <c r="C191" s="14" t="n"/>
+      <c r="D191" s="15" t="n"/>
+      <c r="E191" s="15" t="n"/>
+      <c r="F191" s="15" t="n"/>
+      <c r="G191" s="15" t="n"/>
+      <c r="H191" s="15" t="n"/>
+      <c r="I191" s="15" t="n"/>
+      <c r="J191" s="15" t="n"/>
+      <c r="K191" s="15" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="13" t="n"/>
+      <c r="B192" s="14" t="n"/>
+      <c r="C192" s="14" t="n"/>
+      <c r="D192" s="15" t="n"/>
+      <c r="E192" s="15" t="n"/>
+      <c r="F192" s="15" t="n"/>
+      <c r="G192" s="15" t="n"/>
+      <c r="H192" s="15" t="n"/>
+      <c r="I192" s="15" t="n"/>
+      <c r="J192" s="15" t="n"/>
+      <c r="K192" s="15" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="13" t="n"/>
+      <c r="B193" s="14" t="n"/>
+      <c r="C193" s="14" t="n"/>
+      <c r="D193" s="15" t="n"/>
+      <c r="E193" s="15" t="n"/>
+      <c r="F193" s="15" t="n"/>
+      <c r="G193" s="15" t="n"/>
+      <c r="H193" s="15" t="n"/>
+      <c r="I193" s="15" t="n"/>
+      <c r="J193" s="15" t="n"/>
+      <c r="K193" s="15" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="13" t="n"/>
+      <c r="B194" s="14" t="n"/>
+      <c r="C194" s="14" t="n"/>
+      <c r="D194" s="15" t="n"/>
+      <c r="E194" s="15" t="n"/>
+      <c r="F194" s="15" t="n"/>
+      <c r="G194" s="15" t="n"/>
+      <c r="H194" s="15" t="n"/>
+      <c r="I194" s="15" t="n"/>
+      <c r="J194" s="15" t="n"/>
+      <c r="K194" s="15" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="13" t="n"/>
+      <c r="B195" s="14" t="n"/>
+      <c r="C195" s="14" t="n"/>
+      <c r="D195" s="15" t="n"/>
+      <c r="E195" s="15" t="n"/>
+      <c r="F195" s="15" t="n"/>
+      <c r="G195" s="15" t="n"/>
+      <c r="H195" s="15" t="n"/>
+      <c r="I195" s="15" t="n"/>
+      <c r="J195" s="15" t="n"/>
+      <c r="K195" s="15" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="13" t="n"/>
+      <c r="B196" s="14" t="n"/>
+      <c r="C196" s="14" t="n"/>
+      <c r="D196" s="15" t="n"/>
+      <c r="E196" s="15" t="n"/>
+      <c r="F196" s="15" t="n"/>
+      <c r="G196" s="15" t="n"/>
+      <c r="H196" s="15" t="n"/>
+      <c r="I196" s="15" t="n"/>
+      <c r="J196" s="15" t="n"/>
+      <c r="K196" s="15" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="13" t="n"/>
+      <c r="B197" s="14" t="n"/>
+      <c r="C197" s="14" t="n"/>
+      <c r="D197" s="15" t="n"/>
+      <c r="E197" s="15" t="n"/>
+      <c r="F197" s="15" t="n"/>
+      <c r="G197" s="15" t="n"/>
+      <c r="H197" s="15" t="n"/>
+      <c r="I197" s="15" t="n"/>
+      <c r="J197" s="15" t="n"/>
+      <c r="K197" s="15" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="13" t="n"/>
+      <c r="B198" s="14" t="n"/>
+      <c r="C198" s="14" t="n"/>
+      <c r="D198" s="15" t="n"/>
+      <c r="E198" s="15" t="n"/>
+      <c r="F198" s="15" t="n"/>
+      <c r="G198" s="15" t="n"/>
+      <c r="H198" s="15" t="n"/>
+      <c r="I198" s="15" t="n"/>
+      <c r="J198" s="15" t="n"/>
+      <c r="K198" s="15" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="13" t="n"/>
+      <c r="B199" s="14" t="n"/>
+      <c r="C199" s="14" t="n"/>
+      <c r="D199" s="15" t="n"/>
+      <c r="E199" s="15" t="n"/>
+      <c r="F199" s="15" t="n"/>
+      <c r="G199" s="15" t="n"/>
+      <c r="H199" s="15" t="n"/>
+      <c r="I199" s="15" t="n"/>
+      <c r="J199" s="15" t="n"/>
+      <c r="K199" s="15" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="13" t="n"/>
+      <c r="B200" s="14" t="n"/>
+      <c r="C200" s="14" t="n"/>
+      <c r="D200" s="15" t="n"/>
+      <c r="E200" s="15" t="n"/>
+      <c r="F200" s="15" t="n"/>
+      <c r="G200" s="15" t="n"/>
+      <c r="H200" s="15" t="n"/>
+      <c r="I200" s="15" t="n"/>
+      <c r="J200" s="15" t="n"/>
+      <c r="K200" s="15" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="13" t="n"/>
+      <c r="B201" s="14" t="n"/>
+      <c r="C201" s="14" t="n"/>
+      <c r="D201" s="15" t="n"/>
+      <c r="E201" s="15" t="n"/>
+      <c r="F201" s="15" t="n"/>
+      <c r="G201" s="15" t="n"/>
+      <c r="H201" s="15" t="n"/>
+      <c r="I201" s="15" t="n"/>
+      <c r="J201" s="15" t="n"/>
+      <c r="K201" s="15" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="13" t="n"/>
+      <c r="B202" s="14" t="n"/>
+      <c r="C202" s="14" t="n"/>
+      <c r="D202" s="15" t="n"/>
+      <c r="E202" s="15" t="n"/>
+      <c r="F202" s="15" t="n"/>
+      <c r="G202" s="15" t="n"/>
+      <c r="H202" s="15" t="n"/>
+      <c r="I202" s="15" t="n"/>
+      <c r="J202" s="15" t="n"/>
+      <c r="K202" s="15" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="13" t="n"/>
+      <c r="B203" s="14" t="n"/>
+      <c r="C203" s="14" t="n"/>
+      <c r="D203" s="15" t="n"/>
+      <c r="E203" s="15" t="n"/>
+      <c r="F203" s="15" t="n"/>
+      <c r="G203" s="15" t="n"/>
+      <c r="H203" s="15" t="n"/>
+      <c r="I203" s="15" t="n"/>
+      <c r="J203" s="15" t="n"/>
+      <c r="K203" s="15" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="13" t="n"/>
+      <c r="B204" s="14" t="n"/>
+      <c r="C204" s="14" t="n"/>
+      <c r="D204" s="15" t="n"/>
+      <c r="E204" s="15" t="n"/>
+      <c r="F204" s="15" t="n"/>
+      <c r="G204" s="15" t="n"/>
+      <c r="H204" s="15" t="n"/>
+      <c r="I204" s="15" t="n"/>
+      <c r="J204" s="15" t="n"/>
+      <c r="K204" s="15" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="13" t="n"/>
+      <c r="B205" s="14" t="n"/>
+      <c r="C205" s="14" t="n"/>
+      <c r="D205" s="15" t="n"/>
+      <c r="E205" s="15" t="n"/>
+      <c r="F205" s="15" t="n"/>
+      <c r="G205" s="15" t="n"/>
+      <c r="H205" s="15" t="n"/>
+      <c r="I205" s="15" t="n"/>
+      <c r="J205" s="15" t="n"/>
+      <c r="K205" s="15" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="13" t="n"/>
+      <c r="B206" s="14" t="n"/>
+      <c r="C206" s="14" t="n"/>
+      <c r="D206" s="15" t="n"/>
+      <c r="E206" s="15" t="n"/>
+      <c r="F206" s="15" t="n"/>
+      <c r="G206" s="15" t="n"/>
+      <c r="H206" s="15" t="n"/>
+      <c r="I206" s="15" t="n"/>
+      <c r="J206" s="15" t="n"/>
+      <c r="K206" s="15" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="13" t="n"/>
+      <c r="B207" s="14" t="n"/>
+      <c r="C207" s="14" t="n"/>
+      <c r="D207" s="15" t="n"/>
+      <c r="E207" s="15" t="n"/>
+      <c r="F207" s="15" t="n"/>
+      <c r="G207" s="15" t="n"/>
+      <c r="H207" s="15" t="n"/>
+      <c r="I207" s="15" t="n"/>
+      <c r="J207" s="15" t="n"/>
+      <c r="K207" s="15" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="13" t="n"/>
+      <c r="B208" s="14" t="n"/>
+      <c r="C208" s="14" t="n"/>
+      <c r="D208" s="15" t="n"/>
+      <c r="E208" s="15" t="n"/>
+      <c r="F208" s="15" t="n"/>
+      <c r="G208" s="15" t="n"/>
+      <c r="H208" s="15" t="n"/>
+      <c r="I208" s="15" t="n"/>
+      <c r="J208" s="15" t="n"/>
+      <c r="K208" s="15" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="13" t="n"/>
+      <c r="B209" s="14" t="n"/>
+      <c r="C209" s="14" t="n"/>
+      <c r="D209" s="15" t="n"/>
+      <c r="E209" s="15" t="n"/>
+      <c r="F209" s="15" t="n"/>
+      <c r="G209" s="15" t="n"/>
+      <c r="H209" s="15" t="n"/>
+      <c r="I209" s="15" t="n"/>
+      <c r="J209" s="15" t="n"/>
+      <c r="K209" s="15" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="13" t="n"/>
+      <c r="B210" s="14" t="n"/>
+      <c r="C210" s="14" t="n"/>
+      <c r="D210" s="15" t="n"/>
+      <c r="E210" s="15" t="n"/>
+      <c r="F210" s="15" t="n"/>
+      <c r="G210" s="15" t="n"/>
+      <c r="H210" s="15" t="n"/>
+      <c r="I210" s="15" t="n"/>
+      <c r="J210" s="15" t="n"/>
+      <c r="K210" s="15" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="13" t="n"/>
+      <c r="B211" s="14" t="n"/>
+      <c r="C211" s="14" t="n"/>
+      <c r="D211" s="15" t="n"/>
+      <c r="E211" s="15" t="n"/>
+      <c r="F211" s="15" t="n"/>
+      <c r="G211" s="15" t="n"/>
+      <c r="H211" s="15" t="n"/>
+      <c r="I211" s="15" t="n"/>
+      <c r="J211" s="15" t="n"/>
+      <c r="K211" s="15" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="13" t="n"/>
+      <c r="B212" s="14" t="n"/>
+      <c r="C212" s="14" t="n"/>
+      <c r="D212" s="15" t="n"/>
+      <c r="E212" s="15" t="n"/>
+      <c r="F212" s="15" t="n"/>
+      <c r="G212" s="15" t="n"/>
+      <c r="H212" s="15" t="n"/>
+      <c r="I212" s="15" t="n"/>
+      <c r="J212" s="15" t="n"/>
+      <c r="K212" s="15" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="13" t="n"/>
+      <c r="B213" s="14" t="n"/>
+      <c r="C213" s="14" t="n"/>
+      <c r="D213" s="15" t="n"/>
+      <c r="E213" s="15" t="n"/>
+      <c r="F213" s="15" t="n"/>
+      <c r="G213" s="15" t="n"/>
+      <c r="H213" s="15" t="n"/>
+      <c r="I213" s="15" t="n"/>
+      <c r="J213" s="15" t="n"/>
+      <c r="K213" s="15" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="13" t="n"/>
+      <c r="B214" s="14" t="n"/>
+      <c r="C214" s="14" t="n"/>
+      <c r="D214" s="15" t="n"/>
+      <c r="E214" s="15" t="n"/>
+      <c r="F214" s="15" t="n"/>
+      <c r="G214" s="15" t="n"/>
+      <c r="H214" s="15" t="n"/>
+      <c r="I214" s="15" t="n"/>
+      <c r="J214" s="15" t="n"/>
+      <c r="K214" s="15" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="13" t="n"/>
+      <c r="B215" s="14" t="n"/>
+      <c r="C215" s="14" t="n"/>
+      <c r="D215" s="15" t="n"/>
+      <c r="E215" s="15" t="n"/>
+      <c r="F215" s="15" t="n"/>
+      <c r="G215" s="15" t="n"/>
+      <c r="H215" s="15" t="n"/>
+      <c r="I215" s="15" t="n"/>
+      <c r="J215" s="15" t="n"/>
+      <c r="K215" s="15" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="13" t="n"/>
+      <c r="B216" s="14" t="n"/>
+      <c r="C216" s="14" t="n"/>
+      <c r="D216" s="15" t="n"/>
+      <c r="E216" s="15" t="n"/>
+      <c r="F216" s="15" t="n"/>
+      <c r="G216" s="15" t="n"/>
+      <c r="H216" s="15" t="n"/>
+      <c r="I216" s="15" t="n"/>
+      <c r="J216" s="15" t="n"/>
+      <c r="K216" s="15" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="13" t="n"/>
+      <c r="B217" s="14" t="n"/>
+      <c r="C217" s="14" t="n"/>
+      <c r="D217" s="15" t="n"/>
+      <c r="E217" s="15" t="n"/>
+      <c r="F217" s="15" t="n"/>
+      <c r="G217" s="15" t="n"/>
+      <c r="H217" s="15" t="n"/>
+      <c r="I217" s="15" t="n"/>
+      <c r="J217" s="15" t="n"/>
+      <c r="K217" s="15" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="13" t="n"/>
+      <c r="B218" s="14" t="n"/>
+      <c r="C218" s="14" t="n"/>
+      <c r="D218" s="15" t="n"/>
+      <c r="E218" s="15" t="n"/>
+      <c r="F218" s="15" t="n"/>
+      <c r="G218" s="15" t="n"/>
+      <c r="H218" s="15" t="n"/>
+      <c r="I218" s="15" t="n"/>
+      <c r="J218" s="15" t="n"/>
+      <c r="K218" s="15" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="13" t="n"/>
+      <c r="B219" s="14" t="n"/>
+      <c r="C219" s="14" t="n"/>
+      <c r="D219" s="15" t="n"/>
+      <c r="E219" s="15" t="n"/>
+      <c r="F219" s="15" t="n"/>
+      <c r="G219" s="15" t="n"/>
+      <c r="H219" s="15" t="n"/>
+      <c r="I219" s="15" t="n"/>
+      <c r="J219" s="15" t="n"/>
+      <c r="K219" s="15" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="13" t="n"/>
+      <c r="B220" s="14" t="n"/>
+      <c r="C220" s="14" t="n"/>
+      <c r="D220" s="15" t="n"/>
+      <c r="E220" s="15" t="n"/>
+      <c r="F220" s="15" t="n"/>
+      <c r="G220" s="15" t="n"/>
+      <c r="H220" s="15" t="n"/>
+      <c r="I220" s="15" t="n"/>
+      <c r="J220" s="15" t="n"/>
+      <c r="K220" s="15" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="13" t="n"/>
+      <c r="B221" s="14" t="n"/>
+      <c r="C221" s="14" t="n"/>
+      <c r="D221" s="15" t="n"/>
+      <c r="E221" s="15" t="n"/>
+      <c r="F221" s="15" t="n"/>
+      <c r="G221" s="15" t="n"/>
+      <c r="H221" s="15" t="n"/>
+      <c r="I221" s="15" t="n"/>
+      <c r="J221" s="15" t="n"/>
+      <c r="K221" s="15" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="13" t="n"/>
+      <c r="B222" s="14" t="n"/>
+      <c r="C222" s="14" t="n"/>
+      <c r="D222" s="15" t="n"/>
+      <c r="E222" s="15" t="n"/>
+      <c r="F222" s="15" t="n"/>
+      <c r="G222" s="15" t="n"/>
+      <c r="H222" s="15" t="n"/>
+      <c r="I222" s="15" t="n"/>
+      <c r="J222" s="15" t="n"/>
+      <c r="K222" s="15" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="13" t="n"/>
+      <c r="B223" s="14" t="n"/>
+      <c r="C223" s="14" t="n"/>
+      <c r="D223" s="15" t="n"/>
+      <c r="E223" s="15" t="n"/>
+      <c r="F223" s="15" t="n"/>
+      <c r="G223" s="15" t="n"/>
+      <c r="H223" s="15" t="n"/>
+      <c r="I223" s="15" t="n"/>
+      <c r="J223" s="15" t="n"/>
+      <c r="K223" s="15" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="13" t="n"/>
+      <c r="B224" s="14" t="n"/>
+      <c r="C224" s="14" t="n"/>
+      <c r="D224" s="15" t="n"/>
+      <c r="E224" s="15" t="n"/>
+      <c r="F224" s="15" t="n"/>
+      <c r="G224" s="15" t="n"/>
+      <c r="H224" s="15" t="n"/>
+      <c r="I224" s="15" t="n"/>
+      <c r="J224" s="15" t="n"/>
+      <c r="K224" s="15" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="13" t="n"/>
+      <c r="B225" s="14" t="n"/>
+      <c r="C225" s="14" t="n"/>
+      <c r="D225" s="15" t="n"/>
+      <c r="E225" s="15" t="n"/>
+      <c r="F225" s="15" t="n"/>
+      <c r="G225" s="15" t="n"/>
+      <c r="H225" s="15" t="n"/>
+      <c r="I225" s="15" t="n"/>
+      <c r="J225" s="15" t="n"/>
+      <c r="K225" s="15" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="13" t="n"/>
+      <c r="B226" s="14" t="n"/>
+      <c r="C226" s="14" t="n"/>
+      <c r="D226" s="15" t="n"/>
+      <c r="E226" s="15" t="n"/>
+      <c r="F226" s="15" t="n"/>
+      <c r="G226" s="15" t="n"/>
+      <c r="H226" s="15" t="n"/>
+      <c r="I226" s="15" t="n"/>
+      <c r="J226" s="15" t="n"/>
+      <c r="K226" s="15" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="13" t="n"/>
+      <c r="B227" s="14" t="n"/>
+      <c r="C227" s="14" t="n"/>
+      <c r="D227" s="15" t="n"/>
+      <c r="E227" s="15" t="n"/>
+      <c r="F227" s="15" t="n"/>
+      <c r="G227" s="15" t="n"/>
+      <c r="H227" s="15" t="n"/>
+      <c r="I227" s="15" t="n"/>
+      <c r="J227" s="15" t="n"/>
+      <c r="K227" s="15" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="13" t="n"/>
+      <c r="B228" s="14" t="n"/>
+      <c r="C228" s="14" t="n"/>
+      <c r="D228" s="15" t="n"/>
+      <c r="E228" s="15" t="n"/>
+      <c r="F228" s="15" t="n"/>
+      <c r="G228" s="15" t="n"/>
+      <c r="H228" s="15" t="n"/>
+      <c r="I228" s="15" t="n"/>
+      <c r="J228" s="15" t="n"/>
+      <c r="K228" s="15" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="13" t="n"/>
+      <c r="B229" s="14" t="n"/>
+      <c r="C229" s="14" t="n"/>
+      <c r="D229" s="15" t="n"/>
+      <c r="E229" s="15" t="n"/>
+      <c r="F229" s="15" t="n"/>
+      <c r="G229" s="15" t="n"/>
+      <c r="H229" s="15" t="n"/>
+      <c r="I229" s="15" t="n"/>
+      <c r="J229" s="15" t="n"/>
+      <c r="K229" s="15" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="13" t="n"/>
+      <c r="B230" s="14" t="n"/>
+      <c r="C230" s="14" t="n"/>
+      <c r="D230" s="15" t="n"/>
+      <c r="E230" s="15" t="n"/>
+      <c r="F230" s="15" t="n"/>
+      <c r="G230" s="15" t="n"/>
+      <c r="H230" s="15" t="n"/>
+      <c r="I230" s="15" t="n"/>
+      <c r="J230" s="15" t="n"/>
+      <c r="K230" s="15" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="13" t="n"/>
+      <c r="B231" s="14" t="n"/>
+      <c r="C231" s="14" t="n"/>
+      <c r="D231" s="15" t="n"/>
+      <c r="E231" s="15" t="n"/>
+      <c r="F231" s="15" t="n"/>
+      <c r="G231" s="15" t="n"/>
+      <c r="H231" s="15" t="n"/>
+      <c r="I231" s="15" t="n"/>
+      <c r="J231" s="15" t="n"/>
+      <c r="K231" s="15" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="13" t="n"/>
+      <c r="B232" s="14" t="n"/>
+      <c r="C232" s="14" t="n"/>
+      <c r="D232" s="15" t="n"/>
+      <c r="E232" s="15" t="n"/>
+      <c r="F232" s="15" t="n"/>
+      <c r="G232" s="15" t="n"/>
+      <c r="H232" s="15" t="n"/>
+      <c r="I232" s="15" t="n"/>
+      <c r="J232" s="15" t="n"/>
+      <c r="K232" s="15" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="13" t="n"/>
+      <c r="B233" s="14" t="n"/>
+      <c r="C233" s="14" t="n"/>
+      <c r="D233" s="15" t="n"/>
+      <c r="E233" s="15" t="n"/>
+      <c r="F233" s="15" t="n"/>
+      <c r="G233" s="15" t="n"/>
+      <c r="H233" s="15" t="n"/>
+      <c r="I233" s="15" t="n"/>
+      <c r="J233" s="15" t="n"/>
+      <c r="K233" s="15" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="13" t="n"/>
+      <c r="B234" s="14" t="n"/>
+      <c r="C234" s="14" t="n"/>
+      <c r="D234" s="15" t="n"/>
+      <c r="E234" s="15" t="n"/>
+      <c r="F234" s="15" t="n"/>
+      <c r="G234" s="15" t="n"/>
+      <c r="H234" s="15" t="n"/>
+      <c r="I234" s="15" t="n"/>
+      <c r="J234" s="15" t="n"/>
+      <c r="K234" s="15" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="13" t="n"/>
+      <c r="B235" s="14" t="n"/>
+      <c r="C235" s="14" t="n"/>
+      <c r="D235" s="15" t="n"/>
+      <c r="E235" s="15" t="n"/>
+      <c r="F235" s="15" t="n"/>
+      <c r="G235" s="15" t="n"/>
+      <c r="H235" s="15" t="n"/>
+      <c r="I235" s="15" t="n"/>
+      <c r="J235" s="15" t="n"/>
+      <c r="K235" s="15" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="13" t="n"/>
+      <c r="B236" s="14" t="n"/>
+      <c r="C236" s="14" t="n"/>
+      <c r="D236" s="15" t="n"/>
+      <c r="E236" s="15" t="n"/>
+      <c r="F236" s="15" t="n"/>
+      <c r="G236" s="15" t="n"/>
+      <c r="H236" s="15" t="n"/>
+      <c r="I236" s="15" t="n"/>
+      <c r="J236" s="15" t="n"/>
+      <c r="K236" s="15" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="13" t="n"/>
+      <c r="B237" s="14" t="n"/>
+      <c r="C237" s="14" t="n"/>
+      <c r="D237" s="15" t="n"/>
+      <c r="E237" s="15" t="n"/>
+      <c r="F237" s="15" t="n"/>
+      <c r="G237" s="15" t="n"/>
+      <c r="H237" s="15" t="n"/>
+      <c r="I237" s="15" t="n"/>
+      <c r="J237" s="15" t="n"/>
+      <c r="K237" s="15" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="13" t="n"/>
+      <c r="B238" s="14" t="n"/>
+      <c r="C238" s="14" t="n"/>
+      <c r="D238" s="15" t="n"/>
+      <c r="E238" s="15" t="n"/>
+      <c r="F238" s="15" t="n"/>
+      <c r="G238" s="15" t="n"/>
+      <c r="H238" s="15" t="n"/>
+      <c r="I238" s="15" t="n"/>
+      <c r="J238" s="15" t="n"/>
+      <c r="K238" s="15" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="13" t="n"/>
+      <c r="B239" s="14" t="n"/>
+      <c r="C239" s="14" t="n"/>
+      <c r="D239" s="15" t="n"/>
+      <c r="E239" s="15" t="n"/>
+      <c r="F239" s="15" t="n"/>
+      <c r="G239" s="15" t="n"/>
+      <c r="H239" s="15" t="n"/>
+      <c r="I239" s="15" t="n"/>
+      <c r="J239" s="15" t="n"/>
+      <c r="K239" s="15" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="13" t="n"/>
+      <c r="B240" s="14" t="n"/>
+      <c r="C240" s="14" t="n"/>
+      <c r="D240" s="15" t="n"/>
+      <c r="E240" s="15" t="n"/>
+      <c r="F240" s="15" t="n"/>
+      <c r="G240" s="15" t="n"/>
+      <c r="H240" s="15" t="n"/>
+      <c r="I240" s="15" t="n"/>
+      <c r="J240" s="15" t="n"/>
+      <c r="K240" s="15" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="13" t="n"/>
+      <c r="B241" s="14" t="n"/>
+      <c r="C241" s="14" t="n"/>
+      <c r="D241" s="15" t="n"/>
+      <c r="E241" s="15" t="n"/>
+      <c r="F241" s="15" t="n"/>
+      <c r="G241" s="15" t="n"/>
+      <c r="H241" s="15" t="n"/>
+      <c r="I241" s="15" t="n"/>
+      <c r="J241" s="15" t="n"/>
+      <c r="K241" s="15" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="13" t="n"/>
+      <c r="B242" s="14" t="n"/>
+      <c r="C242" s="14" t="n"/>
+      <c r="D242" s="15" t="n"/>
+      <c r="E242" s="15" t="n"/>
+      <c r="F242" s="15" t="n"/>
+      <c r="G242" s="15" t="n"/>
+      <c r="H242" s="15" t="n"/>
+      <c r="I242" s="15" t="n"/>
+      <c r="J242" s="15" t="n"/>
+      <c r="K242" s="15" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="13" t="n"/>
+      <c r="B243" s="14" t="n"/>
+      <c r="C243" s="14" t="n"/>
+      <c r="D243" s="15" t="n"/>
+      <c r="E243" s="15" t="n"/>
+      <c r="F243" s="15" t="n"/>
+      <c r="G243" s="15" t="n"/>
+      <c r="H243" s="15" t="n"/>
+      <c r="I243" s="15" t="n"/>
+      <c r="J243" s="15" t="n"/>
+      <c r="K243" s="15" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="13" t="n"/>
+      <c r="B244" s="14" t="n"/>
+      <c r="C244" s="14" t="n"/>
+      <c r="D244" s="15" t="n"/>
+      <c r="E244" s="15" t="n"/>
+      <c r="F244" s="15" t="n"/>
+      <c r="G244" s="15" t="n"/>
+      <c r="H244" s="15" t="n"/>
+      <c r="I244" s="15" t="n"/>
+      <c r="J244" s="15" t="n"/>
+      <c r="K244" s="15" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="13" t="n"/>
+      <c r="B245" s="14" t="n"/>
+      <c r="C245" s="14" t="n"/>
+      <c r="D245" s="15" t="n"/>
+      <c r="E245" s="15" t="n"/>
+      <c r="F245" s="15" t="n"/>
+      <c r="G245" s="15" t="n"/>
+      <c r="H245" s="15" t="n"/>
+      <c r="I245" s="15" t="n"/>
+      <c r="J245" s="15" t="n"/>
+      <c r="K245" s="15" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="13" t="n"/>
+      <c r="B246" s="14" t="n"/>
+      <c r="C246" s="14" t="n"/>
+      <c r="D246" s="15" t="n"/>
+      <c r="E246" s="15" t="n"/>
+      <c r="F246" s="15" t="n"/>
+      <c r="G246" s="15" t="n"/>
+      <c r="H246" s="15" t="n"/>
+      <c r="I246" s="15" t="n"/>
+      <c r="J246" s="15" t="n"/>
+      <c r="K246" s="15" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="13" t="n"/>
+      <c r="B247" s="14" t="n"/>
+      <c r="C247" s="14" t="n"/>
+      <c r="D247" s="15" t="n"/>
+      <c r="E247" s="15" t="n"/>
+      <c r="F247" s="15" t="n"/>
+      <c r="G247" s="15" t="n"/>
+      <c r="H247" s="15" t="n"/>
+      <c r="I247" s="15" t="n"/>
+      <c r="J247" s="15" t="n"/>
+      <c r="K247" s="15" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="13" t="n"/>
+      <c r="B248" s="14" t="n"/>
+      <c r="C248" s="14" t="n"/>
+      <c r="D248" s="15" t="n"/>
+      <c r="E248" s="15" t="n"/>
+      <c r="F248" s="15" t="n"/>
+      <c r="G248" s="15" t="n"/>
+      <c r="H248" s="15" t="n"/>
+      <c r="I248" s="15" t="n"/>
+      <c r="J248" s="15" t="n"/>
+      <c r="K248" s="15" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="13" t="n"/>
+      <c r="B249" s="14" t="n"/>
+      <c r="C249" s="14" t="n"/>
+      <c r="D249" s="15" t="n"/>
+      <c r="E249" s="15" t="n"/>
+      <c r="F249" s="15" t="n"/>
+      <c r="G249" s="15" t="n"/>
+      <c r="H249" s="15" t="n"/>
+      <c r="I249" s="15" t="n"/>
+      <c r="J249" s="15" t="n"/>
+      <c r="K249" s="15" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="13" t="n"/>
+      <c r="B250" s="14" t="n"/>
+      <c r="C250" s="14" t="n"/>
+      <c r="D250" s="15" t="n"/>
+      <c r="E250" s="15" t="n"/>
+      <c r="F250" s="15" t="n"/>
+      <c r="G250" s="15" t="n"/>
+      <c r="H250" s="15" t="n"/>
+      <c r="I250" s="15" t="n"/>
+      <c r="J250" s="15" t="n"/>
+      <c r="K250" s="15" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="13" t="n"/>
+      <c r="B251" s="14" t="n"/>
+      <c r="C251" s="14" t="n"/>
+      <c r="D251" s="15" t="n"/>
+      <c r="E251" s="15" t="n"/>
+      <c r="F251" s="15" t="n"/>
+      <c r="G251" s="15" t="n"/>
+      <c r="H251" s="15" t="n"/>
+      <c r="I251" s="15" t="n"/>
+      <c r="J251" s="15" t="n"/>
+      <c r="K251" s="15" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="13" t="n"/>
+      <c r="B252" s="14" t="n"/>
+      <c r="C252" s="14" t="n"/>
+      <c r="D252" s="15" t="n"/>
+      <c r="E252" s="15" t="n"/>
+      <c r="F252" s="15" t="n"/>
+      <c r="G252" s="15" t="n"/>
+      <c r="H252" s="15" t="n"/>
+      <c r="I252" s="15" t="n"/>
+      <c r="J252" s="15" t="n"/>
+      <c r="K252" s="15" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="13" t="n"/>
+      <c r="B253" s="14" t="n"/>
+      <c r="C253" s="14" t="n"/>
+      <c r="D253" s="15" t="n"/>
+      <c r="E253" s="15" t="n"/>
+      <c r="F253" s="15" t="n"/>
+      <c r="G253" s="15" t="n"/>
+      <c r="H253" s="15" t="n"/>
+      <c r="I253" s="15" t="n"/>
+      <c r="J253" s="15" t="n"/>
+      <c r="K253" s="15" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="13" t="n"/>
+      <c r="B254" s="14" t="n"/>
+      <c r="C254" s="14" t="n"/>
+      <c r="D254" s="15" t="n"/>
+      <c r="E254" s="15" t="n"/>
+      <c r="F254" s="15" t="n"/>
+      <c r="G254" s="15" t="n"/>
+      <c r="H254" s="15" t="n"/>
+      <c r="I254" s="15" t="n"/>
+      <c r="J254" s="15" t="n"/>
+      <c r="K254" s="15" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="13" t="n"/>
+      <c r="B255" s="14" t="n"/>
+      <c r="C255" s="14" t="n"/>
+      <c r="D255" s="15" t="n"/>
+      <c r="E255" s="15" t="n"/>
+      <c r="F255" s="15" t="n"/>
+      <c r="G255" s="15" t="n"/>
+      <c r="H255" s="15" t="n"/>
+      <c r="I255" s="15" t="n"/>
+      <c r="J255" s="15" t="n"/>
+      <c r="K255" s="15" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="13" t="n"/>
+      <c r="B256" s="14" t="n"/>
+      <c r="C256" s="14" t="n"/>
+      <c r="D256" s="15" t="n"/>
+      <c r="E256" s="15" t="n"/>
+      <c r="F256" s="15" t="n"/>
+      <c r="G256" s="15" t="n"/>
+      <c r="H256" s="15" t="n"/>
+      <c r="I256" s="15" t="n"/>
+      <c r="J256" s="15" t="n"/>
+      <c r="K256" s="15" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="13" t="n"/>
+      <c r="B257" s="14" t="n"/>
+      <c r="C257" s="14" t="n"/>
+      <c r="D257" s="15" t="n"/>
+      <c r="E257" s="15" t="n"/>
+      <c r="F257" s="15" t="n"/>
+      <c r="G257" s="15" t="n"/>
+      <c r="H257" s="15" t="n"/>
+      <c r="I257" s="15" t="n"/>
+      <c r="J257" s="15" t="n"/>
+      <c r="K257" s="15" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="13" t="n"/>
+      <c r="B258" s="14" t="n"/>
+      <c r="C258" s="14" t="n"/>
+      <c r="D258" s="15" t="n"/>
+      <c r="E258" s="15" t="n"/>
+      <c r="F258" s="15" t="n"/>
+      <c r="G258" s="15" t="n"/>
+      <c r="H258" s="15" t="n"/>
+      <c r="I258" s="15" t="n"/>
+      <c r="J258" s="15" t="n"/>
+      <c r="K258" s="15" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="13" t="n"/>
+      <c r="B259" s="14" t="n"/>
+      <c r="C259" s="14" t="n"/>
+      <c r="D259" s="15" t="n"/>
+      <c r="E259" s="15" t="n"/>
+      <c r="F259" s="15" t="n"/>
+      <c r="G259" s="15" t="n"/>
+      <c r="H259" s="15" t="n"/>
+      <c r="I259" s="15" t="n"/>
+      <c r="J259" s="15" t="n"/>
+      <c r="K259" s="15" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="13" t="n"/>
+      <c r="B260" s="14" t="n"/>
+      <c r="C260" s="14" t="n"/>
+      <c r="D260" s="15" t="n"/>
+      <c r="E260" s="15" t="n"/>
+      <c r="F260" s="15" t="n"/>
+      <c r="G260" s="15" t="n"/>
+      <c r="H260" s="15" t="n"/>
+      <c r="I260" s="15" t="n"/>
+      <c r="J260" s="15" t="n"/>
+      <c r="K260" s="15" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="13" t="n"/>
+      <c r="B261" s="14" t="n"/>
+      <c r="C261" s="14" t="n"/>
+      <c r="D261" s="15" t="n"/>
+      <c r="E261" s="15" t="n"/>
+      <c r="F261" s="15" t="n"/>
+      <c r="G261" s="15" t="n"/>
+      <c r="H261" s="15" t="n"/>
+      <c r="I261" s="15" t="n"/>
+      <c r="J261" s="15" t="n"/>
+      <c r="K261" s="15" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="13" t="n"/>
+      <c r="B262" s="14" t="n"/>
+      <c r="C262" s="14" t="n"/>
+      <c r="D262" s="15" t="n"/>
+      <c r="E262" s="15" t="n"/>
+      <c r="F262" s="15" t="n"/>
+      <c r="G262" s="15" t="n"/>
+      <c r="H262" s="15" t="n"/>
+      <c r="I262" s="15" t="n"/>
+      <c r="J262" s="15" t="n"/>
+      <c r="K262" s="15" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="13" t="n"/>
+      <c r="B263" s="14" t="n"/>
+      <c r="C263" s="14" t="n"/>
+      <c r="D263" s="15" t="n"/>
+      <c r="E263" s="15" t="n"/>
+      <c r="F263" s="15" t="n"/>
+      <c r="G263" s="15" t="n"/>
+      <c r="H263" s="15" t="n"/>
+      <c r="I263" s="15" t="n"/>
+      <c r="J263" s="15" t="n"/>
+      <c r="K263" s="15" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="13" t="n"/>
+      <c r="B264" s="14" t="n"/>
+      <c r="C264" s="14" t="n"/>
+      <c r="D264" s="15" t="n"/>
+      <c r="E264" s="15" t="n"/>
+      <c r="F264" s="15" t="n"/>
+      <c r="G264" s="15" t="n"/>
+      <c r="H264" s="15" t="n"/>
+      <c r="I264" s="15" t="n"/>
+      <c r="J264" s="15" t="n"/>
+      <c r="K264" s="15" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="13" t="n"/>
+      <c r="B265" s="14" t="n"/>
+      <c r="C265" s="14" t="n"/>
+      <c r="D265" s="15" t="n"/>
+      <c r="E265" s="15" t="n"/>
+      <c r="F265" s="15" t="n"/>
+      <c r="G265" s="15" t="n"/>
+      <c r="H265" s="15" t="n"/>
+      <c r="I265" s="15" t="n"/>
+      <c r="J265" s="15" t="n"/>
+      <c r="K265" s="15" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="13" t="n"/>
+      <c r="B266" s="14" t="n"/>
+      <c r="C266" s="14" t="n"/>
+      <c r="D266" s="15" t="n"/>
+      <c r="E266" s="15" t="n"/>
+      <c r="F266" s="15" t="n"/>
+      <c r="G266" s="15" t="n"/>
+      <c r="H266" s="15" t="n"/>
+      <c r="I266" s="15" t="n"/>
+      <c r="J266" s="15" t="n"/>
+      <c r="K266" s="15" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="13" t="n"/>
+      <c r="B267" s="14" t="n"/>
+      <c r="C267" s="14" t="n"/>
+      <c r="D267" s="15" t="n"/>
+      <c r="E267" s="15" t="n"/>
+      <c r="F267" s="15" t="n"/>
+      <c r="G267" s="15" t="n"/>
+      <c r="H267" s="15" t="n"/>
+      <c r="I267" s="15" t="n"/>
+      <c r="J267" s="15" t="n"/>
+      <c r="K267" s="15" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="13" t="n"/>
+      <c r="B268" s="14" t="n"/>
+      <c r="C268" s="14" t="n"/>
+      <c r="D268" s="15" t="n"/>
+      <c r="E268" s="15" t="n"/>
+      <c r="F268" s="15" t="n"/>
+      <c r="G268" s="15" t="n"/>
+      <c r="H268" s="15" t="n"/>
+      <c r="I268" s="15" t="n"/>
+      <c r="J268" s="15" t="n"/>
+      <c r="K268" s="15" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="13" t="n"/>
+      <c r="B269" s="14" t="n"/>
+      <c r="C269" s="14" t="n"/>
+      <c r="D269" s="15" t="n"/>
+      <c r="E269" s="15" t="n"/>
+      <c r="F269" s="15" t="n"/>
+      <c r="G269" s="15" t="n"/>
+      <c r="H269" s="15" t="n"/>
+      <c r="I269" s="15" t="n"/>
+      <c r="J269" s="15" t="n"/>
+      <c r="K269" s="15" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="13" t="n"/>
+      <c r="B270" s="14" t="n"/>
+      <c r="C270" s="14" t="n"/>
+      <c r="D270" s="15" t="n"/>
+      <c r="E270" s="15" t="n"/>
+      <c r="F270" s="15" t="n"/>
+      <c r="G270" s="15" t="n"/>
+      <c r="H270" s="15" t="n"/>
+      <c r="I270" s="15" t="n"/>
+      <c r="J270" s="15" t="n"/>
+      <c r="K270" s="15" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="13" t="n"/>
+      <c r="B271" s="14" t="n"/>
+      <c r="C271" s="14" t="n"/>
+      <c r="D271" s="15" t="n"/>
+      <c r="E271" s="15" t="n"/>
+      <c r="F271" s="15" t="n"/>
+      <c r="G271" s="15" t="n"/>
+      <c r="H271" s="15" t="n"/>
+      <c r="I271" s="15" t="n"/>
+      <c r="J271" s="15" t="n"/>
+      <c r="K271" s="15" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="13" t="n"/>
+      <c r="B272" s="14" t="n"/>
+      <c r="C272" s="14" t="n"/>
+      <c r="D272" s="15" t="n"/>
+      <c r="E272" s="15" t="n"/>
+      <c r="F272" s="15" t="n"/>
+      <c r="G272" s="15" t="n"/>
+      <c r="H272" s="15" t="n"/>
+      <c r="I272" s="15" t="n"/>
+      <c r="J272" s="15" t="n"/>
+      <c r="K272" s="15" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="13" t="n"/>
+      <c r="B273" s="14" t="n"/>
+      <c r="C273" s="14" t="n"/>
+      <c r="D273" s="15" t="n"/>
+      <c r="E273" s="15" t="n"/>
+      <c r="F273" s="15" t="n"/>
+      <c r="G273" s="15" t="n"/>
+      <c r="H273" s="15" t="n"/>
+      <c r="I273" s="15" t="n"/>
+      <c r="J273" s="15" t="n"/>
+      <c r="K273" s="15" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="13" t="n"/>
+      <c r="B274" s="14" t="n"/>
+      <c r="C274" s="14" t="n"/>
+      <c r="D274" s="15" t="n"/>
+      <c r="E274" s="15" t="n"/>
+      <c r="F274" s="15" t="n"/>
+      <c r="G274" s="15" t="n"/>
+      <c r="H274" s="15" t="n"/>
+      <c r="I274" s="15" t="n"/>
+      <c r="J274" s="15" t="n"/>
+      <c r="K274" s="15" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="13" t="n"/>
+      <c r="B275" s="14" t="n"/>
+      <c r="C275" s="14" t="n"/>
+      <c r="D275" s="15" t="n"/>
+      <c r="E275" s="15" t="n"/>
+      <c r="F275" s="15" t="n"/>
+      <c r="G275" s="15" t="n"/>
+      <c r="H275" s="15" t="n"/>
+      <c r="I275" s="15" t="n"/>
+      <c r="J275" s="15" t="n"/>
+      <c r="K275" s="15" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="13" t="n"/>
+      <c r="B276" s="14" t="n"/>
+      <c r="C276" s="14" t="n"/>
+      <c r="D276" s="15" t="n"/>
+      <c r="E276" s="15" t="n"/>
+      <c r="F276" s="15" t="n"/>
+      <c r="G276" s="15" t="n"/>
+      <c r="H276" s="15" t="n"/>
+      <c r="I276" s="15" t="n"/>
+      <c r="J276" s="15" t="n"/>
+      <c r="K276" s="15" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="13" t="n"/>
+      <c r="B277" s="14" t="n"/>
+      <c r="C277" s="14" t="n"/>
+      <c r="D277" s="15" t="n"/>
+      <c r="E277" s="15" t="n"/>
+      <c r="F277" s="15" t="n"/>
+      <c r="G277" s="15" t="n"/>
+      <c r="H277" s="15" t="n"/>
+      <c r="I277" s="15" t="n"/>
+      <c r="J277" s="15" t="n"/>
+      <c r="K277" s="15" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="13" t="n"/>
+      <c r="B278" s="14" t="n"/>
+      <c r="C278" s="14" t="n"/>
+      <c r="D278" s="15" t="n"/>
+      <c r="E278" s="15" t="n"/>
+      <c r="F278" s="15" t="n"/>
+      <c r="G278" s="15" t="n"/>
+      <c r="H278" s="15" t="n"/>
+      <c r="I278" s="15" t="n"/>
+      <c r="J278" s="15" t="n"/>
+      <c r="K278" s="15" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="13" t="n"/>
+      <c r="B279" s="14" t="n"/>
+      <c r="C279" s="14" t="n"/>
+      <c r="D279" s="15" t="n"/>
+      <c r="E279" s="15" t="n"/>
+      <c r="F279" s="15" t="n"/>
+      <c r="G279" s="15" t="n"/>
+      <c r="H279" s="15" t="n"/>
+      <c r="I279" s="15" t="n"/>
+      <c r="J279" s="15" t="n"/>
+      <c r="K279" s="15" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="13" t="n"/>
+      <c r="B280" s="14" t="n"/>
+      <c r="C280" s="14" t="n"/>
+      <c r="D280" s="15" t="n"/>
+      <c r="E280" s="15" t="n"/>
+      <c r="F280" s="15" t="n"/>
+      <c r="G280" s="15" t="n"/>
+      <c r="H280" s="15" t="n"/>
+      <c r="I280" s="15" t="n"/>
+      <c r="J280" s="15" t="n"/>
+      <c r="K280" s="15" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="13" t="n"/>
+      <c r="B281" s="14" t="n"/>
+      <c r="C281" s="14" t="n"/>
+      <c r="D281" s="15" t="n"/>
+      <c r="E281" s="15" t="n"/>
+      <c r="F281" s="15" t="n"/>
+      <c r="G281" s="15" t="n"/>
+      <c r="H281" s="15" t="n"/>
+      <c r="I281" s="15" t="n"/>
+      <c r="J281" s="15" t="n"/>
+      <c r="K281" s="15" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="13" t="n"/>
+      <c r="B282" s="14" t="n"/>
+      <c r="C282" s="14" t="n"/>
+      <c r="D282" s="15" t="n"/>
+      <c r="E282" s="15" t="n"/>
+      <c r="F282" s="15" t="n"/>
+      <c r="G282" s="15" t="n"/>
+      <c r="H282" s="15" t="n"/>
+      <c r="I282" s="15" t="n"/>
+      <c r="J282" s="15" t="n"/>
+      <c r="K282" s="15" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="13" t="n"/>
+      <c r="B283" s="14" t="n"/>
+      <c r="C283" s="14" t="n"/>
+      <c r="D283" s="15" t="n"/>
+      <c r="E283" s="15" t="n"/>
+      <c r="F283" s="15" t="n"/>
+      <c r="G283" s="15" t="n"/>
+      <c r="H283" s="15" t="n"/>
+      <c r="I283" s="15" t="n"/>
+      <c r="J283" s="15" t="n"/>
+      <c r="K283" s="15" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="13" t="n"/>
+      <c r="B284" s="14" t="n"/>
+      <c r="C284" s="14" t="n"/>
+      <c r="D284" s="15" t="n"/>
+      <c r="E284" s="15" t="n"/>
+      <c r="F284" s="15" t="n"/>
+      <c r="G284" s="15" t="n"/>
+      <c r="H284" s="15" t="n"/>
+      <c r="I284" s="15" t="n"/>
+      <c r="J284" s="15" t="n"/>
+      <c r="K284" s="15" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="13" t="n"/>
+      <c r="B285" s="14" t="n"/>
+      <c r="C285" s="14" t="n"/>
+      <c r="D285" s="15" t="n"/>
+      <c r="E285" s="15" t="n"/>
+      <c r="F285" s="15" t="n"/>
+      <c r="G285" s="15" t="n"/>
+      <c r="H285" s="15" t="n"/>
+      <c r="I285" s="15" t="n"/>
+      <c r="J285" s="15" t="n"/>
+      <c r="K285" s="15" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="13" t="n"/>
+      <c r="B286" s="14" t="n"/>
+      <c r="C286" s="14" t="n"/>
+      <c r="D286" s="15" t="n"/>
+      <c r="E286" s="15" t="n"/>
+      <c r="F286" s="15" t="n"/>
+      <c r="G286" s="15" t="n"/>
+      <c r="H286" s="15" t="n"/>
+      <c r="I286" s="15" t="n"/>
+      <c r="J286" s="15" t="n"/>
+      <c r="K286" s="15" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="13" t="n"/>
+      <c r="B287" s="14" t="n"/>
+      <c r="C287" s="14" t="n"/>
+      <c r="D287" s="15" t="n"/>
+      <c r="E287" s="15" t="n"/>
+      <c r="F287" s="15" t="n"/>
+      <c r="G287" s="15" t="n"/>
+      <c r="H287" s="15" t="n"/>
+      <c r="I287" s="15" t="n"/>
+      <c r="J287" s="15" t="n"/>
+      <c r="K287" s="15" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="13" t="n"/>
+      <c r="B288" s="14" t="n"/>
+      <c r="C288" s="14" t="n"/>
+      <c r="D288" s="15" t="n"/>
+      <c r="E288" s="15" t="n"/>
+      <c r="F288" s="15" t="n"/>
+      <c r="G288" s="15" t="n"/>
+      <c r="H288" s="15" t="n"/>
+      <c r="I288" s="15" t="n"/>
+      <c r="J288" s="15" t="n"/>
+      <c r="K288" s="15" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="13" t="n"/>
+      <c r="B289" s="14" t="n"/>
+      <c r="C289" s="14" t="n"/>
+      <c r="D289" s="15" t="n"/>
+      <c r="E289" s="15" t="n"/>
+      <c r="F289" s="15" t="n"/>
+      <c r="G289" s="15" t="n"/>
+      <c r="H289" s="15" t="n"/>
+      <c r="I289" s="15" t="n"/>
+      <c r="J289" s="15" t="n"/>
+      <c r="K289" s="15" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="13" t="n"/>
+      <c r="B290" s="14" t="n"/>
+      <c r="C290" s="14" t="n"/>
+      <c r="D290" s="15" t="n"/>
+      <c r="E290" s="15" t="n"/>
+      <c r="F290" s="15" t="n"/>
+      <c r="G290" s="15" t="n"/>
+      <c r="H290" s="15" t="n"/>
+      <c r="I290" s="15" t="n"/>
+      <c r="J290" s="15" t="n"/>
+      <c r="K290" s="15" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="13" t="n"/>
+      <c r="B291" s="14" t="n"/>
+      <c r="C291" s="14" t="n"/>
+      <c r="D291" s="15" t="n"/>
+      <c r="E291" s="15" t="n"/>
+      <c r="F291" s="15" t="n"/>
+      <c r="G291" s="15" t="n"/>
+      <c r="H291" s="15" t="n"/>
+      <c r="I291" s="15" t="n"/>
+      <c r="J291" s="15" t="n"/>
+      <c r="K291" s="15" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="13" t="n"/>
+      <c r="B292" s="14" t="n"/>
+      <c r="C292" s="14" t="n"/>
+      <c r="D292" s="15" t="n"/>
+      <c r="E292" s="15" t="n"/>
+      <c r="F292" s="15" t="n"/>
+      <c r="G292" s="15" t="n"/>
+      <c r="H292" s="15" t="n"/>
+      <c r="I292" s="15" t="n"/>
+      <c r="J292" s="15" t="n"/>
+      <c r="K292" s="15" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="13" t="n"/>
+      <c r="B293" s="14" t="n"/>
+      <c r="C293" s="14" t="n"/>
+      <c r="D293" s="15" t="n"/>
+      <c r="E293" s="15" t="n"/>
+      <c r="F293" s="15" t="n"/>
+      <c r="G293" s="15" t="n"/>
+      <c r="H293" s="15" t="n"/>
+      <c r="I293" s="15" t="n"/>
+      <c r="J293" s="15" t="n"/>
+      <c r="K293" s="15" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="13" t="n"/>
+      <c r="B294" s="14" t="n"/>
+      <c r="C294" s="14" t="n"/>
+      <c r="D294" s="15" t="n"/>
+      <c r="E294" s="15" t="n"/>
+      <c r="F294" s="15" t="n"/>
+      <c r="G294" s="15" t="n"/>
+      <c r="H294" s="15" t="n"/>
+      <c r="I294" s="15" t="n"/>
+      <c r="J294" s="15" t="n"/>
+      <c r="K294" s="15" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="13" t="n"/>
+      <c r="B295" s="14" t="n"/>
+      <c r="C295" s="14" t="n"/>
+      <c r="D295" s="15" t="n"/>
+      <c r="E295" s="15" t="n"/>
+      <c r="F295" s="15" t="n"/>
+      <c r="G295" s="15" t="n"/>
+      <c r="H295" s="15" t="n"/>
+      <c r="I295" s="15" t="n"/>
+      <c r="J295" s="15" t="n"/>
+      <c r="K295" s="15" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="13" t="n"/>
+      <c r="B296" s="14" t="n"/>
+      <c r="C296" s="14" t="n"/>
+      <c r="D296" s="15" t="n"/>
+      <c r="E296" s="15" t="n"/>
+      <c r="F296" s="15" t="n"/>
+      <c r="G296" s="15" t="n"/>
+      <c r="H296" s="15" t="n"/>
+      <c r="I296" s="15" t="n"/>
+      <c r="J296" s="15" t="n"/>
+      <c r="K296" s="15" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="13" t="n"/>
+      <c r="B297" s="14" t="n"/>
+      <c r="C297" s="14" t="n"/>
+      <c r="D297" s="15" t="n"/>
+      <c r="E297" s="15" t="n"/>
+      <c r="F297" s="15" t="n"/>
+      <c r="G297" s="15" t="n"/>
+      <c r="H297" s="15" t="n"/>
+      <c r="I297" s="15" t="n"/>
+      <c r="J297" s="15" t="n"/>
+      <c r="K297" s="15" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="13" t="n"/>
+      <c r="B298" s="14" t="n"/>
+      <c r="C298" s="14" t="n"/>
+      <c r="D298" s="15" t="n"/>
+      <c r="E298" s="15" t="n"/>
+      <c r="F298" s="15" t="n"/>
+      <c r="G298" s="15" t="n"/>
+      <c r="H298" s="15" t="n"/>
+      <c r="I298" s="15" t="n"/>
+      <c r="J298" s="15" t="n"/>
+      <c r="K298" s="15" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="13" t="n"/>
+      <c r="B299" s="14" t="n"/>
+      <c r="C299" s="14" t="n"/>
+      <c r="D299" s="15" t="n"/>
+      <c r="E299" s="15" t="n"/>
+      <c r="F299" s="15" t="n"/>
+      <c r="G299" s="15" t="n"/>
+      <c r="H299" s="15" t="n"/>
+      <c r="I299" s="15" t="n"/>
+      <c r="J299" s="15" t="n"/>
+      <c r="K299" s="15" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="13" t="n"/>
+      <c r="B300" s="14" t="n"/>
+      <c r="C300" s="14" t="n"/>
+      <c r="D300" s="15" t="n"/>
+      <c r="E300" s="15" t="n"/>
+      <c r="F300" s="15" t="n"/>
+      <c r="G300" s="15" t="n"/>
+      <c r="H300" s="15" t="n"/>
+      <c r="I300" s="15" t="n"/>
+      <c r="J300" s="15" t="n"/>
+      <c r="K300" s="15" t="n"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="13" t="n"/>
+      <c r="B301" s="14" t="n"/>
+      <c r="C301" s="14" t="n"/>
+      <c r="D301" s="15" t="n"/>
+      <c r="E301" s="15" t="n"/>
+      <c r="F301" s="15" t="n"/>
+      <c r="G301" s="15" t="n"/>
+      <c r="H301" s="15" t="n"/>
+      <c r="I301" s="15" t="n"/>
+      <c r="J301" s="15" t="n"/>
+      <c r="K301" s="15" t="n"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="13" t="n"/>
+      <c r="B302" s="14" t="n"/>
+      <c r="C302" s="14" t="n"/>
+      <c r="D302" s="15" t="n"/>
+      <c r="E302" s="15" t="n"/>
+      <c r="F302" s="15" t="n"/>
+      <c r="G302" s="15" t="n"/>
+      <c r="H302" s="15" t="n"/>
+      <c r="I302" s="15" t="n"/>
+      <c r="J302" s="15" t="n"/>
+      <c r="K302" s="15" t="n"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="13" t="n"/>
+      <c r="B303" s="14" t="n"/>
+      <c r="C303" s="14" t="n"/>
+      <c r="D303" s="15" t="n"/>
+      <c r="E303" s="15" t="n"/>
+      <c r="F303" s="15" t="n"/>
+      <c r="G303" s="15" t="n"/>
+      <c r="H303" s="15" t="n"/>
+      <c r="I303" s="15" t="n"/>
+      <c r="J303" s="15" t="n"/>
+      <c r="K303" s="15" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="13" t="n"/>
+      <c r="B304" s="14" t="n"/>
+      <c r="C304" s="14" t="n"/>
+      <c r="D304" s="15" t="n"/>
+      <c r="E304" s="15" t="n"/>
+      <c r="F304" s="15" t="n"/>
+      <c r="G304" s="15" t="n"/>
+      <c r="H304" s="15" t="n"/>
+      <c r="I304" s="15" t="n"/>
+      <c r="J304" s="15" t="n"/>
+      <c r="K304" s="15" t="n"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="13" t="n"/>
+      <c r="B305" s="14" t="n"/>
+      <c r="C305" s="14" t="n"/>
+      <c r="D305" s="15" t="n"/>
+      <c r="E305" s="15" t="n"/>
+      <c r="F305" s="15" t="n"/>
+      <c r="G305" s="15" t="n"/>
+      <c r="H305" s="15" t="n"/>
+      <c r="I305" s="15" t="n"/>
+      <c r="J305" s="15" t="n"/>
+      <c r="K305" s="15" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="13" t="n"/>
+      <c r="B306" s="14" t="n"/>
+      <c r="C306" s="14" t="n"/>
+      <c r="D306" s="15" t="n"/>
+      <c r="E306" s="15" t="n"/>
+      <c r="F306" s="15" t="n"/>
+      <c r="G306" s="15" t="n"/>
+      <c r="H306" s="15" t="n"/>
+      <c r="I306" s="15" t="n"/>
+      <c r="J306" s="15" t="n"/>
+      <c r="K306" s="15" t="n"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="13" t="n"/>
+      <c r="B307" s="14" t="n"/>
+      <c r="C307" s="14" t="n"/>
+      <c r="D307" s="15" t="n"/>
+      <c r="E307" s="15" t="n"/>
+      <c r="F307" s="15" t="n"/>
+      <c r="G307" s="15" t="n"/>
+      <c r="H307" s="15" t="n"/>
+      <c r="I307" s="15" t="n"/>
+      <c r="J307" s="15" t="n"/>
+      <c r="K307" s="15" t="n"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="13" t="n"/>
+      <c r="B308" s="14" t="n"/>
+      <c r="C308" s="14" t="n"/>
+      <c r="D308" s="15" t="n"/>
+      <c r="E308" s="15" t="n"/>
+      <c r="F308" s="15" t="n"/>
+      <c r="G308" s="15" t="n"/>
+      <c r="H308" s="15" t="n"/>
+      <c r="I308" s="15" t="n"/>
+      <c r="J308" s="15" t="n"/>
+      <c r="K308" s="15" t="n"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="13" t="n"/>
+      <c r="B309" s="14" t="n"/>
+      <c r="C309" s="14" t="n"/>
+      <c r="D309" s="15" t="n"/>
+      <c r="E309" s="15" t="n"/>
+      <c r="F309" s="15" t="n"/>
+      <c r="G309" s="15" t="n"/>
+      <c r="H309" s="15" t="n"/>
+      <c r="I309" s="15" t="n"/>
+      <c r="J309" s="15" t="n"/>
+      <c r="K309" s="15" t="n"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="13" t="n"/>
+      <c r="B310" s="14" t="n"/>
+      <c r="C310" s="14" t="n"/>
+      <c r="D310" s="15" t="n"/>
+      <c r="E310" s="15" t="n"/>
+      <c r="F310" s="15" t="n"/>
+      <c r="G310" s="15" t="n"/>
+      <c r="H310" s="15" t="n"/>
+      <c r="I310" s="15" t="n"/>
+      <c r="J310" s="15" t="n"/>
+      <c r="K310" s="15" t="n"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="13" t="n"/>
+      <c r="B311" s="14" t="n"/>
+      <c r="C311" s="14" t="n"/>
+      <c r="D311" s="15" t="n"/>
+      <c r="E311" s="15" t="n"/>
+      <c r="F311" s="15" t="n"/>
+      <c r="G311" s="15" t="n"/>
+      <c r="H311" s="15" t="n"/>
+      <c r="I311" s="15" t="n"/>
+      <c r="J311" s="15" t="n"/>
+      <c r="K311" s="15" t="n"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="13" t="n"/>
+      <c r="B312" s="14" t="n"/>
+      <c r="C312" s="14" t="n"/>
+      <c r="D312" s="15" t="n"/>
+      <c r="E312" s="15" t="n"/>
+      <c r="F312" s="15" t="n"/>
+      <c r="G312" s="15" t="n"/>
+      <c r="H312" s="15" t="n"/>
+      <c r="I312" s="15" t="n"/>
+      <c r="J312" s="15" t="n"/>
+      <c r="K312" s="15" t="n"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="13" t="n"/>
+      <c r="B313" s="14" t="n"/>
+      <c r="C313" s="14" t="n"/>
+      <c r="D313" s="15" t="n"/>
+      <c r="E313" s="15" t="n"/>
+      <c r="F313" s="15" t="n"/>
+      <c r="G313" s="15" t="n"/>
+      <c r="H313" s="15" t="n"/>
+      <c r="I313" s="15" t="n"/>
+      <c r="J313" s="15" t="n"/>
+      <c r="K313" s="15" t="n"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="13" t="n"/>
+      <c r="B314" s="14" t="n"/>
+      <c r="C314" s="14" t="n"/>
+      <c r="D314" s="15" t="n"/>
+      <c r="E314" s="15" t="n"/>
+      <c r="F314" s="15" t="n"/>
+      <c r="G314" s="15" t="n"/>
+      <c r="H314" s="15" t="n"/>
+      <c r="I314" s="15" t="n"/>
+      <c r="J314" s="15" t="n"/>
+      <c r="K314" s="15" t="n"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="13" t="n"/>
+      <c r="B315" s="14" t="n"/>
+      <c r="C315" s="14" t="n"/>
+      <c r="D315" s="15" t="n"/>
+      <c r="E315" s="15" t="n"/>
+      <c r="F315" s="15" t="n"/>
+      <c r="G315" s="15" t="n"/>
+      <c r="H315" s="15" t="n"/>
+      <c r="I315" s="15" t="n"/>
+      <c r="J315" s="15" t="n"/>
+      <c r="K315" s="15" t="n"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="13" t="n"/>
+      <c r="B316" s="14" t="n"/>
+      <c r="C316" s="14" t="n"/>
+      <c r="D316" s="15" t="n"/>
+      <c r="E316" s="15" t="n"/>
+      <c r="F316" s="15" t="n"/>
+      <c r="G316" s="15" t="n"/>
+      <c r="H316" s="15" t="n"/>
+      <c r="I316" s="15" t="n"/>
+      <c r="J316" s="15" t="n"/>
+      <c r="K316" s="15" t="n"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="13" t="n"/>
+      <c r="B317" s="14" t="n"/>
+      <c r="C317" s="14" t="n"/>
+      <c r="D317" s="15" t="n"/>
+      <c r="E317" s="15" t="n"/>
+      <c r="F317" s="15" t="n"/>
+      <c r="G317" s="15" t="n"/>
+      <c r="H317" s="15" t="n"/>
+      <c r="I317" s="15" t="n"/>
+      <c r="J317" s="15" t="n"/>
+      <c r="K317" s="15" t="n"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="13" t="n"/>
+      <c r="B318" s="14" t="n"/>
+      <c r="C318" s="14" t="n"/>
+      <c r="D318" s="15" t="n"/>
+      <c r="E318" s="15" t="n"/>
+      <c r="F318" s="15" t="n"/>
+      <c r="G318" s="15" t="n"/>
+      <c r="H318" s="15" t="n"/>
+      <c r="I318" s="15" t="n"/>
+      <c r="J318" s="15" t="n"/>
+      <c r="K318" s="15" t="n"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="13" t="n"/>
+      <c r="B319" s="14" t="n"/>
+      <c r="C319" s="14" t="n"/>
+      <c r="D319" s="15" t="n"/>
+      <c r="E319" s="15" t="n"/>
+      <c r="F319" s="15" t="n"/>
+      <c r="G319" s="15" t="n"/>
+      <c r="H319" s="15" t="n"/>
+      <c r="I319" s="15" t="n"/>
+      <c r="J319" s="15" t="n"/>
+      <c r="K319" s="15" t="n"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="13" t="n"/>
+      <c r="B320" s="14" t="n"/>
+      <c r="C320" s="14" t="n"/>
+      <c r="D320" s="15" t="n"/>
+      <c r="E320" s="15" t="n"/>
+      <c r="F320" s="15" t="n"/>
+      <c r="G320" s="15" t="n"/>
+      <c r="H320" s="15" t="n"/>
+      <c r="I320" s="15" t="n"/>
+      <c r="J320" s="15" t="n"/>
+      <c r="K320" s="15" t="n"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="13" t="n"/>
+      <c r="B321" s="14" t="n"/>
+      <c r="C321" s="14" t="n"/>
+      <c r="D321" s="15" t="n"/>
+      <c r="E321" s="15" t="n"/>
+      <c r="F321" s="15" t="n"/>
+      <c r="G321" s="15" t="n"/>
+      <c r="H321" s="15" t="n"/>
+      <c r="I321" s="15" t="n"/>
+      <c r="J321" s="15" t="n"/>
+      <c r="K321" s="15" t="n"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="13" t="n"/>
+      <c r="B322" s="14" t="n"/>
+      <c r="C322" s="14" t="n"/>
+      <c r="D322" s="15" t="n"/>
+      <c r="E322" s="15" t="n"/>
+      <c r="F322" s="15" t="n"/>
+      <c r="G322" s="15" t="n"/>
+      <c r="H322" s="15" t="n"/>
+      <c r="I322" s="15" t="n"/>
+      <c r="J322" s="15" t="n"/>
+      <c r="K322" s="15" t="n"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="13" t="n"/>
+      <c r="B323" s="14" t="n"/>
+      <c r="C323" s="14" t="n"/>
+      <c r="D323" s="15" t="n"/>
+      <c r="E323" s="15" t="n"/>
+      <c r="F323" s="15" t="n"/>
+      <c r="G323" s="15" t="n"/>
+      <c r="H323" s="15" t="n"/>
+      <c r="I323" s="15" t="n"/>
+      <c r="J323" s="15" t="n"/>
+      <c r="K323" s="15" t="n"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="13" t="n"/>
+      <c r="B324" s="14" t="n"/>
+      <c r="C324" s="14" t="n"/>
+      <c r="D324" s="15" t="n"/>
+      <c r="E324" s="15" t="n"/>
+      <c r="F324" s="15" t="n"/>
+      <c r="G324" s="15" t="n"/>
+      <c r="H324" s="15" t="n"/>
+      <c r="I324" s="15" t="n"/>
+      <c r="J324" s="15" t="n"/>
+      <c r="K324" s="15" t="n"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="13" t="n"/>
+      <c r="B325" s="14" t="n"/>
+      <c r="C325" s="14" t="n"/>
+      <c r="D325" s="15" t="n"/>
+      <c r="E325" s="15" t="n"/>
+      <c r="F325" s="15" t="n"/>
+      <c r="G325" s="15" t="n"/>
+      <c r="H325" s="15" t="n"/>
+      <c r="I325" s="15" t="n"/>
+      <c r="J325" s="15" t="n"/>
+      <c r="K325" s="15" t="n"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="13" t="n"/>
+      <c r="B326" s="14" t="n"/>
+      <c r="C326" s="14" t="n"/>
+      <c r="D326" s="15" t="n"/>
+      <c r="E326" s="15" t="n"/>
+      <c r="F326" s="15" t="n"/>
+      <c r="G326" s="15" t="n"/>
+      <c r="H326" s="15" t="n"/>
+      <c r="I326" s="15" t="n"/>
+      <c r="J326" s="15" t="n"/>
+      <c r="K326" s="15" t="n"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="13" t="n"/>
+      <c r="B327" s="14" t="n"/>
+      <c r="C327" s="14" t="n"/>
+      <c r="D327" s="15" t="n"/>
+      <c r="E327" s="15" t="n"/>
+      <c r="F327" s="15" t="n"/>
+      <c r="G327" s="15" t="n"/>
+      <c r="H327" s="15" t="n"/>
+      <c r="I327" s="15" t="n"/>
+      <c r="J327" s="15" t="n"/>
+      <c r="K327" s="15" t="n"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="13" t="n"/>
+      <c r="B328" s="14" t="n"/>
+      <c r="C328" s="14" t="n"/>
+      <c r="D328" s="15" t="n"/>
+      <c r="E328" s="15" t="n"/>
+      <c r="F328" s="15" t="n"/>
+      <c r="G328" s="15" t="n"/>
+      <c r="H328" s="15" t="n"/>
+      <c r="I328" s="15" t="n"/>
+      <c r="J328" s="15" t="n"/>
+      <c r="K328" s="15" t="n"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="13" t="n"/>
+      <c r="B329" s="14" t="n"/>
+      <c r="C329" s="14" t="n"/>
+      <c r="D329" s="15" t="n"/>
+      <c r="E329" s="15" t="n"/>
+      <c r="F329" s="15" t="n"/>
+      <c r="G329" s="15" t="n"/>
+      <c r="H329" s="15" t="n"/>
+      <c r="I329" s="15" t="n"/>
+      <c r="J329" s="15" t="n"/>
+      <c r="K329" s="15" t="n"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="13" t="n"/>
+      <c r="B330" s="14" t="n"/>
+      <c r="C330" s="14" t="n"/>
+      <c r="D330" s="15" t="n"/>
+      <c r="E330" s="15" t="n"/>
+      <c r="F330" s="15" t="n"/>
+      <c r="G330" s="15" t="n"/>
+      <c r="H330" s="15" t="n"/>
+      <c r="I330" s="15" t="n"/>
+      <c r="J330" s="15" t="n"/>
+      <c r="K330" s="15" t="n"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="13" t="n"/>
+      <c r="B331" s="14" t="n"/>
+      <c r="C331" s="14" t="n"/>
+      <c r="D331" s="15" t="n"/>
+      <c r="E331" s="15" t="n"/>
+      <c r="F331" s="15" t="n"/>
+      <c r="G331" s="15" t="n"/>
+      <c r="H331" s="15" t="n"/>
+      <c r="I331" s="15" t="n"/>
+      <c r="J331" s="15" t="n"/>
+      <c r="K331" s="15" t="n"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="13" t="n"/>
+      <c r="B332" s="14" t="n"/>
+      <c r="C332" s="14" t="n"/>
+      <c r="D332" s="15" t="n"/>
+      <c r="E332" s="15" t="n"/>
+      <c r="F332" s="15" t="n"/>
+      <c r="G332" s="15" t="n"/>
+      <c r="H332" s="15" t="n"/>
+      <c r="I332" s="15" t="n"/>
+      <c r="J332" s="15" t="n"/>
+      <c r="K332" s="15" t="n"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="13" t="n"/>
+      <c r="B333" s="14" t="n"/>
+      <c r="C333" s="14" t="n"/>
+      <c r="D333" s="15" t="n"/>
+      <c r="E333" s="15" t="n"/>
+      <c r="F333" s="15" t="n"/>
+      <c r="G333" s="15" t="n"/>
+      <c r="H333" s="15" t="n"/>
+      <c r="I333" s="15" t="n"/>
+      <c r="J333" s="15" t="n"/>
+      <c r="K333" s="15" t="n"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="13" t="n"/>
+      <c r="B334" s="14" t="n"/>
+      <c r="C334" s="14" t="n"/>
+      <c r="D334" s="15" t="n"/>
+      <c r="E334" s="15" t="n"/>
+      <c r="F334" s="15" t="n"/>
+      <c r="G334" s="15" t="n"/>
+      <c r="H334" s="15" t="n"/>
+      <c r="I334" s="15" t="n"/>
+      <c r="J334" s="15" t="n"/>
+      <c r="K334" s="15" t="n"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="13" t="n"/>
+      <c r="B335" s="14" t="n"/>
+      <c r="C335" s="14" t="n"/>
+      <c r="D335" s="15" t="n"/>
+      <c r="E335" s="15" t="n"/>
+      <c r="F335" s="15" t="n"/>
+      <c r="G335" s="15" t="n"/>
+      <c r="H335" s="15" t="n"/>
+      <c r="I335" s="15" t="n"/>
+      <c r="J335" s="15" t="n"/>
+      <c r="K335" s="15" t="n"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="13" t="n"/>
+      <c r="B336" s="14" t="n"/>
+      <c r="C336" s="14" t="n"/>
+      <c r="D336" s="15" t="n"/>
+      <c r="E336" s="15" t="n"/>
+      <c r="F336" s="15" t="n"/>
+      <c r="G336" s="15" t="n"/>
+      <c r="H336" s="15" t="n"/>
+      <c r="I336" s="15" t="n"/>
+      <c r="J336" s="15" t="n"/>
+      <c r="K336" s="15" t="n"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="13" t="n"/>
+      <c r="B337" s="14" t="n"/>
+      <c r="C337" s="14" t="n"/>
+      <c r="D337" s="15" t="n"/>
+      <c r="E337" s="15" t="n"/>
+      <c r="F337" s="15" t="n"/>
+      <c r="G337" s="15" t="n"/>
+      <c r="H337" s="15" t="n"/>
+      <c r="I337" s="15" t="n"/>
+      <c r="J337" s="15" t="n"/>
+      <c r="K337" s="15" t="n"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="13" t="n"/>
+      <c r="B338" s="14" t="n"/>
+      <c r="C338" s="14" t="n"/>
+      <c r="D338" s="15" t="n"/>
+      <c r="E338" s="15" t="n"/>
+      <c r="F338" s="15" t="n"/>
+      <c r="G338" s="15" t="n"/>
+      <c r="H338" s="15" t="n"/>
+      <c r="I338" s="15" t="n"/>
+      <c r="J338" s="15" t="n"/>
+      <c r="K338" s="15" t="n"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="13" t="n"/>
+      <c r="B339" s="14" t="n"/>
+      <c r="C339" s="14" t="n"/>
+      <c r="D339" s="15" t="n"/>
+      <c r="E339" s="15" t="n"/>
+      <c r="F339" s="15" t="n"/>
+      <c r="G339" s="15" t="n"/>
+      <c r="H339" s="15" t="n"/>
+      <c r="I339" s="15" t="n"/>
+      <c r="J339" s="15" t="n"/>
+      <c r="K339" s="15" t="n"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="13" t="n"/>
+      <c r="B340" s="14" t="n"/>
+      <c r="C340" s="14" t="n"/>
+      <c r="D340" s="15" t="n"/>
+      <c r="E340" s="15" t="n"/>
+      <c r="F340" s="15" t="n"/>
+      <c r="G340" s="15" t="n"/>
+      <c r="H340" s="15" t="n"/>
+      <c r="I340" s="15" t="n"/>
+      <c r="J340" s="15" t="n"/>
+      <c r="K340" s="15" t="n"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="13" t="n"/>
+      <c r="B341" s="14" t="n"/>
+      <c r="C341" s="14" t="n"/>
+      <c r="D341" s="15" t="n"/>
+      <c r="E341" s="15" t="n"/>
+      <c r="F341" s="15" t="n"/>
+      <c r="G341" s="15" t="n"/>
+      <c r="H341" s="15" t="n"/>
+      <c r="I341" s="15" t="n"/>
+      <c r="J341" s="15" t="n"/>
+      <c r="K341" s="15" t="n"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="13" t="n"/>
+      <c r="B342" s="14" t="n"/>
+      <c r="C342" s="14" t="n"/>
+      <c r="D342" s="15" t="n"/>
+      <c r="E342" s="15" t="n"/>
+      <c r="F342" s="15" t="n"/>
+      <c r="G342" s="15" t="n"/>
+      <c r="H342" s="15" t="n"/>
+      <c r="I342" s="15" t="n"/>
+      <c r="J342" s="15" t="n"/>
+      <c r="K342" s="15" t="n"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="13" t="n"/>
+      <c r="B343" s="14" t="n"/>
+      <c r="C343" s="14" t="n"/>
+      <c r="D343" s="15" t="n"/>
+      <c r="E343" s="15" t="n"/>
+      <c r="F343" s="15" t="n"/>
+      <c r="G343" s="15" t="n"/>
+      <c r="H343" s="15" t="n"/>
+      <c r="I343" s="15" t="n"/>
+      <c r="J343" s="15" t="n"/>
+      <c r="K343" s="15" t="n"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="13" t="n"/>
+      <c r="B344" s="14" t="n"/>
+      <c r="C344" s="14" t="n"/>
+      <c r="D344" s="15" t="n"/>
+      <c r="E344" s="15" t="n"/>
+      <c r="F344" s="15" t="n"/>
+      <c r="G344" s="15" t="n"/>
+      <c r="H344" s="15" t="n"/>
+      <c r="I344" s="15" t="n"/>
+      <c r="J344" s="15" t="n"/>
+      <c r="K344" s="15" t="n"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="13" t="n"/>
+      <c r="B345" s="14" t="n"/>
+      <c r="C345" s="14" t="n"/>
+      <c r="D345" s="15" t="n"/>
+      <c r="E345" s="15" t="n"/>
+      <c r="F345" s="15" t="n"/>
+      <c r="G345" s="15" t="n"/>
+      <c r="H345" s="15" t="n"/>
+      <c r="I345" s="15" t="n"/>
+      <c r="J345" s="15" t="n"/>
+      <c r="K345" s="15" t="n"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="13" t="n"/>
+      <c r="B346" s="14" t="n"/>
+      <c r="C346" s="14" t="n"/>
+      <c r="D346" s="15" t="n"/>
+      <c r="E346" s="15" t="n"/>
+      <c r="F346" s="15" t="n"/>
+      <c r="G346" s="15" t="n"/>
+      <c r="H346" s="15" t="n"/>
+      <c r="I346" s="15" t="n"/>
+      <c r="J346" s="15" t="n"/>
+      <c r="K346" s="15" t="n"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="13" t="n"/>
+      <c r="B347" s="14" t="n"/>
+      <c r="C347" s="14" t="n"/>
+      <c r="D347" s="15" t="n"/>
+      <c r="E347" s="15" t="n"/>
+      <c r="F347" s="15" t="n"/>
+      <c r="G347" s="15" t="n"/>
+      <c r="H347" s="15" t="n"/>
+      <c r="I347" s="15" t="n"/>
+      <c r="J347" s="15" t="n"/>
+      <c r="K347" s="15" t="n"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="13" t="n"/>
+      <c r="B348" s="14" t="n"/>
+      <c r="C348" s="14" t="n"/>
+      <c r="D348" s="15" t="n"/>
+      <c r="E348" s="15" t="n"/>
+      <c r="F348" s="15" t="n"/>
+      <c r="G348" s="15" t="n"/>
+      <c r="H348" s="15" t="n"/>
+      <c r="I348" s="15" t="n"/>
+      <c r="J348" s="15" t="n"/>
+      <c r="K348" s="15" t="n"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="13" t="n"/>
+      <c r="B349" s="14" t="n"/>
+      <c r="C349" s="14" t="n"/>
+      <c r="D349" s="15" t="n"/>
+      <c r="E349" s="15" t="n"/>
+      <c r="F349" s="15" t="n"/>
+      <c r="G349" s="15" t="n"/>
+      <c r="H349" s="15" t="n"/>
+      <c r="I349" s="15" t="n"/>
+      <c r="J349" s="15" t="n"/>
+      <c r="K349" s="15" t="n"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="13" t="n"/>
+      <c r="B350" s="14" t="n"/>
+      <c r="C350" s="14" t="n"/>
+      <c r="D350" s="15" t="n"/>
+      <c r="E350" s="15" t="n"/>
+      <c r="F350" s="15" t="n"/>
+      <c r="G350" s="15" t="n"/>
+      <c r="H350" s="15" t="n"/>
+      <c r="I350" s="15" t="n"/>
+      <c r="J350" s="15" t="n"/>
+      <c r="K350" s="15" t="n"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="13" t="n"/>
+      <c r="B351" s="14" t="n"/>
+      <c r="C351" s="14" t="n"/>
+      <c r="D351" s="15" t="n"/>
+      <c r="E351" s="15" t="n"/>
+      <c r="F351" s="15" t="n"/>
+      <c r="G351" s="15" t="n"/>
+      <c r="H351" s="15" t="n"/>
+      <c r="I351" s="15" t="n"/>
+      <c r="J351" s="15" t="n"/>
+      <c r="K351" s="15" t="n"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="13" t="n"/>
+      <c r="B352" s="14" t="n"/>
+      <c r="C352" s="14" t="n"/>
+      <c r="D352" s="15" t="n"/>
+      <c r="E352" s="15" t="n"/>
+      <c r="F352" s="15" t="n"/>
+      <c r="G352" s="15" t="n"/>
+      <c r="H352" s="15" t="n"/>
+      <c r="I352" s="15" t="n"/>
+      <c r="J352" s="15" t="n"/>
+      <c r="K352" s="15" t="n"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="13" t="n"/>
+      <c r="B353" s="14" t="n"/>
+      <c r="C353" s="14" t="n"/>
+      <c r="D353" s="15" t="n"/>
+      <c r="E353" s="15" t="n"/>
+      <c r="F353" s="15" t="n"/>
+      <c r="G353" s="15" t="n"/>
+      <c r="H353" s="15" t="n"/>
+      <c r="I353" s="15" t="n"/>
+      <c r="J353" s="15" t="n"/>
+      <c r="K353" s="15" t="n"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="13" t="n"/>
+      <c r="B354" s="14" t="n"/>
+      <c r="C354" s="14" t="n"/>
+      <c r="D354" s="15" t="n"/>
+      <c r="E354" s="15" t="n"/>
+      <c r="F354" s="15" t="n"/>
+      <c r="G354" s="15" t="n"/>
+      <c r="H354" s="15" t="n"/>
+      <c r="I354" s="15" t="n"/>
+      <c r="J354" s="15" t="n"/>
+      <c r="K354" s="15" t="n"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="13" t="n"/>
+      <c r="B355" s="14" t="n"/>
+      <c r="C355" s="14" t="n"/>
+      <c r="D355" s="15" t="n"/>
+      <c r="E355" s="15" t="n"/>
+      <c r="F355" s="15" t="n"/>
+      <c r="G355" s="15" t="n"/>
+      <c r="H355" s="15" t="n"/>
+      <c r="I355" s="15" t="n"/>
+      <c r="J355" s="15" t="n"/>
+      <c r="K355" s="15" t="n"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="13" t="n"/>
+      <c r="B356" s="14" t="n"/>
+      <c r="C356" s="14" t="n"/>
+      <c r="D356" s="15" t="n"/>
+      <c r="E356" s="15" t="n"/>
+      <c r="F356" s="15" t="n"/>
+      <c r="G356" s="15" t="n"/>
+      <c r="H356" s="15" t="n"/>
+      <c r="I356" s="15" t="n"/>
+      <c r="J356" s="15" t="n"/>
+      <c r="K356" s="15" t="n"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="13" t="n"/>
+      <c r="B357" s="14" t="n"/>
+      <c r="C357" s="14" t="n"/>
+      <c r="D357" s="15" t="n"/>
+      <c r="E357" s="15" t="n"/>
+      <c r="F357" s="15" t="n"/>
+      <c r="G357" s="15" t="n"/>
+      <c r="H357" s="15" t="n"/>
+      <c r="I357" s="15" t="n"/>
+      <c r="J357" s="15" t="n"/>
+      <c r="K357" s="15" t="n"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="13" t="n"/>
+      <c r="B358" s="14" t="n"/>
+      <c r="C358" s="14" t="n"/>
+      <c r="D358" s="15" t="n"/>
+      <c r="E358" s="15" t="n"/>
+      <c r="F358" s="15" t="n"/>
+      <c r="G358" s="15" t="n"/>
+      <c r="H358" s="15" t="n"/>
+      <c r="I358" s="15" t="n"/>
+      <c r="J358" s="15" t="n"/>
+      <c r="K358" s="15" t="n"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="13" t="n"/>
+      <c r="B359" s="14" t="n"/>
+      <c r="C359" s="14" t="n"/>
+      <c r="D359" s="15" t="n"/>
+      <c r="E359" s="15" t="n"/>
+      <c r="F359" s="15" t="n"/>
+      <c r="G359" s="15" t="n"/>
+      <c r="H359" s="15" t="n"/>
+      <c r="I359" s="15" t="n"/>
+      <c r="J359" s="15" t="n"/>
+      <c r="K359" s="15" t="n"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="13" t="n"/>
+      <c r="B360" s="14" t="n"/>
+      <c r="C360" s="14" t="n"/>
+      <c r="D360" s="15" t="n"/>
+      <c r="E360" s="15" t="n"/>
+      <c r="F360" s="15" t="n"/>
+      <c r="G360" s="15" t="n"/>
+      <c r="H360" s="15" t="n"/>
+      <c r="I360" s="15" t="n"/>
+      <c r="J360" s="15" t="n"/>
+      <c r="K360" s="15" t="n"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="13" t="n"/>
+      <c r="B361" s="14" t="n"/>
+      <c r="C361" s="14" t="n"/>
+      <c r="D361" s="15" t="n"/>
+      <c r="E361" s="15" t="n"/>
+      <c r="F361" s="15" t="n"/>
+      <c r="G361" s="15" t="n"/>
+      <c r="H361" s="15" t="n"/>
+      <c r="I361" s="15" t="n"/>
+      <c r="J361" s="15" t="n"/>
+      <c r="K361" s="15" t="n"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="13" t="n"/>
+      <c r="B362" s="14" t="n"/>
+      <c r="C362" s="14" t="n"/>
+      <c r="D362" s="15" t="n"/>
+      <c r="E362" s="15" t="n"/>
+      <c r="F362" s="15" t="n"/>
+      <c r="G362" s="15" t="n"/>
+      <c r="H362" s="15" t="n"/>
+      <c r="I362" s="15" t="n"/>
+      <c r="J362" s="15" t="n"/>
+      <c r="K362" s="15" t="n"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="13" t="n"/>
+      <c r="B363" s="14" t="n"/>
+      <c r="C363" s="14" t="n"/>
+      <c r="D363" s="15" t="n"/>
+      <c r="E363" s="15" t="n"/>
+      <c r="F363" s="15" t="n"/>
+      <c r="G363" s="15" t="n"/>
+      <c r="H363" s="15" t="n"/>
+      <c r="I363" s="15" t="n"/>
+      <c r="J363" s="15" t="n"/>
+      <c r="K363" s="15" t="n"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="13" t="n"/>
+      <c r="B364" s="14" t="n"/>
+      <c r="C364" s="14" t="n"/>
+      <c r="D364" s="15" t="n"/>
+      <c r="E364" s="15" t="n"/>
+      <c r="F364" s="15" t="n"/>
+      <c r="G364" s="15" t="n"/>
+      <c r="H364" s="15" t="n"/>
+      <c r="I364" s="15" t="n"/>
+      <c r="J364" s="15" t="n"/>
+      <c r="K364" s="15" t="n"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="13" t="n"/>
+      <c r="B365" s="14" t="n"/>
+      <c r="C365" s="14" t="n"/>
+      <c r="D365" s="15" t="n"/>
+      <c r="E365" s="15" t="n"/>
+      <c r="F365" s="15" t="n"/>
+      <c r="G365" s="15" t="n"/>
+      <c r="H365" s="15" t="n"/>
+      <c r="I365" s="15" t="n"/>
+      <c r="J365" s="15" t="n"/>
+      <c r="K365" s="15" t="n"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="13" t="n"/>
+      <c r="B366" s="14" t="n"/>
+      <c r="C366" s="14" t="n"/>
+      <c r="D366" s="15" t="n"/>
+      <c r="E366" s="15" t="n"/>
+      <c r="F366" s="15" t="n"/>
+      <c r="G366" s="15" t="n"/>
+      <c r="H366" s="15" t="n"/>
+      <c r="I366" s="15" t="n"/>
+      <c r="J366" s="15" t="n"/>
+      <c r="K366" s="15" t="n"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="13" t="n"/>
+      <c r="B367" s="14" t="n"/>
+      <c r="C367" s="14" t="n"/>
+      <c r="D367" s="15" t="n"/>
+      <c r="E367" s="15" t="n"/>
+      <c r="F367" s="15" t="n"/>
+      <c r="G367" s="15" t="n"/>
+      <c r="H367" s="15" t="n"/>
+      <c r="I367" s="15" t="n"/>
+      <c r="J367" s="15" t="n"/>
+      <c r="K367" s="15" t="n"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="13" t="n"/>
+      <c r="B368" s="14" t="n"/>
+      <c r="C368" s="14" t="n"/>
+      <c r="D368" s="15" t="n"/>
+      <c r="E368" s="15" t="n"/>
+      <c r="F368" s="15" t="n"/>
+      <c r="G368" s="15" t="n"/>
+      <c r="H368" s="15" t="n"/>
+      <c r="I368" s="15" t="n"/>
+      <c r="J368" s="15" t="n"/>
+      <c r="K368" s="15" t="n"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="13" t="n"/>
+      <c r="B369" s="14" t="n"/>
+      <c r="C369" s="14" t="n"/>
+      <c r="D369" s="15" t="n"/>
+      <c r="E369" s="15" t="n"/>
+      <c r="F369" s="15" t="n"/>
+      <c r="G369" s="15" t="n"/>
+      <c r="H369" s="15" t="n"/>
+      <c r="I369" s="15" t="n"/>
+      <c r="J369" s="15" t="n"/>
+      <c r="K369" s="15" t="n"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="13" t="n"/>
+      <c r="B370" s="14" t="n"/>
+      <c r="C370" s="14" t="n"/>
+      <c r="D370" s="15" t="n"/>
+      <c r="E370" s="15" t="n"/>
+      <c r="F370" s="15" t="n"/>
+      <c r="G370" s="15" t="n"/>
+      <c r="H370" s="15" t="n"/>
+      <c r="I370" s="15" t="n"/>
+      <c r="J370" s="15" t="n"/>
+      <c r="K370" s="15" t="n"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="13" t="n"/>
+      <c r="B371" s="14" t="n"/>
+      <c r="C371" s="14" t="n"/>
+      <c r="D371" s="15" t="n"/>
+      <c r="E371" s="15" t="n"/>
+      <c r="F371" s="15" t="n"/>
+      <c r="G371" s="15" t="n"/>
+      <c r="H371" s="15" t="n"/>
+      <c r="I371" s="15" t="n"/>
+      <c r="J371" s="15" t="n"/>
+      <c r="K371" s="15" t="n"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="13" t="n"/>
+      <c r="B372" s="14" t="n"/>
+      <c r="C372" s="14" t="n"/>
+      <c r="D372" s="15" t="n"/>
+      <c r="E372" s="15" t="n"/>
+      <c r="F372" s="15" t="n"/>
+      <c r="G372" s="15" t="n"/>
+      <c r="H372" s="15" t="n"/>
+      <c r="I372" s="15" t="n"/>
+      <c r="J372" s="15" t="n"/>
+      <c r="K372" s="15" t="n"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="13" t="n"/>
+      <c r="B373" s="14" t="n"/>
+      <c r="C373" s="14" t="n"/>
+      <c r="D373" s="15" t="n"/>
+      <c r="E373" s="15" t="n"/>
+      <c r="F373" s="15" t="n"/>
+      <c r="G373" s="15" t="n"/>
+      <c r="H373" s="15" t="n"/>
+      <c r="I373" s="15" t="n"/>
+      <c r="J373" s="15" t="n"/>
+      <c r="K373" s="15" t="n"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="13" t="n"/>
+      <c r="B374" s="14" t="n"/>
+      <c r="C374" s="14" t="n"/>
+      <c r="D374" s="15" t="n"/>
+      <c r="E374" s="15" t="n"/>
+      <c r="F374" s="15" t="n"/>
+      <c r="G374" s="15" t="n"/>
+      <c r="H374" s="15" t="n"/>
+      <c r="I374" s="15" t="n"/>
+      <c r="J374" s="15" t="n"/>
+      <c r="K374" s="15" t="n"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="13" t="n"/>
+      <c r="B375" s="14" t="n"/>
+      <c r="C375" s="14" t="n"/>
+      <c r="D375" s="15" t="n"/>
+      <c r="E375" s="15" t="n"/>
+      <c r="F375" s="15" t="n"/>
+      <c r="G375" s="15" t="n"/>
+      <c r="H375" s="15" t="n"/>
+      <c r="I375" s="15" t="n"/>
+      <c r="J375" s="15" t="n"/>
+      <c r="K375" s="15" t="n"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="13" t="n"/>
+      <c r="B376" s="14" t="n"/>
+      <c r="C376" s="14" t="n"/>
+      <c r="D376" s="15" t="n"/>
+      <c r="E376" s="15" t="n"/>
+      <c r="F376" s="15" t="n"/>
+      <c r="G376" s="15" t="n"/>
+      <c r="H376" s="15" t="n"/>
+      <c r="I376" s="15" t="n"/>
+      <c r="J376" s="15" t="n"/>
+      <c r="K376" s="15" t="n"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="13" t="n"/>
+      <c r="B377" s="14" t="n"/>
+      <c r="C377" s="14" t="n"/>
+      <c r="D377" s="15" t="n"/>
+      <c r="E377" s="15" t="n"/>
+      <c r="F377" s="15" t="n"/>
+      <c r="G377" s="15" t="n"/>
+      <c r="H377" s="15" t="n"/>
+      <c r="I377" s="15" t="n"/>
+      <c r="J377" s="15" t="n"/>
+      <c r="K377" s="15" t="n"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="13" t="n"/>
+      <c r="B378" s="14" t="n"/>
+      <c r="C378" s="14" t="n"/>
+      <c r="D378" s="15" t="n"/>
+      <c r="E378" s="15" t="n"/>
+      <c r="F378" s="15" t="n"/>
+      <c r="G378" s="15" t="n"/>
+      <c r="H378" s="15" t="n"/>
+      <c r="I378" s="15" t="n"/>
+      <c r="J378" s="15" t="n"/>
+      <c r="K378" s="15" t="n"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="13" t="n"/>
+      <c r="B379" s="14" t="n"/>
+      <c r="C379" s="14" t="n"/>
+      <c r="D379" s="15" t="n"/>
+      <c r="E379" s="15" t="n"/>
+      <c r="F379" s="15" t="n"/>
+      <c r="G379" s="15" t="n"/>
+      <c r="H379" s="15" t="n"/>
+      <c r="I379" s="15" t="n"/>
+      <c r="J379" s="15" t="n"/>
+      <c r="K379" s="15" t="n"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="13" t="n"/>
+      <c r="B380" s="14" t="n"/>
+      <c r="C380" s="14" t="n"/>
+      <c r="D380" s="15" t="n"/>
+      <c r="E380" s="15" t="n"/>
+      <c r="F380" s="15" t="n"/>
+      <c r="G380" s="15" t="n"/>
+      <c r="H380" s="15" t="n"/>
+      <c r="I380" s="15" t="n"/>
+      <c r="J380" s="15" t="n"/>
+      <c r="K380" s="15" t="n"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="13" t="n"/>
+      <c r="B381" s="14" t="n"/>
+      <c r="C381" s="14" t="n"/>
+      <c r="D381" s="15" t="n"/>
+      <c r="E381" s="15" t="n"/>
+      <c r="F381" s="15" t="n"/>
+      <c r="G381" s="15" t="n"/>
+      <c r="H381" s="15" t="n"/>
+      <c r="I381" s="15" t="n"/>
+      <c r="J381" s="15" t="n"/>
+      <c r="K381" s="15" t="n"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="13" t="n"/>
+      <c r="B382" s="14" t="n"/>
+      <c r="C382" s="14" t="n"/>
+      <c r="D382" s="15" t="n"/>
+      <c r="E382" s="15" t="n"/>
+      <c r="F382" s="15" t="n"/>
+      <c r="G382" s="15" t="n"/>
+      <c r="H382" s="15" t="n"/>
+      <c r="I382" s="15" t="n"/>
+      <c r="J382" s="15" t="n"/>
+      <c r="K382" s="15" t="n"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="13" t="n"/>
+      <c r="B383" s="14" t="n"/>
+      <c r="C383" s="14" t="n"/>
+      <c r="D383" s="15" t="n"/>
+      <c r="E383" s="15" t="n"/>
+      <c r="F383" s="15" t="n"/>
+      <c r="G383" s="15" t="n"/>
+      <c r="H383" s="15" t="n"/>
+      <c r="I383" s="15" t="n"/>
+      <c r="J383" s="15" t="n"/>
+      <c r="K383" s="15" t="n"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="13" t="n"/>
+      <c r="B384" s="14" t="n"/>
+      <c r="C384" s="14" t="n"/>
+      <c r="D384" s="15" t="n"/>
+      <c r="E384" s="15" t="n"/>
+      <c r="F384" s="15" t="n"/>
+      <c r="G384" s="15" t="n"/>
+      <c r="H384" s="15" t="n"/>
+      <c r="I384" s="15" t="n"/>
+      <c r="J384" s="15" t="n"/>
+      <c r="K384" s="15" t="n"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="13" t="n"/>
+      <c r="B385" s="14" t="n"/>
+      <c r="C385" s="14" t="n"/>
+      <c r="D385" s="15" t="n"/>
+      <c r="E385" s="15" t="n"/>
+      <c r="F385" s="15" t="n"/>
+      <c r="G385" s="15" t="n"/>
+      <c r="H385" s="15" t="n"/>
+      <c r="I385" s="15" t="n"/>
+      <c r="J385" s="15" t="n"/>
+      <c r="K385" s="15" t="n"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="13" t="n"/>
+      <c r="B386" s="14" t="n"/>
+      <c r="C386" s="14" t="n"/>
+      <c r="D386" s="15" t="n"/>
+      <c r="E386" s="15" t="n"/>
+      <c r="F386" s="15" t="n"/>
+      <c r="G386" s="15" t="n"/>
+      <c r="H386" s="15" t="n"/>
+      <c r="I386" s="15" t="n"/>
+      <c r="J386" s="15" t="n"/>
+      <c r="K386" s="15" t="n"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="13" t="n"/>
+      <c r="B387" s="14" t="n"/>
+      <c r="C387" s="14" t="n"/>
+      <c r="D387" s="15" t="n"/>
+      <c r="E387" s="15" t="n"/>
+      <c r="F387" s="15" t="n"/>
+      <c r="G387" s="15" t="n"/>
+      <c r="H387" s="15" t="n"/>
+      <c r="I387" s="15" t="n"/>
+      <c r="J387" s="15" t="n"/>
+      <c r="K387" s="15" t="n"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="13" t="n"/>
+      <c r="B388" s="14" t="n"/>
+      <c r="C388" s="14" t="n"/>
+      <c r="D388" s="15" t="n"/>
+      <c r="E388" s="15" t="n"/>
+      <c r="F388" s="15" t="n"/>
+      <c r="G388" s="15" t="n"/>
+      <c r="H388" s="15" t="n"/>
+      <c r="I388" s="15" t="n"/>
+      <c r="J388" s="15" t="n"/>
+      <c r="K388" s="15" t="n"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="13" t="n"/>
+      <c r="B389" s="14" t="n"/>
+      <c r="C389" s="14" t="n"/>
+      <c r="D389" s="15" t="n"/>
+      <c r="E389" s="15" t="n"/>
+      <c r="F389" s="15" t="n"/>
+      <c r="G389" s="15" t="n"/>
+      <c r="H389" s="15" t="n"/>
+      <c r="I389" s="15" t="n"/>
+      <c r="J389" s="15" t="n"/>
+      <c r="K389" s="15" t="n"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="13" t="n"/>
+      <c r="B390" s="14" t="n"/>
+      <c r="C390" s="14" t="n"/>
+      <c r="D390" s="15" t="n"/>
+      <c r="E390" s="15" t="n"/>
+      <c r="F390" s="15" t="n"/>
+      <c r="G390" s="15" t="n"/>
+      <c r="H390" s="15" t="n"/>
+      <c r="I390" s="15" t="n"/>
+      <c r="J390" s="15" t="n"/>
+      <c r="K390" s="15" t="n"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="13" t="n"/>
+      <c r="B391" s="14" t="n"/>
+      <c r="C391" s="14" t="n"/>
+      <c r="D391" s="15" t="n"/>
+      <c r="E391" s="15" t="n"/>
+      <c r="F391" s="15" t="n"/>
+      <c r="G391" s="15" t="n"/>
+      <c r="H391" s="15" t="n"/>
+      <c r="I391" s="15" t="n"/>
+      <c r="J391" s="15" t="n"/>
+      <c r="K391" s="15" t="n"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="13" t="n"/>
+      <c r="B392" s="14" t="n"/>
+      <c r="C392" s="14" t="n"/>
+      <c r="D392" s="15" t="n"/>
+      <c r="E392" s="15" t="n"/>
+      <c r="F392" s="15" t="n"/>
+      <c r="G392" s="15" t="n"/>
+      <c r="H392" s="15" t="n"/>
+      <c r="I392" s="15" t="n"/>
+      <c r="J392" s="15" t="n"/>
+      <c r="K392" s="15" t="n"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="13" t="n"/>
+      <c r="B393" s="14" t="n"/>
+      <c r="C393" s="14" t="n"/>
+      <c r="D393" s="15" t="n"/>
+      <c r="E393" s="15" t="n"/>
+      <c r="F393" s="15" t="n"/>
+      <c r="G393" s="15" t="n"/>
+      <c r="H393" s="15" t="n"/>
+      <c r="I393" s="15" t="n"/>
+      <c r="J393" s="15" t="n"/>
+      <c r="K393" s="15" t="n"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="13" t="n"/>
+      <c r="B394" s="14" t="n"/>
+      <c r="C394" s="14" t="n"/>
+      <c r="D394" s="15" t="n"/>
+      <c r="E394" s="15" t="n"/>
+      <c r="F394" s="15" t="n"/>
+      <c r="G394" s="15" t="n"/>
+      <c r="H394" s="15" t="n"/>
+      <c r="I394" s="15" t="n"/>
+      <c r="J394" s="15" t="n"/>
+      <c r="K394" s="15" t="n"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="13" t="n"/>
+      <c r="B395" s="14" t="n"/>
+      <c r="C395" s="14" t="n"/>
+      <c r="D395" s="15" t="n"/>
+      <c r="E395" s="15" t="n"/>
+      <c r="F395" s="15" t="n"/>
+      <c r="G395" s="15" t="n"/>
+      <c r="H395" s="15" t="n"/>
+      <c r="I395" s="15" t="n"/>
+      <c r="J395" s="15" t="n"/>
+      <c r="K395" s="15" t="n"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="13" t="n"/>
+      <c r="B396" s="14" t="n"/>
+      <c r="C396" s="14" t="n"/>
+      <c r="D396" s="15" t="n"/>
+      <c r="E396" s="15" t="n"/>
+      <c r="F396" s="15" t="n"/>
+      <c r="G396" s="15" t="n"/>
+      <c r="H396" s="15" t="n"/>
+      <c r="I396" s="15" t="n"/>
+      <c r="J396" s="15" t="n"/>
+      <c r="K396" s="15" t="n"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="13" t="n"/>
+      <c r="B397" s="14" t="n"/>
+      <c r="C397" s="14" t="n"/>
+      <c r="D397" s="15" t="n"/>
+      <c r="E397" s="15" t="n"/>
+      <c r="F397" s="15" t="n"/>
+      <c r="G397" s="15" t="n"/>
+      <c r="H397" s="15" t="n"/>
+      <c r="I397" s="15" t="n"/>
+      <c r="J397" s="15" t="n"/>
+      <c r="K397" s="15" t="n"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="13" t="n"/>
+      <c r="B398" s="14" t="n"/>
+      <c r="C398" s="14" t="n"/>
+      <c r="D398" s="15" t="n"/>
+      <c r="E398" s="15" t="n"/>
+      <c r="F398" s="15" t="n"/>
+      <c r="G398" s="15" t="n"/>
+      <c r="H398" s="15" t="n"/>
+      <c r="I398" s="15" t="n"/>
+      <c r="J398" s="15" t="n"/>
+      <c r="K398" s="15" t="n"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="13" t="n"/>
+      <c r="B399" s="14" t="n"/>
+      <c r="C399" s="14" t="n"/>
+      <c r="D399" s="15" t="n"/>
+      <c r="E399" s="15" t="n"/>
+      <c r="F399" s="15" t="n"/>
+      <c r="G399" s="15" t="n"/>
+      <c r="H399" s="15" t="n"/>
+      <c r="I399" s="15" t="n"/>
+      <c r="J399" s="15" t="n"/>
+      <c r="K399" s="15" t="n"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="13" t="n"/>
+      <c r="B400" s="14" t="n"/>
+      <c r="C400" s="14" t="n"/>
+      <c r="D400" s="15" t="n"/>
+      <c r="E400" s="15" t="n"/>
+      <c r="F400" s="15" t="n"/>
+      <c r="G400" s="15" t="n"/>
+      <c r="H400" s="15" t="n"/>
+      <c r="I400" s="15" t="n"/>
+      <c r="J400" s="15" t="n"/>
+      <c r="K400" s="15" t="n"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="13" t="n"/>
+      <c r="B401" s="14" t="n"/>
+      <c r="C401" s="14" t="n"/>
+      <c r="D401" s="15" t="n"/>
+      <c r="E401" s="15" t="n"/>
+      <c r="F401" s="15" t="n"/>
+      <c r="G401" s="15" t="n"/>
+      <c r="H401" s="15" t="n"/>
+      <c r="I401" s="15" t="n"/>
+      <c r="J401" s="15" t="n"/>
+      <c r="K401" s="15" t="n"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="13" t="n"/>
+      <c r="B402" s="14" t="n"/>
+      <c r="C402" s="14" t="n"/>
+      <c r="D402" s="15" t="n"/>
+      <c r="E402" s="15" t="n"/>
+      <c r="F402" s="15" t="n"/>
+      <c r="G402" s="15" t="n"/>
+      <c r="H402" s="15" t="n"/>
+      <c r="I402" s="15" t="n"/>
+      <c r="J402" s="15" t="n"/>
+      <c r="K402" s="15" t="n"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="13" t="n"/>
+      <c r="B403" s="14" t="n"/>
+      <c r="C403" s="14" t="n"/>
+      <c r="D403" s="15" t="n"/>
+      <c r="E403" s="15" t="n"/>
+      <c r="F403" s="15" t="n"/>
+      <c r="G403" s="15" t="n"/>
+      <c r="H403" s="15" t="n"/>
+      <c r="I403" s="15" t="n"/>
+      <c r="J403" s="15" t="n"/>
+      <c r="K403" s="15" t="n"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="13" t="n"/>
+      <c r="B404" s="14" t="n"/>
+      <c r="C404" s="14" t="n"/>
+      <c r="D404" s="15" t="n"/>
+      <c r="E404" s="15" t="n"/>
+      <c r="F404" s="15" t="n"/>
+      <c r="G404" s="15" t="n"/>
+      <c r="H404" s="15" t="n"/>
+      <c r="I404" s="15" t="n"/>
+      <c r="J404" s="15" t="n"/>
+      <c r="K404" s="15" t="n"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="13" t="n"/>
+      <c r="B405" s="14" t="n"/>
+      <c r="C405" s="14" t="n"/>
+      <c r="D405" s="15" t="n"/>
+      <c r="E405" s="15" t="n"/>
+      <c r="F405" s="15" t="n"/>
+      <c r="G405" s="15" t="n"/>
+      <c r="H405" s="15" t="n"/>
+      <c r="I405" s="15" t="n"/>
+      <c r="J405" s="15" t="n"/>
+      <c r="K405" s="15" t="n"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="13" t="n"/>
+      <c r="B406" s="14" t="n"/>
+      <c r="C406" s="14" t="n"/>
+      <c r="D406" s="15" t="n"/>
+      <c r="E406" s="15" t="n"/>
+      <c r="F406" s="15" t="n"/>
+      <c r="G406" s="15" t="n"/>
+      <c r="H406" s="15" t="n"/>
+      <c r="I406" s="15" t="n"/>
+      <c r="J406" s="15" t="n"/>
+      <c r="K406" s="15" t="n"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="13" t="n"/>
+      <c r="B407" s="14" t="n"/>
+      <c r="C407" s="14" t="n"/>
+      <c r="D407" s="15" t="n"/>
+      <c r="E407" s="15" t="n"/>
+      <c r="F407" s="15" t="n"/>
+      <c r="G407" s="15" t="n"/>
+      <c r="H407" s="15" t="n"/>
+      <c r="I407" s="15" t="n"/>
+      <c r="J407" s="15" t="n"/>
+      <c r="K407" s="15" t="n"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="13" t="n"/>
+      <c r="B408" s="14" t="n"/>
+      <c r="C408" s="14" t="n"/>
+      <c r="D408" s="15" t="n"/>
+      <c r="E408" s="15" t="n"/>
+      <c r="F408" s="15" t="n"/>
+      <c r="G408" s="15" t="n"/>
+      <c r="H408" s="15" t="n"/>
+      <c r="I408" s="15" t="n"/>
+      <c r="J408" s="15" t="n"/>
+      <c r="K408" s="15" t="n"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="13" t="n"/>
+      <c r="B409" s="14" t="n"/>
+      <c r="C409" s="14" t="n"/>
+      <c r="D409" s="15" t="n"/>
+      <c r="E409" s="15" t="n"/>
+      <c r="F409" s="15" t="n"/>
+      <c r="G409" s="15" t="n"/>
+      <c r="H409" s="15" t="n"/>
+      <c r="I409" s="15" t="n"/>
+      <c r="J409" s="15" t="n"/>
+      <c r="K409" s="15" t="n"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="13" t="n"/>
+      <c r="B410" s="14" t="n"/>
+      <c r="C410" s="14" t="n"/>
+      <c r="D410" s="15" t="n"/>
+      <c r="E410" s="15" t="n"/>
+      <c r="F410" s="15" t="n"/>
+      <c r="G410" s="15" t="n"/>
+      <c r="H410" s="15" t="n"/>
+      <c r="I410" s="15" t="n"/>
+      <c r="J410" s="15" t="n"/>
+      <c r="K410" s="15" t="n"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="13" t="n"/>
+      <c r="B411" s="14" t="n"/>
+      <c r="C411" s="14" t="n"/>
+      <c r="D411" s="15" t="n"/>
+      <c r="E411" s="15" t="n"/>
+      <c r="F411" s="15" t="n"/>
+      <c r="G411" s="15" t="n"/>
+      <c r="H411" s="15" t="n"/>
+      <c r="I411" s="15" t="n"/>
+      <c r="J411" s="15" t="n"/>
+      <c r="K411" s="15" t="n"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="13" t="n"/>
+      <c r="B412" s="14" t="n"/>
+      <c r="C412" s="14" t="n"/>
+      <c r="D412" s="15" t="n"/>
+      <c r="E412" s="15" t="n"/>
+      <c r="F412" s="15" t="n"/>
+      <c r="G412" s="15" t="n"/>
+      <c r="H412" s="15" t="n"/>
+      <c r="I412" s="15" t="n"/>
+      <c r="J412" s="15" t="n"/>
+      <c r="K412" s="15" t="n"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="13" t="n"/>
+      <c r="B413" s="14" t="n"/>
+      <c r="C413" s="14" t="n"/>
+      <c r="D413" s="15" t="n"/>
+      <c r="E413" s="15" t="n"/>
+      <c r="F413" s="15" t="n"/>
+      <c r="G413" s="15" t="n"/>
+      <c r="H413" s="15" t="n"/>
+      <c r="I413" s="15" t="n"/>
+      <c r="J413" s="15" t="n"/>
+      <c r="K413" s="15" t="n"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="13" t="n"/>
+      <c r="B414" s="14" t="n"/>
+      <c r="C414" s="14" t="n"/>
+      <c r="D414" s="15" t="n"/>
+      <c r="E414" s="15" t="n"/>
+      <c r="F414" s="15" t="n"/>
+      <c r="G414" s="15" t="n"/>
+      <c r="H414" s="15" t="n"/>
+      <c r="I414" s="15" t="n"/>
+      <c r="J414" s="15" t="n"/>
+      <c r="K414" s="15" t="n"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="13" t="n"/>
+      <c r="B415" s="14" t="n"/>
+      <c r="C415" s="14" t="n"/>
+      <c r="D415" s="15" t="n"/>
+      <c r="E415" s="15" t="n"/>
+      <c r="F415" s="15" t="n"/>
+      <c r="G415" s="15" t="n"/>
+      <c r="H415" s="15" t="n"/>
+      <c r="I415" s="15" t="n"/>
+      <c r="J415" s="15" t="n"/>
+      <c r="K415" s="15" t="n"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="13" t="n"/>
+      <c r="B416" s="14" t="n"/>
+      <c r="C416" s="14" t="n"/>
+      <c r="D416" s="15" t="n"/>
+      <c r="E416" s="15" t="n"/>
+      <c r="F416" s="15" t="n"/>
+      <c r="G416" s="15" t="n"/>
+      <c r="H416" s="15" t="n"/>
+      <c r="I416" s="15" t="n"/>
+      <c r="J416" s="15" t="n"/>
+      <c r="K416" s="15" t="n"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="13" t="n"/>
+      <c r="B417" s="14" t="n"/>
+      <c r="C417" s="14" t="n"/>
+      <c r="D417" s="15" t="n"/>
+      <c r="E417" s="15" t="n"/>
+      <c r="F417" s="15" t="n"/>
+      <c r="G417" s="15" t="n"/>
+      <c r="H417" s="15" t="n"/>
+      <c r="I417" s="15" t="n"/>
+      <c r="J417" s="15" t="n"/>
+      <c r="K417" s="15" t="n"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="13" t="n"/>
+      <c r="B418" s="14" t="n"/>
+      <c r="C418" s="14" t="n"/>
+      <c r="D418" s="15" t="n"/>
+      <c r="E418" s="15" t="n"/>
+      <c r="F418" s="15" t="n"/>
+      <c r="G418" s="15" t="n"/>
+      <c r="H418" s="15" t="n"/>
+      <c r="I418" s="15" t="n"/>
+      <c r="J418" s="15" t="n"/>
+      <c r="K418" s="15" t="n"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="13" t="n"/>
+      <c r="B419" s="14" t="n"/>
+      <c r="C419" s="14" t="n"/>
+      <c r="D419" s="15" t="n"/>
+      <c r="E419" s="15" t="n"/>
+      <c r="F419" s="15" t="n"/>
+      <c r="G419" s="15" t="n"/>
+      <c r="H419" s="15" t="n"/>
+      <c r="I419" s="15" t="n"/>
+      <c r="J419" s="15" t="n"/>
+      <c r="K419" s="15" t="n"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="13" t="n"/>
+      <c r="B420" s="14" t="n"/>
+      <c r="C420" s="14" t="n"/>
+      <c r="D420" s="15" t="n"/>
+      <c r="E420" s="15" t="n"/>
+      <c r="F420" s="15" t="n"/>
+      <c r="G420" s="15" t="n"/>
+      <c r="H420" s="15" t="n"/>
+      <c r="I420" s="15" t="n"/>
+      <c r="J420" s="15" t="n"/>
+      <c r="K420" s="15" t="n"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="13" t="n"/>
+      <c r="B421" s="14" t="n"/>
+      <c r="C421" s="14" t="n"/>
+      <c r="D421" s="15" t="n"/>
+      <c r="E421" s="15" t="n"/>
+      <c r="F421" s="15" t="n"/>
+      <c r="G421" s="15" t="n"/>
+      <c r="H421" s="15" t="n"/>
+      <c r="I421" s="15" t="n"/>
+      <c r="J421" s="15" t="n"/>
+      <c r="K421" s="15" t="n"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="13" t="n"/>
+      <c r="B422" s="14" t="n"/>
+      <c r="C422" s="14" t="n"/>
+      <c r="D422" s="15" t="n"/>
+      <c r="E422" s="15" t="n"/>
+      <c r="F422" s="15" t="n"/>
+      <c r="G422" s="15" t="n"/>
+      <c r="H422" s="15" t="n"/>
+      <c r="I422" s="15" t="n"/>
+      <c r="J422" s="15" t="n"/>
+      <c r="K422" s="15" t="n"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="13" t="n"/>
+      <c r="B423" s="14" t="n"/>
+      <c r="C423" s="14" t="n"/>
+      <c r="D423" s="15" t="n"/>
+      <c r="E423" s="15" t="n"/>
+      <c r="F423" s="15" t="n"/>
+      <c r="G423" s="15" t="n"/>
+      <c r="H423" s="15" t="n"/>
+      <c r="I423" s="15" t="n"/>
+      <c r="J423" s="15" t="n"/>
+      <c r="K423" s="15" t="n"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="13" t="n"/>
+      <c r="B424" s="14" t="n"/>
+      <c r="C424" s="14" t="n"/>
+      <c r="D424" s="15" t="n"/>
+      <c r="E424" s="15" t="n"/>
+      <c r="F424" s="15" t="n"/>
+      <c r="G424" s="15" t="n"/>
+      <c r="H424" s="15" t="n"/>
+      <c r="I424" s="15" t="n"/>
+      <c r="J424" s="15" t="n"/>
+      <c r="K424" s="15" t="n"/>
+    </row>
+    <row r="425">
+      <c r="A425" s="13" t="n"/>
+      <c r="B425" s="14" t="n"/>
+      <c r="C425" s="14" t="n"/>
+      <c r="D425" s="15" t="n"/>
+      <c r="E425" s="15" t="n"/>
+      <c r="F425" s="15" t="n"/>
+      <c r="G425" s="15" t="n"/>
+      <c r="H425" s="15" t="n"/>
+      <c r="I425" s="15" t="n"/>
+      <c r="J425" s="15" t="n"/>
+      <c r="K425" s="15" t="n"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="13" t="n"/>
+      <c r="B426" s="14" t="n"/>
+      <c r="C426" s="14" t="n"/>
+      <c r="D426" s="15" t="n"/>
+      <c r="E426" s="15" t="n"/>
+      <c r="F426" s="15" t="n"/>
+      <c r="G426" s="15" t="n"/>
+      <c r="H426" s="15" t="n"/>
+      <c r="I426" s="15" t="n"/>
+      <c r="J426" s="15" t="n"/>
+      <c r="K426" s="15" t="n"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="13" t="n"/>
+      <c r="B427" s="14" t="n"/>
+      <c r="C427" s="14" t="n"/>
+      <c r="D427" s="15" t="n"/>
+      <c r="E427" s="15" t="n"/>
+      <c r="F427" s="15" t="n"/>
+      <c r="G427" s="15" t="n"/>
+      <c r="H427" s="15" t="n"/>
+      <c r="I427" s="15" t="n"/>
+      <c r="J427" s="15" t="n"/>
+      <c r="K427" s="15" t="n"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="13" t="n"/>
+      <c r="B428" s="14" t="n"/>
+      <c r="C428" s="14" t="n"/>
+      <c r="D428" s="15" t="n"/>
+      <c r="E428" s="15" t="n"/>
+      <c r="F428" s="15" t="n"/>
+      <c r="G428" s="15" t="n"/>
+      <c r="H428" s="15" t="n"/>
+      <c r="I428" s="15" t="n"/>
+      <c r="J428" s="15" t="n"/>
+      <c r="K428" s="15" t="n"/>
+    </row>
+    <row r="429">
+      <c r="A429" s="13" t="n"/>
+      <c r="B429" s="14" t="n"/>
+      <c r="C429" s="14" t="n"/>
+      <c r="D429" s="15" t="n"/>
+      <c r="E429" s="15" t="n"/>
+      <c r="F429" s="15" t="n"/>
+      <c r="G429" s="15" t="n"/>
+      <c r="H429" s="15" t="n"/>
+      <c r="I429" s="15" t="n"/>
+      <c r="J429" s="15" t="n"/>
+      <c r="K429" s="15" t="n"/>
+    </row>
+    <row r="430">
+      <c r="A430" s="13" t="n"/>
+      <c r="B430" s="14" t="n"/>
+      <c r="C430" s="14" t="n"/>
+      <c r="D430" s="15" t="n"/>
+      <c r="E430" s="15" t="n"/>
+      <c r="F430" s="15" t="n"/>
+      <c r="G430" s="15" t="n"/>
+      <c r="H430" s="15" t="n"/>
+      <c r="I430" s="15" t="n"/>
+      <c r="J430" s="15" t="n"/>
+      <c r="K430" s="15" t="n"/>
+    </row>
+    <row r="431">
+      <c r="A431" s="13" t="n"/>
+      <c r="B431" s="14" t="n"/>
+      <c r="C431" s="14" t="n"/>
+      <c r="D431" s="15" t="n"/>
+      <c r="E431" s="15" t="n"/>
+      <c r="F431" s="15" t="n"/>
+      <c r="G431" s="15" t="n"/>
+      <c r="H431" s="15" t="n"/>
+      <c r="I431" s="15" t="n"/>
+      <c r="J431" s="15" t="n"/>
+      <c r="K431" s="15" t="n"/>
+    </row>
+    <row r="432">
+      <c r="A432" s="13" t="n"/>
+      <c r="B432" s="14" t="n"/>
+      <c r="C432" s="14" t="n"/>
+      <c r="D432" s="15" t="n"/>
+      <c r="E432" s="15" t="n"/>
+      <c r="F432" s="15" t="n"/>
+      <c r="G432" s="15" t="n"/>
+      <c r="H432" s="15" t="n"/>
+      <c r="I432" s="15" t="n"/>
+      <c r="J432" s="15" t="n"/>
+      <c r="K432" s="15" t="n"/>
+    </row>
+    <row r="433">
+      <c r="A433" s="13" t="n"/>
+      <c r="B433" s="14" t="n"/>
+      <c r="C433" s="14" t="n"/>
+      <c r="D433" s="15" t="n"/>
+      <c r="E433" s="15" t="n"/>
+      <c r="F433" s="15" t="n"/>
+      <c r="G433" s="15" t="n"/>
+      <c r="H433" s="15" t="n"/>
+      <c r="I433" s="15" t="n"/>
+      <c r="J433" s="15" t="n"/>
+      <c r="K433" s="15" t="n"/>
+    </row>
+    <row r="434">
+      <c r="A434" s="13" t="n"/>
+      <c r="B434" s="14" t="n"/>
+      <c r="C434" s="14" t="n"/>
+      <c r="D434" s="15" t="n"/>
+      <c r="E434" s="15" t="n"/>
+      <c r="F434" s="15" t="n"/>
+      <c r="G434" s="15" t="n"/>
+      <c r="H434" s="15" t="n"/>
+      <c r="I434" s="15" t="n"/>
+      <c r="J434" s="15" t="n"/>
+      <c r="K434" s="15" t="n"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="13" t="n"/>
+      <c r="B435" s="14" t="n"/>
+      <c r="C435" s="14" t="n"/>
+      <c r="D435" s="15" t="n"/>
+      <c r="E435" s="15" t="n"/>
+      <c r="F435" s="15" t="n"/>
+      <c r="G435" s="15" t="n"/>
+      <c r="H435" s="15" t="n"/>
+      <c r="I435" s="15" t="n"/>
+      <c r="J435" s="15" t="n"/>
+      <c r="K435" s="15" t="n"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="13" t="n"/>
+      <c r="B436" s="14" t="n"/>
+      <c r="C436" s="14" t="n"/>
+      <c r="D436" s="15" t="n"/>
+      <c r="E436" s="15" t="n"/>
+      <c r="F436" s="15" t="n"/>
+      <c r="G436" s="15" t="n"/>
+      <c r="H436" s="15" t="n"/>
+      <c r="I436" s="15" t="n"/>
+      <c r="J436" s="15" t="n"/>
+      <c r="K436" s="15" t="n"/>
+    </row>
+    <row r="437">
+      <c r="A437" s="13" t="n"/>
+      <c r="B437" s="14" t="n"/>
+      <c r="C437" s="14" t="n"/>
+      <c r="D437" s="15" t="n"/>
+      <c r="E437" s="15" t="n"/>
+      <c r="F437" s="15" t="n"/>
+      <c r="G437" s="15" t="n"/>
+      <c r="H437" s="15" t="n"/>
+      <c r="I437" s="15" t="n"/>
+      <c r="J437" s="15" t="n"/>
+      <c r="K437" s="15" t="n"/>
+    </row>
+    <row r="438">
+      <c r="A438" s="13" t="n"/>
+      <c r="B438" s="14" t="n"/>
+      <c r="C438" s="14" t="n"/>
+      <c r="D438" s="15" t="n"/>
+      <c r="E438" s="15" t="n"/>
+      <c r="F438" s="15" t="n"/>
+      <c r="G438" s="15" t="n"/>
+      <c r="H438" s="15" t="n"/>
+      <c r="I438" s="15" t="n"/>
+      <c r="J438" s="15" t="n"/>
+      <c r="K438" s="15" t="n"/>
+    </row>
+    <row r="439">
+      <c r="A439" s="13" t="n"/>
+      <c r="B439" s="14" t="n"/>
+      <c r="C439" s="14" t="n"/>
+      <c r="D439" s="15" t="n"/>
+      <c r="E439" s="15" t="n"/>
+      <c r="F439" s="15" t="n"/>
+      <c r="G439" s="15" t="n"/>
+      <c r="H439" s="15" t="n"/>
+      <c r="I439" s="15" t="n"/>
+      <c r="J439" s="15" t="n"/>
+      <c r="K439" s="15" t="n"/>
+    </row>
+    <row r="440">
+      <c r="A440" s="13" t="n"/>
+      <c r="B440" s="14" t="n"/>
+      <c r="C440" s="14" t="n"/>
+      <c r="D440" s="15" t="n"/>
+      <c r="E440" s="15" t="n"/>
+      <c r="F440" s="15" t="n"/>
+      <c r="G440" s="15" t="n"/>
+      <c r="H440" s="15" t="n"/>
+      <c r="I440" s="15" t="n"/>
+      <c r="J440" s="15" t="n"/>
+      <c r="K440" s="15" t="n"/>
+    </row>
+    <row r="441">
+      <c r="A441" s="13" t="n"/>
+      <c r="B441" s="14" t="n"/>
+      <c r="C441" s="14" t="n"/>
+      <c r="D441" s="15" t="n"/>
+      <c r="E441" s="15" t="n"/>
+      <c r="F441" s="15" t="n"/>
+      <c r="G441" s="15" t="n"/>
+      <c r="H441" s="15" t="n"/>
+      <c r="I441" s="15" t="n"/>
+      <c r="J441" s="15" t="n"/>
+      <c r="K441" s="15" t="n"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="13" t="n"/>
+      <c r="B442" s="14" t="n"/>
+      <c r="C442" s="14" t="n"/>
+      <c r="D442" s="15" t="n"/>
+      <c r="E442" s="15" t="n"/>
+      <c r="F442" s="15" t="n"/>
+      <c r="G442" s="15" t="n"/>
+      <c r="H442" s="15" t="n"/>
+      <c r="I442" s="15" t="n"/>
+      <c r="J442" s="15" t="n"/>
+      <c r="K442" s="15" t="n"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="13" t="n"/>
+      <c r="B443" s="14" t="n"/>
+      <c r="C443" s="14" t="n"/>
+      <c r="D443" s="15" t="n"/>
+      <c r="E443" s="15" t="n"/>
+      <c r="F443" s="15" t="n"/>
+      <c r="G443" s="15" t="n"/>
+      <c r="H443" s="15" t="n"/>
+      <c r="I443" s="15" t="n"/>
+      <c r="J443" s="15" t="n"/>
+      <c r="K443" s="15" t="n"/>
+    </row>
+    <row r="444">
+      <c r="A444" s="13" t="n"/>
+      <c r="B444" s="14" t="n"/>
+      <c r="C444" s="14" t="n"/>
+      <c r="D444" s="15" t="n"/>
+      <c r="E444" s="15" t="n"/>
+      <c r="F444" s="15" t="n"/>
+      <c r="G444" s="15" t="n"/>
+      <c r="H444" s="15" t="n"/>
+      <c r="I444" s="15" t="n"/>
+      <c r="J444" s="15" t="n"/>
+      <c r="K444" s="15" t="n"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="13" t="n"/>
+      <c r="B445" s="14" t="n"/>
+      <c r="C445" s="14" t="n"/>
+      <c r="D445" s="15" t="n"/>
+      <c r="E445" s="15" t="n"/>
+      <c r="F445" s="15" t="n"/>
+      <c r="G445" s="15" t="n"/>
+      <c r="H445" s="15" t="n"/>
+      <c r="I445" s="15" t="n"/>
+      <c r="J445" s="15" t="n"/>
+      <c r="K445" s="15" t="n"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="13" t="n"/>
+      <c r="B446" s="14" t="n"/>
+      <c r="C446" s="14" t="n"/>
+      <c r="D446" s="15" t="n"/>
+      <c r="E446" s="15" t="n"/>
+      <c r="F446" s="15" t="n"/>
+      <c r="G446" s="15" t="n"/>
+      <c r="H446" s="15" t="n"/>
+      <c r="I446" s="15" t="n"/>
+      <c r="J446" s="15" t="n"/>
+      <c r="K446" s="15" t="n"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="13" t="n"/>
+      <c r="B447" s="14" t="n"/>
+      <c r="C447" s="14" t="n"/>
+      <c r="D447" s="15" t="n"/>
+      <c r="E447" s="15" t="n"/>
+      <c r="F447" s="15" t="n"/>
+      <c r="G447" s="15" t="n"/>
+      <c r="H447" s="15" t="n"/>
+      <c r="I447" s="15" t="n"/>
+      <c r="J447" s="15" t="n"/>
+      <c r="K447" s="15" t="n"/>
+    </row>
+    <row r="448">
+      <c r="A448" s="13" t="n"/>
+      <c r="B448" s="14" t="n"/>
+      <c r="C448" s="14" t="n"/>
+      <c r="D448" s="15" t="n"/>
+      <c r="E448" s="15" t="n"/>
+      <c r="F448" s="15" t="n"/>
+      <c r="G448" s="15" t="n"/>
+      <c r="H448" s="15" t="n"/>
+      <c r="I448" s="15" t="n"/>
+      <c r="J448" s="15" t="n"/>
+      <c r="K448" s="15" t="n"/>
+    </row>
+    <row r="449">
+      <c r="A449" s="13" t="n"/>
+      <c r="B449" s="14" t="n"/>
+      <c r="C449" s="14" t="n"/>
+      <c r="D449" s="15" t="n"/>
+      <c r="E449" s="15" t="n"/>
+      <c r="F449" s="15" t="n"/>
+      <c r="G449" s="15" t="n"/>
+      <c r="H449" s="15" t="n"/>
+      <c r="I449" s="15" t="n"/>
+      <c r="J449" s="15" t="n"/>
+      <c r="K449" s="15" t="n"/>
+    </row>
+    <row r="450">
+      <c r="A450" s="13" t="n"/>
+      <c r="B450" s="14" t="n"/>
+      <c r="C450" s="14" t="n"/>
+      <c r="D450" s="15" t="n"/>
+      <c r="E450" s="15" t="n"/>
+      <c r="F450" s="15" t="n"/>
+      <c r="G450" s="15" t="n"/>
+      <c r="H450" s="15" t="n"/>
+      <c r="I450" s="15" t="n"/>
+      <c r="J450" s="15" t="n"/>
+      <c r="K450" s="15" t="n"/>
+    </row>
+    <row r="451">
+      <c r="A451" s="13" t="n"/>
+      <c r="B451" s="14" t="n"/>
+      <c r="C451" s="14" t="n"/>
+      <c r="D451" s="15" t="n"/>
+      <c r="E451" s="15" t="n"/>
+      <c r="F451" s="15" t="n"/>
+      <c r="G451" s="15" t="n"/>
+      <c r="H451" s="15" t="n"/>
+      <c r="I451" s="15" t="n"/>
+      <c r="J451" s="15" t="n"/>
+      <c r="K451" s="15" t="n"/>
+    </row>
+    <row r="452">
+      <c r="A452" s="13" t="n"/>
+      <c r="B452" s="14" t="n"/>
+      <c r="C452" s="14" t="n"/>
+      <c r="D452" s="15" t="n"/>
+      <c r="E452" s="15" t="n"/>
+      <c r="F452" s="15" t="n"/>
+      <c r="G452" s="15" t="n"/>
+      <c r="H452" s="15" t="n"/>
+      <c r="I452" s="15" t="n"/>
+      <c r="J452" s="15" t="n"/>
+      <c r="K452" s="15" t="n"/>
+    </row>
+    <row r="453">
+      <c r="A453" s="13" t="n"/>
+      <c r="B453" s="14" t="n"/>
+      <c r="C453" s="14" t="n"/>
+      <c r="D453" s="15" t="n"/>
+      <c r="E453" s="15" t="n"/>
+      <c r="F453" s="15" t="n"/>
+      <c r="G453" s="15" t="n"/>
+      <c r="H453" s="15" t="n"/>
+      <c r="I453" s="15" t="n"/>
+      <c r="J453" s="15" t="n"/>
+      <c r="K453" s="15" t="n"/>
+    </row>
+    <row r="454">
+      <c r="A454" s="13" t="n"/>
+      <c r="B454" s="14" t="n"/>
+      <c r="C454" s="14" t="n"/>
+      <c r="D454" s="15" t="n"/>
+      <c r="E454" s="15" t="n"/>
+      <c r="F454" s="15" t="n"/>
+      <c r="G454" s="15" t="n"/>
+      <c r="H454" s="15" t="n"/>
+      <c r="I454" s="15" t="n"/>
+      <c r="J454" s="15" t="n"/>
+      <c r="K454" s="15" t="n"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="13" t="n"/>
+      <c r="B455" s="14" t="n"/>
+      <c r="C455" s="14" t="n"/>
+      <c r="D455" s="15" t="n"/>
+      <c r="E455" s="15" t="n"/>
+      <c r="F455" s="15" t="n"/>
+      <c r="G455" s="15" t="n"/>
+      <c r="H455" s="15" t="n"/>
+      <c r="I455" s="15" t="n"/>
+      <c r="J455" s="15" t="n"/>
+      <c r="K455" s="15" t="n"/>
+    </row>
+    <row r="456">
+      <c r="A456" s="13" t="n"/>
+      <c r="B456" s="14" t="n"/>
+      <c r="C456" s="14" t="n"/>
+      <c r="D456" s="15" t="n"/>
+      <c r="E456" s="15" t="n"/>
+      <c r="F456" s="15" t="n"/>
+      <c r="G456" s="15" t="n"/>
+      <c r="H456" s="15" t="n"/>
+      <c r="I456" s="15" t="n"/>
+      <c r="J456" s="15" t="n"/>
+      <c r="K456" s="15" t="n"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="13" t="n"/>
+      <c r="B457" s="14" t="n"/>
+      <c r="C457" s="14" t="n"/>
+      <c r="D457" s="15" t="n"/>
+      <c r="E457" s="15" t="n"/>
+      <c r="F457" s="15" t="n"/>
+      <c r="G457" s="15" t="n"/>
+      <c r="H457" s="15" t="n"/>
+      <c r="I457" s="15" t="n"/>
+      <c r="J457" s="15" t="n"/>
+      <c r="K457" s="15" t="n"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="13" t="n"/>
+      <c r="B458" s="14" t="n"/>
+      <c r="C458" s="14" t="n"/>
+      <c r="D458" s="15" t="n"/>
+      <c r="E458" s="15" t="n"/>
+      <c r="F458" s="15" t="n"/>
+      <c r="G458" s="15" t="n"/>
+      <c r="H458" s="15" t="n"/>
+      <c r="I458" s="15" t="n"/>
+      <c r="J458" s="15" t="n"/>
+      <c r="K458" s="15" t="n"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="13" t="n"/>
+      <c r="B459" s="14" t="n"/>
+      <c r="C459" s="14" t="n"/>
+      <c r="D459" s="15" t="n"/>
+      <c r="E459" s="15" t="n"/>
+      <c r="F459" s="15" t="n"/>
+      <c r="G459" s="15" t="n"/>
+      <c r="H459" s="15" t="n"/>
+      <c r="I459" s="15" t="n"/>
+      <c r="J459" s="15" t="n"/>
+      <c r="K459" s="15" t="n"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="13" t="n"/>
+      <c r="B460" s="14" t="n"/>
+      <c r="C460" s="14" t="n"/>
+      <c r="D460" s="15" t="n"/>
+      <c r="E460" s="15" t="n"/>
+      <c r="F460" s="15" t="n"/>
+      <c r="G460" s="15" t="n"/>
+      <c r="H460" s="15" t="n"/>
+      <c r="I460" s="15" t="n"/>
+      <c r="J460" s="15" t="n"/>
+      <c r="K460" s="15" t="n"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="13" t="n"/>
+      <c r="B461" s="14" t="n"/>
+      <c r="C461" s="14" t="n"/>
+      <c r="D461" s="15" t="n"/>
+      <c r="E461" s="15" t="n"/>
+      <c r="F461" s="15" t="n"/>
+      <c r="G461" s="15" t="n"/>
+      <c r="H461" s="15" t="n"/>
+      <c r="I461" s="15" t="n"/>
+      <c r="J461" s="15" t="n"/>
+      <c r="K461" s="15" t="n"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="13" t="n"/>
+      <c r="B462" s="14" t="n"/>
+      <c r="C462" s="14" t="n"/>
+      <c r="D462" s="15" t="n"/>
+      <c r="E462" s="15" t="n"/>
+      <c r="F462" s="15" t="n"/>
+      <c r="G462" s="15" t="n"/>
+      <c r="H462" s="15" t="n"/>
+      <c r="I462" s="15" t="n"/>
+      <c r="J462" s="15" t="n"/>
+      <c r="K462" s="15" t="n"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="13" t="n"/>
+      <c r="B463" s="14" t="n"/>
+      <c r="C463" s="14" t="n"/>
+      <c r="D463" s="15" t="n"/>
+      <c r="E463" s="15" t="n"/>
+      <c r="F463" s="15" t="n"/>
+      <c r="G463" s="15" t="n"/>
+      <c r="H463" s="15" t="n"/>
+      <c r="I463" s="15" t="n"/>
+      <c r="J463" s="15" t="n"/>
+      <c r="K463" s="15" t="n"/>
+    </row>
+    <row r="464">
+      <c r="A464" s="13" t="n"/>
+      <c r="B464" s="14" t="n"/>
+      <c r="C464" s="14" t="n"/>
+      <c r="D464" s="15" t="n"/>
+      <c r="E464" s="15" t="n"/>
+      <c r="F464" s="15" t="n"/>
+      <c r="G464" s="15" t="n"/>
+      <c r="H464" s="15" t="n"/>
+      <c r="I464" s="15" t="n"/>
+      <c r="J464" s="15" t="n"/>
+      <c r="K464" s="15" t="n"/>
+    </row>
+    <row r="465">
+      <c r="A465" s="13" t="n"/>
+      <c r="B465" s="14" t="n"/>
+      <c r="C465" s="14" t="n"/>
+      <c r="D465" s="15" t="n"/>
+      <c r="E465" s="15" t="n"/>
+      <c r="F465" s="15" t="n"/>
+      <c r="G465" s="15" t="n"/>
+      <c r="H465" s="15" t="n"/>
+      <c r="I465" s="15" t="n"/>
+      <c r="J465" s="15" t="n"/>
+      <c r="K465" s="15" t="n"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="13" t="n"/>
+      <c r="B466" s="14" t="n"/>
+      <c r="C466" s="14" t="n"/>
+      <c r="D466" s="15" t="n"/>
+      <c r="E466" s="15" t="n"/>
+      <c r="F466" s="15" t="n"/>
+      <c r="G466" s="15" t="n"/>
+      <c r="H466" s="15" t="n"/>
+      <c r="I466" s="15" t="n"/>
+      <c r="J466" s="15" t="n"/>
+      <c r="K466" s="15" t="n"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="13" t="n"/>
+      <c r="B467" s="14" t="n"/>
+      <c r="C467" s="14" t="n"/>
+      <c r="D467" s="15" t="n"/>
+      <c r="E467" s="15" t="n"/>
+      <c r="F467" s="15" t="n"/>
+      <c r="G467" s="15" t="n"/>
+      <c r="H467" s="15" t="n"/>
+      <c r="I467" s="15" t="n"/>
+      <c r="J467" s="15" t="n"/>
+      <c r="K467" s="15" t="n"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="13" t="n"/>
+      <c r="B468" s="14" t="n"/>
+      <c r="C468" s="14" t="n"/>
+      <c r="D468" s="15" t="n"/>
+      <c r="E468" s="15" t="n"/>
+      <c r="F468" s="15" t="n"/>
+      <c r="G468" s="15" t="n"/>
+      <c r="H468" s="15" t="n"/>
+      <c r="I468" s="15" t="n"/>
+      <c r="J468" s="15" t="n"/>
+      <c r="K468" s="15" t="n"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="13" t="n"/>
+      <c r="B469" s="14" t="n"/>
+      <c r="C469" s="14" t="n"/>
+      <c r="D469" s="15" t="n"/>
+      <c r="E469" s="15" t="n"/>
+      <c r="F469" s="15" t="n"/>
+      <c r="G469" s="15" t="n"/>
+      <c r="H469" s="15" t="n"/>
+      <c r="I469" s="15" t="n"/>
+      <c r="J469" s="15" t="n"/>
+      <c r="K469" s="15" t="n"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="13" t="n"/>
+      <c r="B470" s="14" t="n"/>
+      <c r="C470" s="14" t="n"/>
+      <c r="D470" s="15" t="n"/>
+      <c r="E470" s="15" t="n"/>
+      <c r="F470" s="15" t="n"/>
+      <c r="G470" s="15" t="n"/>
+      <c r="H470" s="15" t="n"/>
+      <c r="I470" s="15" t="n"/>
+      <c r="J470" s="15" t="n"/>
+      <c r="K470" s="15" t="n"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="13" t="n"/>
+      <c r="B471" s="14" t="n"/>
+      <c r="C471" s="14" t="n"/>
+      <c r="D471" s="15" t="n"/>
+      <c r="E471" s="15" t="n"/>
+      <c r="F471" s="15" t="n"/>
+      <c r="G471" s="15" t="n"/>
+      <c r="H471" s="15" t="n"/>
+      <c r="I471" s="15" t="n"/>
+      <c r="J471" s="15" t="n"/>
+      <c r="K471" s="15" t="n"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="13" t="n"/>
+      <c r="B472" s="14" t="n"/>
+      <c r="C472" s="14" t="n"/>
+      <c r="D472" s="15" t="n"/>
+      <c r="E472" s="15" t="n"/>
+      <c r="F472" s="15" t="n"/>
+      <c r="G472" s="15" t="n"/>
+      <c r="H472" s="15" t="n"/>
+      <c r="I472" s="15" t="n"/>
+      <c r="J472" s="15" t="n"/>
+      <c r="K472" s="15" t="n"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="13" t="n"/>
+      <c r="B473" s="14" t="n"/>
+      <c r="C473" s="14" t="n"/>
+      <c r="D473" s="15" t="n"/>
+      <c r="E473" s="15" t="n"/>
+      <c r="F473" s="15" t="n"/>
+      <c r="G473" s="15" t="n"/>
+      <c r="H473" s="15" t="n"/>
+      <c r="I473" s="15" t="n"/>
+      <c r="J473" s="15" t="n"/>
+      <c r="K473" s="15" t="n"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="13" t="n"/>
+      <c r="B474" s="14" t="n"/>
+      <c r="C474" s="14" t="n"/>
+      <c r="D474" s="15" t="n"/>
+      <c r="E474" s="15" t="n"/>
+      <c r="F474" s="15" t="n"/>
+      <c r="G474" s="15" t="n"/>
+      <c r="H474" s="15" t="n"/>
+      <c r="I474" s="15" t="n"/>
+      <c r="J474" s="15" t="n"/>
+      <c r="K474" s="15" t="n"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="13" t="n"/>
+      <c r="B475" s="14" t="n"/>
+      <c r="C475" s="14" t="n"/>
+      <c r="D475" s="15" t="n"/>
+      <c r="E475" s="15" t="n"/>
+      <c r="F475" s="15" t="n"/>
+      <c r="G475" s="15" t="n"/>
+      <c r="H475" s="15" t="n"/>
+      <c r="I475" s="15" t="n"/>
+      <c r="J475" s="15" t="n"/>
+      <c r="K475" s="15" t="n"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="13" t="n"/>
+      <c r="B476" s="14" t="n"/>
+      <c r="C476" s="14" t="n"/>
+      <c r="D476" s="15" t="n"/>
+      <c r="E476" s="15" t="n"/>
+      <c r="F476" s="15" t="n"/>
+      <c r="G476" s="15" t="n"/>
+      <c r="H476" s="15" t="n"/>
+      <c r="I476" s="15" t="n"/>
+      <c r="J476" s="15" t="n"/>
+      <c r="K476" s="15" t="n"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="13" t="n"/>
+      <c r="B477" s="14" t="n"/>
+      <c r="C477" s="14" t="n"/>
+      <c r="D477" s="15" t="n"/>
+      <c r="E477" s="15" t="n"/>
+      <c r="F477" s="15" t="n"/>
+      <c r="G477" s="15" t="n"/>
+      <c r="H477" s="15" t="n"/>
+      <c r="I477" s="15" t="n"/>
+      <c r="J477" s="15" t="n"/>
+      <c r="K477" s="15" t="n"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="13" t="n"/>
+      <c r="B478" s="14" t="n"/>
+      <c r="C478" s="14" t="n"/>
+      <c r="D478" s="15" t="n"/>
+      <c r="E478" s="15" t="n"/>
+      <c r="F478" s="15" t="n"/>
+      <c r="G478" s="15" t="n"/>
+      <c r="H478" s="15" t="n"/>
+      <c r="I478" s="15" t="n"/>
+      <c r="J478" s="15" t="n"/>
+      <c r="K478" s="15" t="n"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="13" t="n"/>
+      <c r="B479" s="14" t="n"/>
+      <c r="C479" s="14" t="n"/>
+      <c r="D479" s="15" t="n"/>
+      <c r="E479" s="15" t="n"/>
+      <c r="F479" s="15" t="n"/>
+      <c r="G479" s="15" t="n"/>
+      <c r="H479" s="15" t="n"/>
+      <c r="I479" s="15" t="n"/>
+      <c r="J479" s="15" t="n"/>
+      <c r="K479" s="15" t="n"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="13" t="n"/>
+      <c r="B480" s="14" t="n"/>
+      <c r="C480" s="14" t="n"/>
+      <c r="D480" s="15" t="n"/>
+      <c r="E480" s="15" t="n"/>
+      <c r="F480" s="15" t="n"/>
+      <c r="G480" s="15" t="n"/>
+      <c r="H480" s="15" t="n"/>
+      <c r="I480" s="15" t="n"/>
+      <c r="J480" s="15" t="n"/>
+      <c r="K480" s="15" t="n"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="13" t="n"/>
+      <c r="B481" s="14" t="n"/>
+      <c r="C481" s="14" t="n"/>
+      <c r="D481" s="15" t="n"/>
+      <c r="E481" s="15" t="n"/>
+      <c r="F481" s="15" t="n"/>
+      <c r="G481" s="15" t="n"/>
+      <c r="H481" s="15" t="n"/>
+      <c r="I481" s="15" t="n"/>
+      <c r="J481" s="15" t="n"/>
+      <c r="K481" s="15" t="n"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="13" t="n"/>
+      <c r="B482" s="14" t="n"/>
+      <c r="C482" s="14" t="n"/>
+      <c r="D482" s="15" t="n"/>
+      <c r="E482" s="15" t="n"/>
+      <c r="F482" s="15" t="n"/>
+      <c r="G482" s="15" t="n"/>
+      <c r="H482" s="15" t="n"/>
+      <c r="I482" s="15" t="n"/>
+      <c r="J482" s="15" t="n"/>
+      <c r="K482" s="15" t="n"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="13" t="n"/>
+      <c r="B483" s="14" t="n"/>
+      <c r="C483" s="14" t="n"/>
+      <c r="D483" s="15" t="n"/>
+      <c r="E483" s="15" t="n"/>
+      <c r="F483" s="15" t="n"/>
+      <c r="G483" s="15" t="n"/>
+      <c r="H483" s="15" t="n"/>
+      <c r="I483" s="15" t="n"/>
+      <c r="J483" s="15" t="n"/>
+      <c r="K483" s="15" t="n"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="13" t="n"/>
+      <c r="B484" s="14" t="n"/>
+      <c r="C484" s="14" t="n"/>
+      <c r="D484" s="15" t="n"/>
+      <c r="E484" s="15" t="n"/>
+      <c r="F484" s="15" t="n"/>
+      <c r="G484" s="15" t="n"/>
+      <c r="H484" s="15" t="n"/>
+      <c r="I484" s="15" t="n"/>
+      <c r="J484" s="15" t="n"/>
+      <c r="K484" s="15" t="n"/>
+    </row>
+    <row r="485">
+      <c r="A485" s="13" t="n"/>
+      <c r="B485" s="14" t="n"/>
+      <c r="C485" s="14" t="n"/>
+      <c r="D485" s="15" t="n"/>
+      <c r="E485" s="15" t="n"/>
+      <c r="F485" s="15" t="n"/>
+      <c r="G485" s="15" t="n"/>
+      <c r="H485" s="15" t="n"/>
+      <c r="I485" s="15" t="n"/>
+      <c r="J485" s="15" t="n"/>
+      <c r="K485" s="15" t="n"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="13" t="n"/>
+      <c r="B486" s="14" t="n"/>
+      <c r="C486" s="14" t="n"/>
+      <c r="D486" s="15" t="n"/>
+      <c r="E486" s="15" t="n"/>
+      <c r="F486" s="15" t="n"/>
+      <c r="G486" s="15" t="n"/>
+      <c r="H486" s="15" t="n"/>
+      <c r="I486" s="15" t="n"/>
+      <c r="J486" s="15" t="n"/>
+      <c r="K486" s="15" t="n"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="13" t="n"/>
+      <c r="B487" s="14" t="n"/>
+      <c r="C487" s="14" t="n"/>
+      <c r="D487" s="15" t="n"/>
+      <c r="E487" s="15" t="n"/>
+      <c r="F487" s="15" t="n"/>
+      <c r="G487" s="15" t="n"/>
+      <c r="H487" s="15" t="n"/>
+      <c r="I487" s="15" t="n"/>
+      <c r="J487" s="15" t="n"/>
+      <c r="K487" s="15" t="n"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="13" t="n"/>
+      <c r="B488" s="14" t="n"/>
+      <c r="C488" s="14" t="n"/>
+      <c r="D488" s="15" t="n"/>
+      <c r="E488" s="15" t="n"/>
+      <c r="F488" s="15" t="n"/>
+      <c r="G488" s="15" t="n"/>
+      <c r="H488" s="15" t="n"/>
+      <c r="I488" s="15" t="n"/>
+      <c r="J488" s="15" t="n"/>
+      <c r="K488" s="15" t="n"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="13" t="n"/>
+      <c r="B489" s="14" t="n"/>
+      <c r="C489" s="14" t="n"/>
+      <c r="D489" s="15" t="n"/>
+      <c r="E489" s="15" t="n"/>
+      <c r="F489" s="15" t="n"/>
+      <c r="G489" s="15" t="n"/>
+      <c r="H489" s="15" t="n"/>
+      <c r="I489" s="15" t="n"/>
+      <c r="J489" s="15" t="n"/>
+      <c r="K489" s="15" t="n"/>
+    </row>
+    <row r="490">
+      <c r="A490" s="13" t="n"/>
+      <c r="B490" s="14" t="n"/>
+      <c r="C490" s="14" t="n"/>
+      <c r="D490" s="15" t="n"/>
+      <c r="E490" s="15" t="n"/>
+      <c r="F490" s="15" t="n"/>
+      <c r="G490" s="15" t="n"/>
+      <c r="H490" s="15" t="n"/>
+      <c r="I490" s="15" t="n"/>
+      <c r="J490" s="15" t="n"/>
+      <c r="K490" s="15" t="n"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="13" t="n"/>
+      <c r="B491" s="14" t="n"/>
+      <c r="C491" s="14" t="n"/>
+      <c r="D491" s="15" t="n"/>
+      <c r="E491" s="15" t="n"/>
+      <c r="F491" s="15" t="n"/>
+      <c r="G491" s="15" t="n"/>
+      <c r="H491" s="15" t="n"/>
+      <c r="I491" s="15" t="n"/>
+      <c r="J491" s="15" t="n"/>
+      <c r="K491" s="15" t="n"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="13" t="n"/>
+      <c r="B492" s="14" t="n"/>
+      <c r="C492" s="14" t="n"/>
+      <c r="D492" s="15" t="n"/>
+      <c r="E492" s="15" t="n"/>
+      <c r="F492" s="15" t="n"/>
+      <c r="G492" s="15" t="n"/>
+      <c r="H492" s="15" t="n"/>
+      <c r="I492" s="15" t="n"/>
+      <c r="J492" s="15" t="n"/>
+      <c r="K492" s="15" t="n"/>
+    </row>
+    <row r="493">
+      <c r="A493" s="13" t="n"/>
+      <c r="B493" s="14" t="n"/>
+      <c r="C493" s="14" t="n"/>
+      <c r="D493" s="15" t="n"/>
+      <c r="E493" s="15" t="n"/>
+      <c r="F493" s="15" t="n"/>
+      <c r="G493" s="15" t="n"/>
+      <c r="H493" s="15" t="n"/>
+      <c r="I493" s="15" t="n"/>
+      <c r="J493" s="15" t="n"/>
+      <c r="K493" s="15" t="n"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="13" t="n"/>
+      <c r="B494" s="14" t="n"/>
+      <c r="C494" s="14" t="n"/>
+      <c r="D494" s="15" t="n"/>
+      <c r="E494" s="15" t="n"/>
+      <c r="F494" s="15" t="n"/>
+      <c r="G494" s="15" t="n"/>
+      <c r="H494" s="15" t="n"/>
+      <c r="I494" s="15" t="n"/>
+      <c r="J494" s="15" t="n"/>
+      <c r="K494" s="15" t="n"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="13" t="n"/>
+      <c r="B495" s="14" t="n"/>
+      <c r="C495" s="14" t="n"/>
+      <c r="D495" s="15" t="n"/>
+      <c r="E495" s="15" t="n"/>
+      <c r="F495" s="15" t="n"/>
+      <c r="G495" s="15" t="n"/>
+      <c r="H495" s="15" t="n"/>
+      <c r="I495" s="15" t="n"/>
+      <c r="J495" s="15" t="n"/>
+      <c r="K495" s="15" t="n"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="13" t="n"/>
+      <c r="B496" s="14" t="n"/>
+      <c r="C496" s="14" t="n"/>
+      <c r="D496" s="15" t="n"/>
+      <c r="E496" s="15" t="n"/>
+      <c r="F496" s="15" t="n"/>
+      <c r="G496" s="15" t="n"/>
+      <c r="H496" s="15" t="n"/>
+      <c r="I496" s="15" t="n"/>
+      <c r="J496" s="15" t="n"/>
+      <c r="K496" s="15" t="n"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="13" t="n"/>
+      <c r="B497" s="14" t="n"/>
+      <c r="C497" s="14" t="n"/>
+      <c r="D497" s="15" t="n"/>
+      <c r="E497" s="15" t="n"/>
+      <c r="F497" s="15" t="n"/>
+      <c r="G497" s="15" t="n"/>
+      <c r="H497" s="15" t="n"/>
+      <c r="I497" s="15" t="n"/>
+      <c r="J497" s="15" t="n"/>
+      <c r="K497" s="15" t="n"/>
+    </row>
+    <row r="498">
+      <c r="A498" s="13" t="n"/>
+      <c r="B498" s="14" t="n"/>
+      <c r="C498" s="14" t="n"/>
+      <c r="D498" s="15" t="n"/>
+      <c r="E498" s="15" t="n"/>
+      <c r="F498" s="15" t="n"/>
+      <c r="G498" s="15" t="n"/>
+      <c r="H498" s="15" t="n"/>
+      <c r="I498" s="15" t="n"/>
+      <c r="J498" s="15" t="n"/>
+      <c r="K498" s="15" t="n"/>
+    </row>
+    <row r="499">
+      <c r="A499" s="13" t="n"/>
+      <c r="B499" s="14" t="n"/>
+      <c r="C499" s="14" t="n"/>
+      <c r="D499" s="15" t="n"/>
+      <c r="E499" s="15" t="n"/>
+      <c r="F499" s="15" t="n"/>
+      <c r="G499" s="15" t="n"/>
+      <c r="H499" s="15" t="n"/>
+      <c r="I499" s="15" t="n"/>
+      <c r="J499" s="15" t="n"/>
+      <c r="K499" s="15" t="n"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="13" t="n"/>
+      <c r="B500" s="14" t="n"/>
+      <c r="C500" s="14" t="n"/>
+      <c r="D500" s="15" t="n"/>
+      <c r="E500" s="15" t="n"/>
+      <c r="F500" s="15" t="n"/>
+      <c r="G500" s="15" t="n"/>
+      <c r="H500" s="15" t="n"/>
+      <c r="I500" s="15" t="n"/>
+      <c r="J500" s="15" t="n"/>
+      <c r="K500" s="15" t="n"/>
+    </row>
+    <row r="501">
+      <c r="A501" s="13" t="n"/>
+      <c r="B501" s="14" t="n"/>
+      <c r="C501" s="14" t="n"/>
+      <c r="D501" s="15" t="n"/>
+      <c r="E501" s="15" t="n"/>
+      <c r="F501" s="15" t="n"/>
+      <c r="G501" s="15" t="n"/>
+      <c r="H501" s="15" t="n"/>
+      <c r="I501" s="15" t="n"/>
+      <c r="J501" s="15" t="n"/>
+      <c r="K501" s="15" t="n"/>
+    </row>
+    <row r="502">
+      <c r="A502" s="13" t="n"/>
+      <c r="B502" s="14" t="n"/>
+      <c r="C502" s="14" t="n"/>
+      <c r="D502" s="15" t="n"/>
+      <c r="E502" s="15" t="n"/>
+      <c r="F502" s="15" t="n"/>
+      <c r="G502" s="15" t="n"/>
+      <c r="H502" s="15" t="n"/>
+      <c r="I502" s="15" t="n"/>
+      <c r="J502" s="15" t="n"/>
+      <c r="K502" s="15" t="n"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="13" t="n"/>
+      <c r="B503" s="14" t="n"/>
+      <c r="C503" s="14" t="n"/>
+      <c r="D503" s="15" t="n"/>
+      <c r="E503" s="15" t="n"/>
+      <c r="F503" s="15" t="n"/>
+      <c r="G503" s="15" t="n"/>
+      <c r="H503" s="15" t="n"/>
+      <c r="I503" s="15" t="n"/>
+      <c r="J503" s="15" t="n"/>
+      <c r="K503" s="15" t="n"/>
+    </row>
+    <row r="504">
+      <c r="A504" s="13" t="n"/>
+      <c r="B504" s="14" t="n"/>
+      <c r="C504" s="14" t="n"/>
+      <c r="D504" s="15" t="n"/>
+      <c r="E504" s="15" t="n"/>
+      <c r="F504" s="15" t="n"/>
+      <c r="G504" s="15" t="n"/>
+      <c r="H504" s="15" t="n"/>
+      <c r="I504" s="15" t="n"/>
+      <c r="J504" s="15" t="n"/>
+      <c r="K504" s="15" t="n"/>
+    </row>
+    <row r="505">
+      <c r="A505" s="13" t="n"/>
+      <c r="B505" s="14" t="n"/>
+      <c r="C505" s="14" t="n"/>
+      <c r="D505" s="15" t="n"/>
+      <c r="E505" s="15" t="n"/>
+      <c r="F505" s="15" t="n"/>
+      <c r="G505" s="15" t="n"/>
+      <c r="H505" s="15" t="n"/>
+      <c r="I505" s="15" t="n"/>
+      <c r="J505" s="15" t="n"/>
+      <c r="K505" s="15" t="n"/>
+    </row>
+    <row r="506">
+      <c r="A506" s="13" t="n"/>
+      <c r="B506" s="14" t="n"/>
+      <c r="C506" s="14" t="n"/>
+      <c r="D506" s="15" t="n"/>
+      <c r="E506" s="15" t="n"/>
+      <c r="F506" s="15" t="n"/>
+      <c r="G506" s="15" t="n"/>
+      <c r="H506" s="15" t="n"/>
+      <c r="I506" s="15" t="n"/>
+      <c r="J506" s="15" t="n"/>
+      <c r="K506" s="15" t="n"/>
+    </row>
+    <row r="507">
+      <c r="A507" s="13" t="n"/>
+      <c r="B507" s="14" t="n"/>
+      <c r="C507" s="14" t="n"/>
+      <c r="D507" s="15" t="n"/>
+      <c r="E507" s="15" t="n"/>
+      <c r="F507" s="15" t="n"/>
+      <c r="G507" s="15" t="n"/>
+      <c r="H507" s="15" t="n"/>
+      <c r="I507" s="15" t="n"/>
+      <c r="J507" s="15" t="n"/>
+      <c r="K507" s="15" t="n"/>
+    </row>
+    <row r="508">
+      <c r="A508" s="13" t="n"/>
+      <c r="B508" s="14" t="n"/>
+      <c r="C508" s="14" t="n"/>
+      <c r="D508" s="15" t="n"/>
+      <c r="E508" s="15" t="n"/>
+      <c r="F508" s="15" t="n"/>
+      <c r="G508" s="15" t="n"/>
+      <c r="H508" s="15" t="n"/>
+      <c r="I508" s="15" t="n"/>
+      <c r="J508" s="15" t="n"/>
+      <c r="K508" s="15" t="n"/>
+    </row>
+    <row r="509">
+      <c r="A509" s="13" t="n"/>
+      <c r="B509" s="14" t="n"/>
+      <c r="C509" s="14" t="n"/>
+      <c r="D509" s="15" t="n"/>
+      <c r="E509" s="15" t="n"/>
+      <c r="F509" s="15" t="n"/>
+      <c r="G509" s="15" t="n"/>
+      <c r="H509" s="15" t="n"/>
+      <c r="I509" s="15" t="n"/>
+      <c r="J509" s="15" t="n"/>
+      <c r="K509" s="15" t="n"/>
+    </row>
+    <row r="510">
+      <c r="A510" s="13" t="n"/>
+      <c r="B510" s="14" t="n"/>
+      <c r="C510" s="14" t="n"/>
+      <c r="D510" s="15" t="n"/>
+      <c r="E510" s="15" t="n"/>
+      <c r="F510" s="15" t="n"/>
+      <c r="G510" s="15" t="n"/>
+      <c r="H510" s="15" t="n"/>
+      <c r="I510" s="15" t="n"/>
+      <c r="J510" s="15" t="n"/>
+      <c r="K510" s="15" t="n"/>
+    </row>
+    <row r="511">
+      <c r="A511" s="13" t="n"/>
+      <c r="B511" s="14" t="n"/>
+      <c r="C511" s="14" t="n"/>
+      <c r="D511" s="15" t="n"/>
+      <c r="E511" s="15" t="n"/>
+      <c r="F511" s="15" t="n"/>
+      <c r="G511" s="15" t="n"/>
+      <c r="H511" s="15" t="n"/>
+      <c r="I511" s="15" t="n"/>
+      <c r="J511" s="15" t="n"/>
+      <c r="K511" s="15" t="n"/>
+    </row>
+    <row r="512">
+      <c r="A512" s="13" t="n"/>
+      <c r="B512" s="14" t="n"/>
+      <c r="C512" s="14" t="n"/>
+      <c r="D512" s="15" t="n"/>
+      <c r="E512" s="15" t="n"/>
+      <c r="F512" s="15" t="n"/>
+      <c r="G512" s="15" t="n"/>
+      <c r="H512" s="15" t="n"/>
+      <c r="I512" s="15" t="n"/>
+      <c r="J512" s="15" t="n"/>
+      <c r="K512" s="15" t="n"/>
+    </row>
+    <row r="513">
+      <c r="A513" s="13" t="n"/>
+      <c r="B513" s="14" t="n"/>
+      <c r="C513" s="14" t="n"/>
+      <c r="D513" s="15" t="n"/>
+      <c r="E513" s="15" t="n"/>
+      <c r="F513" s="15" t="n"/>
+      <c r="G513" s="15" t="n"/>
+      <c r="H513" s="15" t="n"/>
+      <c r="I513" s="15" t="n"/>
+      <c r="J513" s="15" t="n"/>
+      <c r="K513" s="15" t="n"/>
+    </row>
+    <row r="514">
+      <c r="A514" s="13" t="n"/>
+      <c r="B514" s="14" t="n"/>
+      <c r="C514" s="14" t="n"/>
+      <c r="D514" s="15" t="n"/>
+      <c r="E514" s="15" t="n"/>
+      <c r="F514" s="15" t="n"/>
+      <c r="G514" s="15" t="n"/>
+      <c r="H514" s="15" t="n"/>
+      <c r="I514" s="15" t="n"/>
+      <c r="J514" s="15" t="n"/>
+      <c r="K514" s="15" t="n"/>
+    </row>
+    <row r="515">
+      <c r="A515" s="13" t="n"/>
+      <c r="B515" s="14" t="n"/>
+      <c r="C515" s="14" t="n"/>
+      <c r="D515" s="15" t="n"/>
+      <c r="E515" s="15" t="n"/>
+      <c r="F515" s="15" t="n"/>
+      <c r="G515" s="15" t="n"/>
+      <c r="H515" s="15" t="n"/>
+      <c r="I515" s="15" t="n"/>
+      <c r="J515" s="15" t="n"/>
+      <c r="K515" s="15" t="n"/>
+    </row>
+    <row r="516">
+      <c r="A516" s="13" t="n"/>
+      <c r="B516" s="14" t="n"/>
+      <c r="C516" s="14" t="n"/>
+      <c r="D516" s="15" t="n"/>
+      <c r="E516" s="15" t="n"/>
+      <c r="F516" s="15" t="n"/>
+      <c r="G516" s="15" t="n"/>
+      <c r="H516" s="15" t="n"/>
+      <c r="I516" s="15" t="n"/>
+      <c r="J516" s="15" t="n"/>
+      <c r="K516" s="15" t="n"/>
+    </row>
+    <row r="517">
+      <c r="A517" s="13" t="n"/>
+      <c r="B517" s="14" t="n"/>
+      <c r="C517" s="14" t="n"/>
+      <c r="D517" s="15" t="n"/>
+      <c r="E517" s="15" t="n"/>
+      <c r="F517" s="15" t="n"/>
+      <c r="G517" s="15" t="n"/>
+      <c r="H517" s="15" t="n"/>
+      <c r="I517" s="15" t="n"/>
+      <c r="J517" s="15" t="n"/>
+      <c r="K517" s="15" t="n"/>
+    </row>
+    <row r="518">
+      <c r="A518" s="13" t="n"/>
+      <c r="B518" s="14" t="n"/>
+      <c r="C518" s="14" t="n"/>
+      <c r="D518" s="15" t="n"/>
+      <c r="E518" s="15" t="n"/>
+      <c r="F518" s="15" t="n"/>
+      <c r="G518" s="15" t="n"/>
+      <c r="H518" s="15" t="n"/>
+      <c r="I518" s="15" t="n"/>
+      <c r="J518" s="15" t="n"/>
+      <c r="K518" s="15" t="n"/>
+    </row>
+    <row r="519">
+      <c r="A519" s="13" t="n"/>
+      <c r="B519" s="14" t="n"/>
+      <c r="C519" s="14" t="n"/>
+      <c r="D519" s="15" t="n"/>
+      <c r="E519" s="15" t="n"/>
+      <c r="F519" s="15" t="n"/>
+      <c r="G519" s="15" t="n"/>
+      <c r="H519" s="15" t="n"/>
+      <c r="I519" s="15" t="n"/>
+      <c r="J519" s="15" t="n"/>
+      <c r="K519" s="15" t="n"/>
+    </row>
+    <row r="520">
+      <c r="A520" s="13" t="n"/>
+      <c r="B520" s="14" t="n"/>
+      <c r="C520" s="14" t="n"/>
+      <c r="D520" s="15" t="n"/>
+      <c r="E520" s="15" t="n"/>
+      <c r="F520" s="15" t="n"/>
+      <c r="G520" s="15" t="n"/>
+      <c r="H520" s="15" t="n"/>
+      <c r="I520" s="15" t="n"/>
+      <c r="J520" s="15" t="n"/>
+      <c r="K520" s="15" t="n"/>
+    </row>
+    <row r="521">
+      <c r="A521" s="13" t="n"/>
+      <c r="B521" s="14" t="n"/>
+      <c r="C521" s="14" t="n"/>
+      <c r="D521" s="15" t="n"/>
+      <c r="E521" s="15" t="n"/>
+      <c r="F521" s="15" t="n"/>
+      <c r="G521" s="15" t="n"/>
+      <c r="H521" s="15" t="n"/>
+      <c r="I521" s="15" t="n"/>
+      <c r="J521" s="15" t="n"/>
+      <c r="K521" s="15" t="n"/>
+    </row>
+    <row r="522">
+      <c r="A522" s="13" t="n"/>
+      <c r="B522" s="14" t="n"/>
+      <c r="C522" s="14" t="n"/>
+      <c r="D522" s="15" t="n"/>
+      <c r="E522" s="15" t="n"/>
+      <c r="F522" s="15" t="n"/>
+      <c r="G522" s="15" t="n"/>
+      <c r="H522" s="15" t="n"/>
+      <c r="I522" s="15" t="n"/>
+      <c r="J522" s="15" t="n"/>
+      <c r="K522" s="15" t="n"/>
+    </row>
+    <row r="523">
+      <c r="A523" s="13" t="n"/>
+      <c r="B523" s="14" t="n"/>
+      <c r="C523" s="14" t="n"/>
+      <c r="D523" s="15" t="n"/>
+      <c r="E523" s="15" t="n"/>
+      <c r="F523" s="15" t="n"/>
+      <c r="G523" s="15" t="n"/>
+      <c r="H523" s="15" t="n"/>
+      <c r="I523" s="15" t="n"/>
+      <c r="J523" s="15" t="n"/>
+      <c r="K523" s="15" t="n"/>
+    </row>
+    <row r="524">
+      <c r="A524" s="13" t="n"/>
+      <c r="B524" s="14" t="n"/>
+      <c r="C524" s="14" t="n"/>
+      <c r="D524" s="15" t="n"/>
+      <c r="E524" s="15" t="n"/>
+      <c r="F524" s="15" t="n"/>
+      <c r="G524" s="15" t="n"/>
+      <c r="H524" s="15" t="n"/>
+      <c r="I524" s="15" t="n"/>
+      <c r="J524" s="15" t="n"/>
+      <c r="K524" s="15" t="n"/>
+    </row>
+    <row r="525">
+      <c r="A525" s="13" t="n"/>
+      <c r="B525" s="14" t="n"/>
+      <c r="C525" s="14" t="n"/>
+      <c r="D525" s="15" t="n"/>
+      <c r="E525" s="15" t="n"/>
+      <c r="F525" s="15" t="n"/>
+      <c r="G525" s="15" t="n"/>
+      <c r="H525" s="15" t="n"/>
+      <c r="I525" s="15" t="n"/>
+      <c r="J525" s="15" t="n"/>
+      <c r="K525" s="15" t="n"/>
+    </row>
+    <row r="526">
+      <c r="A526" s="13" t="n"/>
+      <c r="B526" s="14" t="n"/>
+      <c r="C526" s="14" t="n"/>
+      <c r="D526" s="15" t="n"/>
+      <c r="E526" s="15" t="n"/>
+      <c r="F526" s="15" t="n"/>
+      <c r="G526" s="15" t="n"/>
+      <c r="H526" s="15" t="n"/>
+      <c r="I526" s="15" t="n"/>
+      <c r="J526" s="15" t="n"/>
+      <c r="K526" s="15" t="n"/>
+    </row>
+    <row r="527">
+      <c r="A527" s="13" t="n"/>
+      <c r="B527" s="14" t="n"/>
+      <c r="C527" s="14" t="n"/>
+      <c r="D527" s="15" t="n"/>
+      <c r="E527" s="15" t="n"/>
+      <c r="F527" s="15" t="n"/>
+      <c r="G527" s="15" t="n"/>
+      <c r="H527" s="15" t="n"/>
+      <c r="I527" s="15" t="n"/>
+      <c r="J527" s="15" t="n"/>
+      <c r="K527" s="15" t="n"/>
+    </row>
+    <row r="528">
+      <c r="A528" s="13" t="n"/>
+      <c r="B528" s="14" t="n"/>
+      <c r="C528" s="14" t="n"/>
+      <c r="D528" s="15" t="n"/>
+      <c r="E528" s="15" t="n"/>
+      <c r="F528" s="15" t="n"/>
+      <c r="G528" s="15" t="n"/>
+      <c r="H528" s="15" t="n"/>
+      <c r="I528" s="15" t="n"/>
+      <c r="J528" s="15" t="n"/>
+      <c r="K528" s="15" t="n"/>
+    </row>
+    <row r="529">
+      <c r="A529" s="13" t="n"/>
+      <c r="B529" s="14" t="n"/>
+      <c r="C529" s="14" t="n"/>
+      <c r="D529" s="15" t="n"/>
+      <c r="E529" s="15" t="n"/>
+      <c r="F529" s="15" t="n"/>
+      <c r="G529" s="15" t="n"/>
+      <c r="H529" s="15" t="n"/>
+      <c r="I529" s="15" t="n"/>
+      <c r="J529" s="15" t="n"/>
+      <c r="K529" s="15" t="n"/>
+    </row>
+    <row r="530">
+      <c r="A530" s="13" t="n"/>
+      <c r="B530" s="14" t="n"/>
+      <c r="C530" s="14" t="n"/>
+      <c r="D530" s="15" t="n"/>
+      <c r="E530" s="15" t="n"/>
+      <c r="F530" s="15" t="n"/>
+      <c r="G530" s="15" t="n"/>
+      <c r="H530" s="15" t="n"/>
+      <c r="I530" s="15" t="n"/>
+      <c r="J530" s="15" t="n"/>
+      <c r="K530" s="15" t="n"/>
+    </row>
+    <row r="531">
+      <c r="A531" s="13" t="n"/>
+      <c r="B531" s="14" t="n"/>
+      <c r="C531" s="14" t="n"/>
+      <c r="D531" s="15" t="n"/>
+      <c r="E531" s="15" t="n"/>
+      <c r="F531" s="15" t="n"/>
+      <c r="G531" s="15" t="n"/>
+      <c r="H531" s="15" t="n"/>
+      <c r="I531" s="15" t="n"/>
+      <c r="J531" s="15" t="n"/>
+      <c r="K531" s="15" t="n"/>
+    </row>
+    <row r="532">
+      <c r="A532" s="13" t="n"/>
+      <c r="B532" s="14" t="n"/>
+      <c r="C532" s="14" t="n"/>
+      <c r="D532" s="15" t="n"/>
+      <c r="E532" s="15" t="n"/>
+      <c r="F532" s="15" t="n"/>
+      <c r="G532" s="15" t="n"/>
+      <c r="H532" s="15" t="n"/>
+      <c r="I532" s="15" t="n"/>
+      <c r="J532" s="15" t="n"/>
+      <c r="K532" s="15" t="n"/>
+    </row>
+    <row r="533">
+      <c r="A533" s="13" t="n"/>
+      <c r="B533" s="14" t="n"/>
+      <c r="C533" s="14" t="n"/>
+      <c r="D533" s="15" t="n"/>
+      <c r="E533" s="15" t="n"/>
+      <c r="F533" s="15" t="n"/>
+      <c r="G533" s="15" t="n"/>
+      <c r="H533" s="15" t="n"/>
+      <c r="I533" s="15" t="n"/>
+      <c r="J533" s="15" t="n"/>
+      <c r="K533" s="15" t="n"/>
+    </row>
+    <row r="534">
+      <c r="A534" s="13" t="n"/>
+      <c r="B534" s="14" t="n"/>
+      <c r="C534" s="14" t="n"/>
+      <c r="D534" s="15" t="n"/>
+      <c r="E534" s="15" t="n"/>
+      <c r="F534" s="15" t="n"/>
+      <c r="G534" s="15" t="n"/>
+      <c r="H534" s="15" t="n"/>
+      <c r="I534" s="15" t="n"/>
+      <c r="J534" s="15" t="n"/>
+      <c r="K534" s="15" t="n"/>
+    </row>
+    <row r="535">
+      <c r="A535" s="13" t="n"/>
+      <c r="B535" s="14" t="n"/>
+      <c r="C535" s="14" t="n"/>
+      <c r="D535" s="15" t="n"/>
+      <c r="E535" s="15" t="n"/>
+      <c r="F535" s="15" t="n"/>
+      <c r="G535" s="15" t="n"/>
+      <c r="H535" s="15" t="n"/>
+      <c r="I535" s="15" t="n"/>
+      <c r="J535" s="15" t="n"/>
+      <c r="K535" s="15" t="n"/>
+    </row>
+    <row r="536">
+      <c r="A536" s="13" t="n"/>
+      <c r="B536" s="14" t="n"/>
+      <c r="C536" s="14" t="n"/>
+      <c r="D536" s="15" t="n"/>
+      <c r="E536" s="15" t="n"/>
+      <c r="F536" s="15" t="n"/>
+      <c r="G536" s="15" t="n"/>
+      <c r="H536" s="15" t="n"/>
+      <c r="I536" s="15" t="n"/>
+      <c r="J536" s="15" t="n"/>
+      <c r="K536" s="15" t="n"/>
+    </row>
+    <row r="537">
+      <c r="A537" s="13" t="n"/>
+      <c r="B537" s="14" t="n"/>
+      <c r="C537" s="14" t="n"/>
+      <c r="D537" s="15" t="n"/>
+      <c r="E537" s="15" t="n"/>
+      <c r="F537" s="15" t="n"/>
+      <c r="G537" s="15" t="n"/>
+      <c r="H537" s="15" t="n"/>
+      <c r="I537" s="15" t="n"/>
+      <c r="J537" s="15" t="n"/>
+      <c r="K537" s="15" t="n"/>
+    </row>
+    <row r="538">
+      <c r="A538" s="13" t="n"/>
+      <c r="B538" s="14" t="n"/>
+      <c r="C538" s="14" t="n"/>
+      <c r="D538" s="15" t="n"/>
+      <c r="E538" s="15" t="n"/>
+      <c r="F538" s="15" t="n"/>
+      <c r="G538" s="15" t="n"/>
+      <c r="H538" s="15" t="n"/>
+      <c r="I538" s="15" t="n"/>
+      <c r="J538" s="15" t="n"/>
+      <c r="K538" s="15" t="n"/>
+    </row>
+    <row r="539">
+      <c r="A539" s="13" t="n"/>
+      <c r="B539" s="14" t="n"/>
+      <c r="C539" s="14" t="n"/>
+      <c r="D539" s="15" t="n"/>
+      <c r="E539" s="15" t="n"/>
+      <c r="F539" s="15" t="n"/>
+      <c r="G539" s="15" t="n"/>
+      <c r="H539" s="15" t="n"/>
+      <c r="I539" s="15" t="n"/>
+      <c r="J539" s="15" t="n"/>
+      <c r="K539" s="15" t="n"/>
+    </row>
+    <row r="540">
+      <c r="A540" s="13" t="n"/>
+      <c r="B540" s="14" t="n"/>
+      <c r="C540" s="14" t="n"/>
+      <c r="D540" s="15" t="n"/>
+      <c r="E540" s="15" t="n"/>
+      <c r="F540" s="15" t="n"/>
+      <c r="G540" s="15" t="n"/>
+      <c r="H540" s="15" t="n"/>
+      <c r="I540" s="15" t="n"/>
+      <c r="J540" s="15" t="n"/>
+      <c r="K540" s="15" t="n"/>
+    </row>
+    <row r="541">
+      <c r="A541" s="13" t="n"/>
+      <c r="B541" s="14" t="n"/>
+      <c r="C541" s="14" t="n"/>
+      <c r="D541" s="15" t="n"/>
+      <c r="E541" s="15" t="n"/>
+      <c r="F541" s="15" t="n"/>
+      <c r="G541" s="15" t="n"/>
+      <c r="H541" s="15" t="n"/>
+      <c r="I541" s="15" t="n"/>
+      <c r="J541" s="15" t="n"/>
+      <c r="K541" s="15" t="n"/>
+    </row>
+    <row r="542">
+      <c r="A542" s="13" t="n"/>
+      <c r="B542" s="14" t="n"/>
+      <c r="C542" s="14" t="n"/>
+      <c r="D542" s="15" t="n"/>
+      <c r="E542" s="15" t="n"/>
+      <c r="F542" s="15" t="n"/>
+      <c r="G542" s="15" t="n"/>
+      <c r="H542" s="15" t="n"/>
+      <c r="I542" s="15" t="n"/>
+      <c r="J542" s="15" t="n"/>
+      <c r="K542" s="15" t="n"/>
+    </row>
+    <row r="543">
+      <c r="A543" s="13" t="n"/>
+      <c r="B543" s="14" t="n"/>
+      <c r="C543" s="14" t="n"/>
+      <c r="D543" s="15" t="n"/>
+      <c r="E543" s="15" t="n"/>
+      <c r="F543" s="15" t="n"/>
+      <c r="G543" s="15" t="n"/>
+      <c r="H543" s="15" t="n"/>
+      <c r="I543" s="15" t="n"/>
+      <c r="J543" s="15" t="n"/>
+      <c r="K543" s="15" t="n"/>
+    </row>
+    <row r="544">
+      <c r="A544" s="13" t="n"/>
+      <c r="B544" s="14" t="n"/>
+      <c r="C544" s="14" t="n"/>
+      <c r="D544" s="15" t="n"/>
+      <c r="E544" s="15" t="n"/>
+      <c r="F544" s="15" t="n"/>
+      <c r="G544" s="15" t="n"/>
+      <c r="H544" s="15" t="n"/>
+      <c r="I544" s="15" t="n"/>
+      <c r="J544" s="15" t="n"/>
+      <c r="K544" s="15" t="n"/>
+    </row>
+    <row r="545">
+      <c r="A545" s="13" t="n"/>
+      <c r="B545" s="14" t="n"/>
+      <c r="C545" s="14" t="n"/>
+      <c r="D545" s="15" t="n"/>
+      <c r="E545" s="15" t="n"/>
+      <c r="F545" s="15" t="n"/>
+      <c r="G545" s="15" t="n"/>
+      <c r="H545" s="15" t="n"/>
+      <c r="I545" s="15" t="n"/>
+      <c r="J545" s="15" t="n"/>
+      <c r="K545" s="15" t="n"/>
+    </row>
+    <row r="546">
+      <c r="A546" s="13" t="n"/>
+      <c r="B546" s="14" t="n"/>
+      <c r="C546" s="14" t="n"/>
+      <c r="D546" s="15" t="n"/>
+      <c r="E546" s="15" t="n"/>
+      <c r="F546" s="15" t="n"/>
+      <c r="G546" s="15" t="n"/>
+      <c r="H546" s="15" t="n"/>
+      <c r="I546" s="15" t="n"/>
+      <c r="J546" s="15" t="n"/>
+      <c r="K546" s="15" t="n"/>
+    </row>
+    <row r="547">
+      <c r="A547" s="13" t="n"/>
+      <c r="B547" s="14" t="n"/>
+      <c r="C547" s="14" t="n"/>
+      <c r="D547" s="15" t="n"/>
+      <c r="E547" s="15" t="n"/>
+      <c r="F547" s="15" t="n"/>
+      <c r="G547" s="15" t="n"/>
+      <c r="H547" s="15" t="n"/>
+      <c r="I547" s="15" t="n"/>
+      <c r="J547" s="15" t="n"/>
+      <c r="K547" s="15" t="n"/>
+    </row>
+    <row r="548">
+      <c r="A548" s="13" t="n"/>
+      <c r="B548" s="14" t="n"/>
+      <c r="C548" s="14" t="n"/>
+      <c r="D548" s="15" t="n"/>
+      <c r="E548" s="15" t="n"/>
+      <c r="F548" s="15" t="n"/>
+      <c r="G548" s="15" t="n"/>
+      <c r="H548" s="15" t="n"/>
+      <c r="I548" s="15" t="n"/>
+      <c r="J548" s="15" t="n"/>
+      <c r="K548" s="15" t="n"/>
+    </row>
+    <row r="549">
+      <c r="A549" s="13" t="n"/>
+      <c r="B549" s="14" t="n"/>
+      <c r="C549" s="14" t="n"/>
+      <c r="D549" s="15" t="n"/>
+      <c r="E549" s="15" t="n"/>
+      <c r="F549" s="15" t="n"/>
+      <c r="G549" s="15" t="n"/>
+      <c r="H549" s="15" t="n"/>
+      <c r="I549" s="15" t="n"/>
+      <c r="J549" s="15" t="n"/>
+      <c r="K549" s="15" t="n"/>
+    </row>
+    <row r="550">
+      <c r="A550" s="13" t="n"/>
+      <c r="B550" s="14" t="n"/>
+      <c r="C550" s="14" t="n"/>
+      <c r="D550" s="15" t="n"/>
+      <c r="E550" s="15" t="n"/>
+      <c r="F550" s="15" t="n"/>
+      <c r="G550" s="15" t="n"/>
+      <c r="H550" s="15" t="n"/>
+      <c r="I550" s="15" t="n"/>
+      <c r="J550" s="15" t="n"/>
+      <c r="K550" s="15" t="n"/>
+    </row>
+    <row r="551">
+      <c r="A551" s="13" t="n"/>
+      <c r="B551" s="14" t="n"/>
+      <c r="C551" s="14" t="n"/>
+      <c r="D551" s="15" t="n"/>
+      <c r="E551" s="15" t="n"/>
+      <c r="F551" s="15" t="n"/>
+      <c r="G551" s="15" t="n"/>
+      <c r="H551" s="15" t="n"/>
+      <c r="I551" s="15" t="n"/>
+      <c r="J551" s="15" t="n"/>
+      <c r="K551" s="15" t="n"/>
+    </row>
+    <row r="552">
+      <c r="A552" s="13" t="n"/>
+      <c r="B552" s="14" t="n"/>
+      <c r="C552" s="14" t="n"/>
+      <c r="D552" s="15" t="n"/>
+      <c r="E552" s="15" t="n"/>
+      <c r="F552" s="15" t="n"/>
+      <c r="G552" s="15" t="n"/>
+      <c r="H552" s="15" t="n"/>
+      <c r="I552" s="15" t="n"/>
+      <c r="J552" s="15" t="n"/>
+      <c r="K552" s="15" t="n"/>
+    </row>
+    <row r="553">
+      <c r="A553" s="13" t="n"/>
+      <c r="B553" s="14" t="n"/>
+      <c r="C553" s="14" t="n"/>
+      <c r="D553" s="15" t="n"/>
+      <c r="E553" s="15" t="n"/>
+      <c r="F553" s="15" t="n"/>
+      <c r="G553" s="15" t="n"/>
+      <c r="H553" s="15" t="n"/>
+      <c r="I553" s="15" t="n"/>
+      <c r="J553" s="15" t="n"/>
+      <c r="K553" s="15" t="n"/>
+    </row>
+    <row r="554">
+      <c r="A554" s="13" t="n"/>
+      <c r="B554" s="14" t="n"/>
+      <c r="C554" s="14" t="n"/>
+      <c r="D554" s="15" t="n"/>
+      <c r="E554" s="15" t="n"/>
+      <c r="F554" s="15" t="n"/>
+      <c r="G554" s="15" t="n"/>
+      <c r="H554" s="15" t="n"/>
+      <c r="I554" s="15" t="n"/>
+      <c r="J554" s="15" t="n"/>
+      <c r="K554" s="15" t="n"/>
+    </row>
+    <row r="555">
+      <c r="A555" s="13" t="n"/>
+      <c r="B555" s="14" t="n"/>
+      <c r="C555" s="14" t="n"/>
+      <c r="D555" s="15" t="n"/>
+      <c r="E555" s="15" t="n"/>
+      <c r="F555" s="15" t="n"/>
+      <c r="G555" s="15" t="n"/>
+      <c r="H555" s="15" t="n"/>
+      <c r="I555" s="15" t="n"/>
+      <c r="J555" s="15" t="n"/>
+      <c r="K555" s="15" t="n"/>
+    </row>
+    <row r="556">
+      <c r="A556" s="13" t="n"/>
+      <c r="B556" s="14" t="n"/>
+      <c r="C556" s="14" t="n"/>
+      <c r="D556" s="15" t="n"/>
+      <c r="E556" s="15" t="n"/>
+      <c r="F556" s="15" t="n"/>
+      <c r="G556" s="15" t="n"/>
+      <c r="H556" s="15" t="n"/>
+      <c r="I556" s="15" t="n"/>
+      <c r="J556" s="15" t="n"/>
+      <c r="K556" s="15" t="n"/>
+    </row>
+    <row r="557">
+      <c r="A557" s="13" t="n"/>
+      <c r="B557" s="14" t="n"/>
+      <c r="C557" s="14" t="n"/>
+      <c r="D557" s="15" t="n"/>
+      <c r="E557" s="15" t="n"/>
+      <c r="F557" s="15" t="n"/>
+      <c r="G557" s="15" t="n"/>
+      <c r="H557" s="15" t="n"/>
+      <c r="I557" s="15" t="n"/>
+      <c r="J557" s="15" t="n"/>
+      <c r="K557" s="15" t="n"/>
+    </row>
+    <row r="558">
+      <c r="A558" s="13" t="n"/>
+      <c r="B558" s="14" t="n"/>
+      <c r="C558" s="14" t="n"/>
+      <c r="D558" s="15" t="n"/>
+      <c r="E558" s="15" t="n"/>
+      <c r="F558" s="15" t="n"/>
+      <c r="G558" s="15" t="n"/>
+      <c r="H558" s="15" t="n"/>
+      <c r="I558" s="15" t="n"/>
+      <c r="J558" s="15" t="n"/>
+      <c r="K558" s="15" t="n"/>
+    </row>
+    <row r="559">
+      <c r="A559" s="13" t="n"/>
+      <c r="B559" s="14" t="n"/>
+      <c r="C559" s="14" t="n"/>
+      <c r="D559" s="15" t="n"/>
+      <c r="E559" s="15" t="n"/>
+      <c r="F559" s="15" t="n"/>
+      <c r="G559" s="15" t="n"/>
+      <c r="H559" s="15" t="n"/>
+      <c r="I559" s="15" t="n"/>
+      <c r="J559" s="15" t="n"/>
+      <c r="K559" s="15" t="n"/>
+    </row>
+    <row r="560">
+      <c r="A560" s="13" t="n"/>
+      <c r="B560" s="14" t="n"/>
+      <c r="C560" s="14" t="n"/>
+      <c r="D560" s="15" t="n"/>
+      <c r="E560" s="15" t="n"/>
+      <c r="F560" s="15" t="n"/>
+      <c r="G560" s="15" t="n"/>
+      <c r="H560" s="15" t="n"/>
+      <c r="I560" s="15" t="n"/>
+      <c r="J560" s="15" t="n"/>
+      <c r="K560" s="15" t="n"/>
+    </row>
+    <row r="561">
+      <c r="A561" s="13" t="n"/>
+      <c r="B561" s="14" t="n"/>
+      <c r="C561" s="14" t="n"/>
+      <c r="D561" s="15" t="n"/>
+      <c r="E561" s="15" t="n"/>
+      <c r="F561" s="15" t="n"/>
+      <c r="G561" s="15" t="n"/>
+      <c r="H561" s="15" t="n"/>
+      <c r="I561" s="15" t="n"/>
+      <c r="J561" s="15" t="n"/>
+      <c r="K561" s="15" t="n"/>
+    </row>
+    <row r="562">
+      <c r="A562" s="13" t="n"/>
+      <c r="B562" s="14" t="n"/>
+      <c r="C562" s="14" t="n"/>
+      <c r="D562" s="15" t="n"/>
+      <c r="E562" s="15" t="n"/>
+      <c r="F562" s="15" t="n"/>
+      <c r="G562" s="15" t="n"/>
+      <c r="H562" s="15" t="n"/>
+      <c r="I562" s="15" t="n"/>
+      <c r="J562" s="15" t="n"/>
+      <c r="K562" s="15" t="n"/>
+    </row>
+    <row r="563">
+      <c r="A563" s="13" t="n"/>
+      <c r="B563" s="14" t="n"/>
+      <c r="C563" s="14" t="n"/>
+      <c r="D563" s="15" t="n"/>
+      <c r="E563" s="15" t="n"/>
+      <c r="F563" s="15" t="n"/>
+      <c r="G563" s="15" t="n"/>
+      <c r="H563" s="15" t="n"/>
+      <c r="I563" s="15" t="n"/>
+      <c r="J563" s="15" t="n"/>
+      <c r="K563" s="15" t="n"/>
+    </row>
+    <row r="564">
+      <c r="A564" s="13" t="n"/>
+      <c r="B564" s="14" t="n"/>
+      <c r="C564" s="14" t="n"/>
+      <c r="D564" s="15" t="n"/>
+      <c r="E564" s="15" t="n"/>
+      <c r="F564" s="15" t="n"/>
+      <c r="G564" s="15" t="n"/>
+      <c r="H564" s="15" t="n"/>
+      <c r="I564" s="15" t="n"/>
+      <c r="J564" s="15" t="n"/>
+      <c r="K564" s="15" t="n"/>
+    </row>
+    <row r="565">
+      <c r="A565" s="13" t="n"/>
+      <c r="B565" s="14" t="n"/>
+      <c r="C565" s="14" t="n"/>
+      <c r="D565" s="15" t="n"/>
+      <c r="E565" s="15" t="n"/>
+      <c r="F565" s="15" t="n"/>
+      <c r="G565" s="15" t="n"/>
+      <c r="H565" s="15" t="n"/>
+      <c r="I565" s="15" t="n"/>
+      <c r="J565" s="15" t="n"/>
+      <c r="K565" s="15" t="n"/>
+    </row>
+    <row r="566">
+      <c r="A566" s="13" t="n"/>
+      <c r="B566" s="14" t="n"/>
+      <c r="C566" s="14" t="n"/>
+      <c r="D566" s="15" t="n"/>
+      <c r="E566" s="15" t="n"/>
+      <c r="F566" s="15" t="n"/>
+      <c r="G566" s="15" t="n"/>
+      <c r="H566" s="15" t="n"/>
+      <c r="I566" s="15" t="n"/>
+      <c r="J566" s="15" t="n"/>
+      <c r="K566" s="15" t="n"/>
+    </row>
+    <row r="567">
+      <c r="A567" s="13" t="n"/>
+      <c r="B567" s="14" t="n"/>
+      <c r="C567" s="14" t="n"/>
+      <c r="D567" s="15" t="n"/>
+      <c r="E567" s="15" t="n"/>
+      <c r="F567" s="15" t="n"/>
+      <c r="G567" s="15" t="n"/>
+      <c r="H567" s="15" t="n"/>
+      <c r="I567" s="15" t="n"/>
+      <c r="J567" s="15" t="n"/>
+      <c r="K567" s="15" t="n"/>
+    </row>
+    <row r="568">
+      <c r="A568" s="13" t="n"/>
+      <c r="B568" s="14" t="n"/>
+      <c r="C568" s="14" t="n"/>
+      <c r="D568" s="15" t="n"/>
+      <c r="E568" s="15" t="n"/>
+      <c r="F568" s="15" t="n"/>
+      <c r="G568" s="15" t="n"/>
+      <c r="H568" s="15" t="n"/>
+      <c r="I568" s="15" t="n"/>
+      <c r="J568" s="15" t="n"/>
+      <c r="K568" s="15" t="n"/>
+    </row>
+    <row r="569">
+      <c r="A569" s="13" t="n"/>
+      <c r="B569" s="14" t="n"/>
+      <c r="C569" s="14" t="n"/>
+      <c r="D569" s="15" t="n"/>
+      <c r="E569" s="15" t="n"/>
+      <c r="F569" s="15" t="n"/>
+      <c r="G569" s="15" t="n"/>
+      <c r="H569" s="15" t="n"/>
+      <c r="I569" s="15" t="n"/>
+      <c r="J569" s="15" t="n"/>
+      <c r="K569" s="15" t="n"/>
+    </row>
+    <row r="570">
+      <c r="A570" s="13" t="n"/>
+      <c r="B570" s="14" t="n"/>
+      <c r="C570" s="14" t="n"/>
+      <c r="D570" s="15" t="n"/>
+      <c r="E570" s="15" t="n"/>
+      <c r="F570" s="15" t="n"/>
+      <c r="G570" s="15" t="n"/>
+      <c r="H570" s="15" t="n"/>
+      <c r="I570" s="15" t="n"/>
+      <c r="J570" s="15" t="n"/>
+      <c r="K570" s="15" t="n"/>
+    </row>
+    <row r="571">
+      <c r="A571" s="13" t="n"/>
+      <c r="B571" s="14" t="n"/>
+      <c r="C571" s="14" t="n"/>
+      <c r="D571" s="15" t="n"/>
+      <c r="E571" s="15" t="n"/>
+      <c r="F571" s="15" t="n"/>
+      <c r="G571" s="15" t="n"/>
+      <c r="H571" s="15" t="n"/>
+      <c r="I571" s="15" t="n"/>
+      <c r="J571" s="15" t="n"/>
+      <c r="K571" s="15" t="n"/>
+    </row>
+    <row r="572">
+      <c r="A572" s="13" t="n"/>
+      <c r="B572" s="14" t="n"/>
+      <c r="C572" s="14" t="n"/>
+      <c r="D572" s="15" t="n"/>
+      <c r="E572" s="15" t="n"/>
+      <c r="F572" s="15" t="n"/>
+      <c r="G572" s="15" t="n"/>
+      <c r="H572" s="15" t="n"/>
+      <c r="I572" s="15" t="n"/>
+      <c r="J572" s="15" t="n"/>
+      <c r="K572" s="15" t="n"/>
+    </row>
+    <row r="573">
+      <c r="A573" s="13" t="n"/>
+      <c r="B573" s="14" t="n"/>
+      <c r="C573" s="14" t="n"/>
+      <c r="D573" s="15" t="n"/>
+      <c r="E573" s="15" t="n"/>
+      <c r="F573" s="15" t="n"/>
+      <c r="G573" s="15" t="n"/>
+      <c r="H573" s="15" t="n"/>
+      <c r="I573" s="15" t="n"/>
+      <c r="J573" s="15" t="n"/>
+      <c r="K573" s="15" t="n"/>
+    </row>
+    <row r="574">
+      <c r="A574" s="13" t="n"/>
+      <c r="B574" s="14" t="n"/>
+      <c r="C574" s="14" t="n"/>
+      <c r="D574" s="15" t="n"/>
+      <c r="E574" s="15" t="n"/>
+      <c r="F574" s="15" t="n"/>
+      <c r="G574" s="15" t="n"/>
+      <c r="H574" s="15" t="n"/>
+      <c r="I574" s="15" t="n"/>
+      <c r="J574" s="15" t="n"/>
+      <c r="K574" s="15" t="n"/>
+    </row>
+    <row r="575">
+      <c r="A575" s="13" t="n"/>
+      <c r="B575" s="14" t="n"/>
+      <c r="C575" s="14" t="n"/>
+      <c r="D575" s="15" t="n"/>
+      <c r="E575" s="15" t="n"/>
+      <c r="F575" s="15" t="n"/>
+      <c r="G575" s="15" t="n"/>
+      <c r="H575" s="15" t="n"/>
+      <c r="I575" s="15" t="n"/>
+      <c r="J575" s="15" t="n"/>
+      <c r="K575" s="15" t="n"/>
+    </row>
+    <row r="576">
+      <c r="A576" s="13" t="n"/>
+      <c r="B576" s="14" t="n"/>
+      <c r="C576" s="14" t="n"/>
+      <c r="D576" s="15" t="n"/>
+      <c r="E576" s="15" t="n"/>
+      <c r="F576" s="15" t="n"/>
+      <c r="G576" s="15" t="n"/>
+      <c r="H576" s="15" t="n"/>
+      <c r="I576" s="15" t="n"/>
+      <c r="J576" s="15" t="n"/>
+      <c r="K576" s="15" t="n"/>
+    </row>
+    <row r="577">
+      <c r="A577" s="13" t="n"/>
+      <c r="B577" s="14" t="n"/>
+      <c r="C577" s="14" t="n"/>
+      <c r="D577" s="15" t="n"/>
+      <c r="E577" s="15" t="n"/>
+      <c r="F577" s="15" t="n"/>
+      <c r="G577" s="15" t="n"/>
+      <c r="H577" s="15" t="n"/>
+      <c r="I577" s="15" t="n"/>
+      <c r="J577" s="15" t="n"/>
+      <c r="K577" s="15" t="n"/>
+    </row>
+    <row r="578">
+      <c r="A578" s="13" t="n"/>
+      <c r="B578" s="14" t="n"/>
+      <c r="C578" s="14" t="n"/>
+      <c r="D578" s="15" t="n"/>
+      <c r="E578" s="15" t="n"/>
+      <c r="F578" s="15" t="n"/>
+      <c r="G578" s="15" t="n"/>
+      <c r="H578" s="15" t="n"/>
+      <c r="I578" s="15" t="n"/>
+      <c r="J578" s="15" t="n"/>
+      <c r="K578" s="15" t="n"/>
+    </row>
+    <row r="579">
+      <c r="A579" s="13" t="n"/>
+      <c r="B579" s="14" t="n"/>
+      <c r="C579" s="14" t="n"/>
+      <c r="D579" s="15" t="n"/>
+      <c r="E579" s="15" t="n"/>
+      <c r="F579" s="15" t="n"/>
+      <c r="G579" s="15" t="n"/>
+      <c r="H579" s="15" t="n"/>
+      <c r="I579" s="15" t="n"/>
+      <c r="J579" s="15" t="n"/>
+      <c r="K579" s="15" t="n"/>
+    </row>
+    <row r="580">
+      <c r="A580" s="13" t="n"/>
+      <c r="B580" s="14" t="n"/>
+      <c r="C580" s="14" t="n"/>
+      <c r="D580" s="15" t="n"/>
+      <c r="E580" s="15" t="n"/>
+      <c r="F580" s="15" t="n"/>
+      <c r="G580" s="15" t="n"/>
+      <c r="H580" s="15" t="n"/>
+      <c r="I580" s="15" t="n"/>
+      <c r="J580" s="15" t="n"/>
+      <c r="K580" s="15" t="n"/>
+    </row>
+    <row r="581">
+      <c r="A581" s="13" t="n"/>
+      <c r="B581" s="14" t="n"/>
+      <c r="C581" s="14" t="n"/>
+      <c r="D581" s="15" t="n"/>
+      <c r="E581" s="15" t="n"/>
+      <c r="F581" s="15" t="n"/>
+      <c r="G581" s="15" t="n"/>
+      <c r="H581" s="15" t="n"/>
+      <c r="I581" s="15" t="n"/>
+      <c r="J581" s="15" t="n"/>
+      <c r="K581" s="15" t="n"/>
+    </row>
+    <row r="582">
+      <c r="A582" s="13" t="n"/>
+      <c r="B582" s="14" t="n"/>
+      <c r="C582" s="14" t="n"/>
+      <c r="D582" s="15" t="n"/>
+      <c r="E582" s="15" t="n"/>
+      <c r="F582" s="15" t="n"/>
+      <c r="G582" s="15" t="n"/>
+      <c r="H582" s="15" t="n"/>
+      <c r="I582" s="15" t="n"/>
+      <c r="J582" s="15" t="n"/>
+      <c r="K582" s="15" t="n"/>
+    </row>
+    <row r="583">
+      <c r="A583" s="13" t="n"/>
+      <c r="B583" s="14" t="n"/>
+      <c r="C583" s="14" t="n"/>
+      <c r="D583" s="15" t="n"/>
+      <c r="E583" s="15" t="n"/>
+      <c r="F583" s="15" t="n"/>
+      <c r="G583" s="15" t="n"/>
+      <c r="H583" s="15" t="n"/>
+      <c r="I583" s="15" t="n"/>
+      <c r="J583" s="15" t="n"/>
+      <c r="K583" s="15" t="n"/>
+    </row>
+    <row r="584">
+      <c r="A584" s="13" t="n"/>
+      <c r="B584" s="14" t="n"/>
+      <c r="C584" s="14" t="n"/>
+      <c r="D584" s="15" t="n"/>
+      <c r="E584" s="15" t="n"/>
+      <c r="F584" s="15" t="n"/>
+      <c r="G584" s="15" t="n"/>
+      <c r="H584" s="15" t="n"/>
+      <c r="I584" s="15" t="n"/>
+      <c r="J584" s="15" t="n"/>
+      <c r="K584" s="15" t="n"/>
+    </row>
+    <row r="585">
+      <c r="A585" s="13" t="n"/>
+      <c r="B585" s="14" t="n"/>
+      <c r="C585" s="14" t="n"/>
+      <c r="D585" s="15" t="n"/>
+      <c r="E585" s="15" t="n"/>
+      <c r="F585" s="15" t="n"/>
+      <c r="G585" s="15" t="n"/>
+      <c r="H585" s="15" t="n"/>
+      <c r="I585" s="15" t="n"/>
+      <c r="J585" s="15" t="n"/>
+      <c r="K585" s="15" t="n"/>
+    </row>
+    <row r="586">
+      <c r="A586" s="13" t="n"/>
+      <c r="B586" s="14" t="n"/>
+      <c r="C586" s="14" t="n"/>
+      <c r="D586" s="15" t="n"/>
+      <c r="E586" s="15" t="n"/>
+      <c r="F586" s="15" t="n"/>
+      <c r="G586" s="15" t="n"/>
+      <c r="H586" s="15" t="n"/>
+      <c r="I586" s="15" t="n"/>
+      <c r="J586" s="15" t="n"/>
+      <c r="K586" s="15" t="n"/>
+    </row>
+    <row r="587">
+      <c r="A587" s="13" t="n"/>
+      <c r="B587" s="14" t="n"/>
+      <c r="C587" s="14" t="n"/>
+      <c r="D587" s="15" t="n"/>
+      <c r="E587" s="15" t="n"/>
+      <c r="F587" s="15" t="n"/>
+      <c r="G587" s="15" t="n"/>
+      <c r="H587" s="15" t="n"/>
+      <c r="I587" s="15" t="n"/>
+      <c r="J587" s="15" t="n"/>
+      <c r="K587" s="15" t="n"/>
+    </row>
+    <row r="588">
+      <c r="A588" s="13" t="n"/>
+      <c r="B588" s="14" t="n"/>
+      <c r="C588" s="14" t="n"/>
+      <c r="D588" s="15" t="n"/>
+      <c r="E588" s="15" t="n"/>
+      <c r="F588" s="15" t="n"/>
+      <c r="G588" s="15" t="n"/>
+      <c r="H588" s="15" t="n"/>
+      <c r="I588" s="15" t="n"/>
+      <c r="J588" s="15" t="n"/>
+      <c r="K588" s="15" t="n"/>
+    </row>
+    <row r="589">
+      <c r="A589" s="13" t="n"/>
+      <c r="B589" s="14" t="n"/>
+      <c r="C589" s="14" t="n"/>
+      <c r="D589" s="15" t="n"/>
+      <c r="E589" s="15" t="n"/>
+      <c r="F589" s="15" t="n"/>
+      <c r="G589" s="15" t="n"/>
+      <c r="H589" s="15" t="n"/>
+      <c r="I589" s="15" t="n"/>
+      <c r="J589" s="15" t="n"/>
+      <c r="K589" s="15" t="n"/>
+    </row>
+    <row r="590">
+      <c r="A590" s="13" t="n"/>
+      <c r="B590" s="14" t="n"/>
+      <c r="C590" s="14" t="n"/>
+      <c r="D590" s="15" t="n"/>
+      <c r="E590" s="15" t="n"/>
+      <c r="F590" s="15" t="n"/>
+      <c r="G590" s="15" t="n"/>
+      <c r="H590" s="15" t="n"/>
+      <c r="I590" s="15" t="n"/>
+      <c r="J590" s="15" t="n"/>
+      <c r="K590" s="15" t="n"/>
+    </row>
+    <row r="591">
+      <c r="A591" s="13" t="n"/>
+      <c r="B591" s="14" t="n"/>
+      <c r="C591" s="14" t="n"/>
+      <c r="D591" s="15" t="n"/>
+      <c r="E591" s="15" t="n"/>
+      <c r="F591" s="15" t="n"/>
+      <c r="G591" s="15" t="n"/>
+      <c r="H591" s="15" t="n"/>
+      <c r="I591" s="15" t="n"/>
+      <c r="J591" s="15" t="n"/>
+      <c r="K591" s="15" t="n"/>
+    </row>
+    <row r="592">
+      <c r="A592" s="13" t="n"/>
+      <c r="B592" s="14" t="n"/>
+      <c r="C592" s="14" t="n"/>
+      <c r="D592" s="15" t="n"/>
+      <c r="E592" s="15" t="n"/>
+      <c r="F592" s="15" t="n"/>
+      <c r="G592" s="15" t="n"/>
+      <c r="H592" s="15" t="n"/>
+      <c r="I592" s="15" t="n"/>
+      <c r="J592" s="15" t="n"/>
+      <c r="K592" s="15" t="n"/>
+    </row>
+    <row r="593">
+      <c r="A593" s="13" t="n"/>
+      <c r="B593" s="14" t="n"/>
+      <c r="C593" s="14" t="n"/>
+      <c r="D593" s="15" t="n"/>
+      <c r="E593" s="15" t="n"/>
+      <c r="F593" s="15" t="n"/>
+      <c r="G593" s="15" t="n"/>
+      <c r="H593" s="15" t="n"/>
+      <c r="I593" s="15" t="n"/>
+      <c r="J593" s="15" t="n"/>
+      <c r="K593" s="15" t="n"/>
+    </row>
+    <row r="594">
+      <c r="A594" s="13" t="n"/>
+      <c r="B594" s="14" t="n"/>
+      <c r="C594" s="14" t="n"/>
+      <c r="D594" s="15" t="n"/>
+      <c r="E594" s="15" t="n"/>
+      <c r="F594" s="15" t="n"/>
+      <c r="G594" s="15" t="n"/>
+      <c r="H594" s="15" t="n"/>
+      <c r="I594" s="15" t="n"/>
+      <c r="J594" s="15" t="n"/>
+      <c r="K594" s="15" t="n"/>
+    </row>
+    <row r="595">
+      <c r="A595" s="13" t="n"/>
+      <c r="B595" s="14" t="n"/>
+      <c r="C595" s="14" t="n"/>
+      <c r="D595" s="15" t="n"/>
+      <c r="E595" s="15" t="n"/>
+      <c r="F595" s="15" t="n"/>
+      <c r="G595" s="15" t="n"/>
+      <c r="H595" s="15" t="n"/>
+      <c r="I595" s="15" t="n"/>
+      <c r="J595" s="15" t="n"/>
+      <c r="K595" s="15" t="n"/>
+    </row>
+    <row r="596">
+      <c r="A596" s="13" t="n"/>
+      <c r="B596" s="14" t="n"/>
+      <c r="C596" s="14" t="n"/>
+      <c r="D596" s="15" t="n"/>
+      <c r="E596" s="15" t="n"/>
+      <c r="F596" s="15" t="n"/>
+      <c r="G596" s="15" t="n"/>
+      <c r="H596" s="15" t="n"/>
+      <c r="I596" s="15" t="n"/>
+      <c r="J596" s="15" t="n"/>
+      <c r="K596" s="15" t="n"/>
+    </row>
+    <row r="597">
+      <c r="A597" s="13" t="n"/>
+      <c r="B597" s="14" t="n"/>
+      <c r="C597" s="14" t="n"/>
+      <c r="D597" s="15" t="n"/>
+      <c r="E597" s="15" t="n"/>
+      <c r="F597" s="15" t="n"/>
+      <c r="G597" s="15" t="n"/>
+      <c r="H597" s="15" t="n"/>
+      <c r="I597" s="15" t="n"/>
+      <c r="J597" s="15" t="n"/>
+      <c r="K597" s="15" t="n"/>
+    </row>
+    <row r="598">
+      <c r="A598" s="13" t="n"/>
+      <c r="B598" s="14" t="n"/>
+      <c r="C598" s="14" t="n"/>
+      <c r="D598" s="15" t="n"/>
+      <c r="E598" s="15" t="n"/>
+      <c r="F598" s="15" t="n"/>
+      <c r="G598" s="15" t="n"/>
+      <c r="H598" s="15" t="n"/>
+      <c r="I598" s="15" t="n"/>
+      <c r="J598" s="15" t="n"/>
+      <c r="K598" s="15" t="n"/>
+    </row>
+    <row r="599">
+      <c r="A599" s="13" t="n"/>
+      <c r="B599" s="14" t="n"/>
+      <c r="C599" s="14" t="n"/>
+      <c r="D599" s="15" t="n"/>
+      <c r="E599" s="15" t="n"/>
+      <c r="F599" s="15" t="n"/>
+      <c r="G599" s="15" t="n"/>
+      <c r="H599" s="15" t="n"/>
+      <c r="I599" s="15" t="n"/>
+      <c r="J599" s="15" t="n"/>
+      <c r="K599" s="15" t="n"/>
+    </row>
+    <row r="600">
+      <c r="A600" s="13" t="n"/>
+      <c r="B600" s="14" t="n"/>
+      <c r="C600" s="14" t="n"/>
+      <c r="D600" s="15" t="n"/>
+      <c r="E600" s="15" t="n"/>
+      <c r="F600" s="15" t="n"/>
+      <c r="G600" s="15" t="n"/>
+      <c r="H600" s="15" t="n"/>
+      <c r="I600" s="15" t="n"/>
+      <c r="J600" s="15" t="n"/>
+      <c r="K600" s="15" t="n"/>
+    </row>
+    <row r="601">
+      <c r="A601" s="13" t="n"/>
+      <c r="B601" s="14" t="n"/>
+      <c r="C601" s="14" t="n"/>
+      <c r="D601" s="15" t="n"/>
+      <c r="E601" s="15" t="n"/>
+      <c r="F601" s="15" t="n"/>
+      <c r="G601" s="15" t="n"/>
+      <c r="H601" s="15" t="n"/>
+      <c r="I601" s="15" t="n"/>
+      <c r="J601" s="15" t="n"/>
+      <c r="K601" s="15" t="n"/>
+    </row>
+    <row r="602">
+      <c r="A602" s="13" t="n"/>
+      <c r="B602" s="14" t="n"/>
+      <c r="C602" s="14" t="n"/>
+      <c r="D602" s="15" t="n"/>
+      <c r="E602" s="15" t="n"/>
+      <c r="F602" s="15" t="n"/>
+      <c r="G602" s="15" t="n"/>
+      <c r="H602" s="15" t="n"/>
+      <c r="I602" s="15" t="n"/>
+      <c r="J602" s="15" t="n"/>
+      <c r="K602" s="15" t="n"/>
+    </row>
+    <row r="603">
+      <c r="A603" s="13" t="n"/>
+      <c r="B603" s="14" t="n"/>
+      <c r="C603" s="14" t="n"/>
+      <c r="D603" s="15" t="n"/>
+      <c r="E603" s="15" t="n"/>
+      <c r="F603" s="15" t="n"/>
+      <c r="G603" s="15" t="n"/>
+      <c r="H603" s="15" t="n"/>
+      <c r="I603" s="15" t="n"/>
+      <c r="J603" s="15" t="n"/>
+      <c r="K603" s="15" t="n"/>
+    </row>
+    <row r="604">
+      <c r="A604" s="13" t="n"/>
+      <c r="B604" s="14" t="n"/>
+      <c r="C604" s="14" t="n"/>
+      <c r="D604" s="15" t="n"/>
+      <c r="E604" s="15" t="n"/>
+      <c r="F604" s="15" t="n"/>
+      <c r="G604" s="15" t="n"/>
+      <c r="H604" s="15" t="n"/>
+      <c r="I604" s="15" t="n"/>
+      <c r="J604" s="15" t="n"/>
+      <c r="K604" s="15" t="n"/>
+    </row>
+    <row r="605">
+      <c r="A605" s="13" t="n"/>
+      <c r="B605" s="14" t="n"/>
+      <c r="C605" s="14" t="n"/>
+      <c r="D605" s="15" t="n"/>
+      <c r="E605" s="15" t="n"/>
+      <c r="F605" s="15" t="n"/>
+      <c r="G605" s="15" t="n"/>
+      <c r="H605" s="15" t="n"/>
+      <c r="I605" s="15" t="n"/>
+      <c r="J605" s="15" t="n"/>
+      <c r="K605" s="15" t="n"/>
+    </row>
+    <row r="606">
+      <c r="A606" s="13" t="n"/>
+      <c r="B606" s="14" t="n"/>
+      <c r="C606" s="14" t="n"/>
+      <c r="D606" s="15" t="n"/>
+      <c r="E606" s="15" t="n"/>
+      <c r="F606" s="15" t="n"/>
+      <c r="G606" s="15" t="n"/>
+      <c r="H606" s="15" t="n"/>
+      <c r="I606" s="15" t="n"/>
+      <c r="J606" s="15" t="n"/>
+      <c r="K606" s="15" t="n"/>
+    </row>
+    <row r="607">
+      <c r="A607" s="13" t="n"/>
+      <c r="B607" s="14" t="n"/>
+      <c r="C607" s="14" t="n"/>
+      <c r="D607" s="15" t="n"/>
+      <c r="E607" s="15" t="n"/>
+      <c r="F607" s="15" t="n"/>
+      <c r="G607" s="15" t="n"/>
+      <c r="H607" s="15" t="n"/>
+      <c r="I607" s="15" t="n"/>
+      <c r="J607" s="15" t="n"/>
+      <c r="K607" s="15" t="n"/>
+    </row>
+    <row r="608">
+      <c r="A608" s="13" t="n"/>
+      <c r="B608" s="14" t="n"/>
+      <c r="C608" s="14" t="n"/>
+      <c r="D608" s="15" t="n"/>
+      <c r="E608" s="15" t="n"/>
+      <c r="F608" s="15" t="n"/>
+      <c r="G608" s="15" t="n"/>
+      <c r="H608" s="15" t="n"/>
+      <c r="I608" s="15" t="n"/>
+      <c r="J608" s="15" t="n"/>
+      <c r="K608" s="15" t="n"/>
+    </row>
+    <row r="609">
+      <c r="A609" s="13" t="n"/>
+      <c r="B609" s="14" t="n"/>
+      <c r="C609" s="14" t="n"/>
+      <c r="D609" s="15" t="n"/>
+      <c r="E609" s="15" t="n"/>
+      <c r="F609" s="15" t="n"/>
+      <c r="G609" s="15" t="n"/>
+      <c r="H609" s="15" t="n"/>
+      <c r="I609" s="15" t="n"/>
+      <c r="J609" s="15" t="n"/>
+      <c r="K609" s="15" t="n"/>
+    </row>
+    <row r="610">
+      <c r="A610" s="13" t="n"/>
+      <c r="B610" s="14" t="n"/>
+      <c r="C610" s="14" t="n"/>
+      <c r="D610" s="15" t="n"/>
+      <c r="E610" s="15" t="n"/>
+      <c r="F610" s="15" t="n"/>
+      <c r="G610" s="15" t="n"/>
+      <c r="H610" s="15" t="n"/>
+      <c r="I610" s="15" t="n"/>
+      <c r="J610" s="15" t="n"/>
+      <c r="K610" s="15" t="n"/>
+    </row>
+    <row r="611">
+      <c r="A611" s="13" t="n"/>
+      <c r="B611" s="14" t="n"/>
+      <c r="C611" s="14" t="n"/>
+      <c r="D611" s="15" t="n"/>
+      <c r="E611" s="15" t="n"/>
+      <c r="F611" s="15" t="n"/>
+      <c r="G611" s="15" t="n"/>
+      <c r="H611" s="15" t="n"/>
+      <c r="I611" s="15" t="n"/>
+      <c r="J611" s="15" t="n"/>
+      <c r="K611" s="15" t="n"/>
+    </row>
+    <row r="612">
+      <c r="A612" s="13" t="n"/>
+      <c r="B612" s="14" t="n"/>
+      <c r="C612" s="14" t="n"/>
+      <c r="D612" s="15" t="n"/>
+      <c r="E612" s="15" t="n"/>
+      <c r="F612" s="15" t="n"/>
+      <c r="G612" s="15" t="n"/>
+      <c r="H612" s="15" t="n"/>
+      <c r="I612" s="15" t="n"/>
+      <c r="J612" s="15" t="n"/>
+      <c r="K612" s="15" t="n"/>
+    </row>
+    <row r="613">
+      <c r="A613" s="13" t="n"/>
+      <c r="B613" s="14" t="n"/>
+      <c r="C613" s="14" t="n"/>
+      <c r="D613" s="15" t="n"/>
+      <c r="E613" s="15" t="n"/>
+      <c r="F613" s="15" t="n"/>
+      <c r="G613" s="15" t="n"/>
+      <c r="H613" s="15" t="n"/>
+      <c r="I613" s="15" t="n"/>
+      <c r="J613" s="15" t="n"/>
+      <c r="K613" s="15" t="n"/>
+    </row>
+    <row r="614">
+      <c r="A614" s="13" t="n"/>
+      <c r="B614" s="14" t="n"/>
+      <c r="C614" s="14" t="n"/>
+      <c r="D614" s="15" t="n"/>
+      <c r="E614" s="15" t="n"/>
+      <c r="F614" s="15" t="n"/>
+      <c r="G614" s="15" t="n"/>
+      <c r="H614" s="15" t="n"/>
+      <c r="I614" s="15" t="n"/>
+      <c r="J614" s="15" t="n"/>
+      <c r="K614" s="15" t="n"/>
+    </row>
+    <row r="615">
+      <c r="A615" s="13" t="n"/>
+      <c r="B615" s="14" t="n"/>
+      <c r="C615" s="14" t="n"/>
+      <c r="D615" s="15" t="n"/>
+      <c r="E615" s="15" t="n"/>
+      <c r="F615" s="15" t="n"/>
+      <c r="G615" s="15" t="n"/>
+      <c r="H615" s="15" t="n"/>
+      <c r="I615" s="15" t="n"/>
+      <c r="J615" s="15" t="n"/>
+      <c r="K615" s="15" t="n"/>
+    </row>
+    <row r="616">
+      <c r="A616" s="13" t="n"/>
+      <c r="B616" s="14" t="n"/>
+      <c r="C616" s="14" t="n"/>
+      <c r="D616" s="15" t="n"/>
+      <c r="E616" s="15" t="n"/>
+      <c r="F616" s="15" t="n"/>
+      <c r="G616" s="15" t="n"/>
+      <c r="H616" s="15" t="n"/>
+      <c r="I616" s="15" t="n"/>
+      <c r="J616" s="15" t="n"/>
+      <c r="K616" s="15" t="n"/>
+    </row>
+    <row r="617">
+      <c r="A617" s="13" t="n"/>
+      <c r="B617" s="14" t="n"/>
+      <c r="C617" s="14" t="n"/>
+      <c r="D617" s="15" t="n"/>
+      <c r="E617" s="15" t="n"/>
+      <c r="F617" s="15" t="n"/>
+      <c r="G617" s="15" t="n"/>
+      <c r="H617" s="15" t="n"/>
+      <c r="I617" s="15" t="n"/>
+      <c r="J617" s="15" t="n"/>
+      <c r="K617" s="15" t="n"/>
+    </row>
+    <row r="618">
+      <c r="A618" s="13" t="n"/>
+      <c r="B618" s="14" t="n"/>
+      <c r="C618" s="14" t="n"/>
+      <c r="D618" s="15" t="n"/>
+      <c r="E618" s="15" t="n"/>
+      <c r="F618" s="15" t="n"/>
+      <c r="G618" s="15" t="n"/>
+      <c r="H618" s="15" t="n"/>
+      <c r="I618" s="15" t="n"/>
+      <c r="J618" s="15" t="n"/>
+      <c r="K618" s="15" t="n"/>
+    </row>
+    <row r="619">
+      <c r="A619" s="13" t="n"/>
+      <c r="B619" s="14" t="n"/>
+      <c r="C619" s="14" t="n"/>
+      <c r="D619" s="15" t="n"/>
+      <c r="E619" s="15" t="n"/>
+      <c r="F619" s="15" t="n"/>
+      <c r="G619" s="15" t="n"/>
+      <c r="H619" s="15" t="n"/>
+      <c r="I619" s="15" t="n"/>
+      <c r="J619" s="15" t="n"/>
+      <c r="K619" s="15" t="n"/>
+    </row>
+    <row r="620">
+      <c r="A620" s="13" t="n"/>
+      <c r="B620" s="14" t="n"/>
+      <c r="C620" s="14" t="n"/>
+      <c r="D620" s="15" t="n"/>
+      <c r="E620" s="15" t="n"/>
+      <c r="F620" s="15" t="n"/>
+      <c r="G620" s="15" t="n"/>
+      <c r="H620" s="15" t="n"/>
+      <c r="I620" s="15" t="n"/>
+      <c r="J620" s="15" t="n"/>
+      <c r="K620" s="15" t="n"/>
+    </row>
+    <row r="630">
+      <c r="A630" s="16" t="inlineStr">
         <is>
           <t>▶ 按钮"列举杂质"由构建脚本自动放置（E40 区域）</t>
         </is>

--- a/ExactMass_Impurities.xlsx
+++ b/ExactMass_Impurities.xlsx
@@ -1848,7 +1848,11 @@
           <t>H</t>
         </is>
       </c>
-      <c r="D3" s="8" t="n"/>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
       <c r="E3" s="8" t="n"/>
       <c r="F3" s="8" t="n"/>
       <c r="G3" s="8" t="n"/>
@@ -1886,10 +1890,14 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
+          <t>natural</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="8" t="n"/>
       <c r="E4" s="8" t="n"/>
       <c r="F4" s="8" t="n"/>
       <c r="G4" s="8" t="n"/>
@@ -1921,12 +1929,14 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="D5" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="9" t="n"/>
       <c r="E5" s="9" t="n"/>
       <c r="F5" s="9" t="n"/>
       <c r="G5" s="9" t="n"/>
